--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -616,7 +616,7 @@
     <t>Rangers</t>
   </si>
   <si>
-    <t>2026-08-31 19:44:46</t>
+    <t>2026-08-31 21:58:10</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
         <v>155</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
         <v>1.72</v>
@@ -1222,13 +1222,13 @@
         <v>7.2</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1237,7 +1237,7 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
         <v>1.9</v>
@@ -1249,19 +1249,19 @@
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X2">
         <v>17</v>
@@ -1324,34 +1324,34 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1360,16 +1360,16 @@
         <v>14</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH2">
         <v>3.8</v>
@@ -1697,13 +1697,13 @@
         <v>1.53</v>
       </c>
       <c r="G4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>4.5</v>
@@ -1745,7 +1745,7 @@
         <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X4">
         <v>28</v>
@@ -1781,7 +1781,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1790,7 +1790,7 @@
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AM4">
         <v>110</v>
@@ -1808,7 +1808,7 @@
         <v>18.5</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AS4">
         <v>11</v>
@@ -1904,7 +1904,7 @@
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
@@ -1936,19 +1936,19 @@
         <v>158</v>
       </c>
       <c r="F5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
         <v>3.65</v>
@@ -1960,34 +1960,34 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X5">
         <v>14.5</v>
@@ -1996,25 +1996,25 @@
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA5">
         <v>32</v>
       </c>
       <c r="AB5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE5">
         <v>28</v>
       </c>
       <c r="AF5">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AG5">
         <v>17</v>
@@ -2044,10 +2044,10 @@
         <v>19</v>
       </c>
       <c r="AP5">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
         <v>11</v>
@@ -2062,16 +2062,16 @@
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW5">
         <v>20</v>
       </c>
       <c r="AX5">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ5">
         <v>16</v>
@@ -2080,22 +2080,22 @@
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC5">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2217,7 +2217,7 @@
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
         <v>1.63</v>
@@ -2322,7 +2322,7 @@
         <v>6.6</v>
       </c>
       <c r="BB6">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BC6">
         <v>7</v>
@@ -2420,19 +2420,19 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G7">
         <v>4.5</v>
       </c>
       <c r="H7">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
         <v>3.25</v>
@@ -2441,43 +2441,43 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P7">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
         <v>2.54</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
         <v>5.3</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X7">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>14.5</v>
@@ -2525,61 +2525,61 @@
         <v>130</v>
       </c>
       <c r="AO7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BB7">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC7">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD7">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE7">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BG7">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2674,7 +2674,7 @@
         <v>2.06</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
         <v>3.8</v>
@@ -2692,28 +2692,28 @@
         <v>1.32</v>
       </c>
       <c r="P8">
+        <v>1.97</v>
+      </c>
+      <c r="Q8">
         <v>1.96</v>
       </c>
-      <c r="Q8">
-        <v>1.95</v>
-      </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8">
         <v>3.45</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="U8">
         <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X8">
         <v>14.5</v>
@@ -2722,13 +2722,13 @@
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AA8">
         <v>27</v>
       </c>
       <c r="AB8">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>13</v>
       </c>
       <c r="AQ8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR8">
         <v>11</v>
@@ -2788,13 +2788,13 @@
         <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW8">
         <v>19</v>
       </c>
       <c r="AX8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY8">
         <v>15</v>
@@ -2803,25 +2803,25 @@
         <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC8">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF8">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2916,13 +2916,13 @@
         <v>3.85</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
         <v>4</v>
       </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2946,19 +2946,19 @@
         <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U9">
         <v>2.16</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.59</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
         <v>16.5</v>
@@ -3021,7 +3021,7 @@
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="AT9">
         <v>9</v>
@@ -3030,10 +3030,10 @@
         <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AW9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX9">
         <v>13</v>
@@ -3045,31 +3045,31 @@
         <v>15</v>
       </c>
       <c r="BA9">
+        <v>4.4</v>
+      </c>
+      <c r="BB9">
+        <v>4.2</v>
+      </c>
+      <c r="BC9">
+        <v>4.1</v>
+      </c>
+      <c r="BD9">
+        <v>4.3</v>
+      </c>
+      <c r="BE9">
         <v>4.6</v>
-      </c>
-      <c r="BB9">
-        <v>4.3</v>
-      </c>
-      <c r="BC9">
-        <v>4.3</v>
-      </c>
-      <c r="BD9">
-        <v>4.5</v>
-      </c>
-      <c r="BE9">
-        <v>4.8</v>
       </c>
       <c r="BF9">
         <v>13.5</v>
       </c>
       <c r="BG9">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI9">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
@@ -3090,7 +3090,7 @@
         <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
@@ -3114,7 +3114,7 @@
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
@@ -3146,25 +3146,25 @@
         <v>163</v>
       </c>
       <c r="F10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H10">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I10">
         <v>2.08</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
         <v>1.08</v>
@@ -3173,61 +3173,61 @@
         <v>3.35</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q10">
         <v>2.06</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W10">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X10">
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH10">
         <v>23</v>
@@ -3236,28 +3236,28 @@
         <v>48</v>
       </c>
       <c r="AJ10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK10">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AL10">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="AM10">
         <v>140</v>
       </c>
       <c r="AN10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP10">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR10">
         <v>10.5</v>
@@ -3266,10 +3266,10 @@
         <v>18.5</v>
       </c>
       <c r="AT10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
         <v>9.4</v>
@@ -3281,31 +3281,31 @@
         <v>24</v>
       </c>
       <c r="AY10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ10">
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC10">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD10">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BE10">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF10">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH10">
         <v>3.6</v>
@@ -3320,16 +3320,16 @@
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>44</v>
@@ -3347,7 +3347,7 @@
         <v>5.2</v>
       </c>
       <c r="BU10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV10">
         <v>17</v>
@@ -3362,7 +3362,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3418,22 +3418,22 @@
         <v>1.29</v>
       </c>
       <c r="P11">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
         <v>3.15</v>
       </c>
       <c r="T11">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="V11">
         <v>1.3</v>
@@ -3484,7 +3484,7 @@
         <v>22</v>
       </c>
       <c r="AL11">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -3517,7 +3517,7 @@
         <v>12.5</v>
       </c>
       <c r="AW11">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX11">
         <v>11</v>
@@ -3529,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>25</v>
+        <v>6.4</v>
       </c>
       <c r="BB11">
         <v>20</v>
@@ -3538,7 +3538,7 @@
         <v>17.5</v>
       </c>
       <c r="BD11">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="BE11">
         <v>6.6</v>
@@ -3633,10 +3633,10 @@
         <v>2.58</v>
       </c>
       <c r="G12">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
         <v>3.25</v>
@@ -3654,13 +3654,13 @@
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q12">
         <v>2.34</v>
@@ -3669,10 +3669,10 @@
         <v>1.24</v>
       </c>
       <c r="S12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T12">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U12">
         <v>1.92</v>
@@ -3681,7 +3681,7 @@
         <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X12">
         <v>10.5</v>
@@ -3690,7 +3690,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AA12">
         <v>70</v>
@@ -3714,7 +3714,7 @@
         <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>75</v>
@@ -3762,34 +3762,34 @@
         <v>6.8</v>
       </c>
       <c r="AX12">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BA12">
         <v>7</v>
       </c>
       <c r="BB12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC12">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BD12">
         <v>7</v>
       </c>
       <c r="BE12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF12">
         <v>6.6</v>
       </c>
       <c r="BG12">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3875,7 +3875,7 @@
         <v>2.9</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="H13">
         <v>3.05</v>
@@ -3884,7 +3884,7 @@
         <v>3.35</v>
       </c>
       <c r="J13">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="K13">
         <v>3.1</v>
@@ -3893,19 +3893,19 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O13">
         <v>1.74</v>
       </c>
       <c r="P13">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Q13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
         <v>1.13</v>
@@ -3923,7 +3923,7 @@
         <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X13">
         <v>7.8</v>
@@ -4037,7 +4037,7 @@
         <v>2.74</v>
       </c>
       <c r="BI13">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -4126,7 +4126,7 @@
         <v>970</v>
       </c>
       <c r="J14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
         <v>1000</v>
@@ -4162,10 +4162,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4356,7 +4356,7 @@
         <v>168</v>
       </c>
       <c r="F15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G15">
         <v>110</v>
@@ -4365,10 +4365,10 @@
         <v>1.08</v>
       </c>
       <c r="I15">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K15">
         <v>1000</v>
@@ -4380,13 +4380,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O15">
         <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
         <v>1.44</v>
@@ -4404,10 +4404,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4849,13 +4849,13 @@
         <v>3.9</v>
       </c>
       <c r="I17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
         <v>3.65</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4870,10 +4870,10 @@
         <v>1.3</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R17">
         <v>1.4</v>
@@ -4882,19 +4882,19 @@
         <v>3.2</v>
       </c>
       <c r="T17">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="U17">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
         <v>1.89</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y17">
         <v>16</v>
@@ -4954,10 +4954,10 @@
         <v>13.5</v>
       </c>
       <c r="AR17">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
         <v>8.800000000000001</v>
@@ -4969,7 +4969,7 @@
         <v>14.5</v>
       </c>
       <c r="AW17">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
         <v>11.5</v>
@@ -4978,46 +4978,46 @@
         <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>12</v>
       </c>
       <c r="BG17">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>4.5</v>
       </c>
       <c r="BI17">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17">
         <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
         <v>6.8</v>
@@ -5029,13 +5029,13 @@
         <v>20</v>
       </c>
       <c r="BQ17">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
         <v>40</v>
       </c>
       <c r="BS17">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
         <v>10.5</v>
@@ -5047,19 +5047,19 @@
         <v>46</v>
       </c>
       <c r="BW17">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>55</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>34</v>
       </c>
       <c r="CA17">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>200</v>
@@ -5082,46 +5082,46 @@
         <v>171</v>
       </c>
       <c r="F18">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="H18">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="I18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="J18">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="K18">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="L18">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="O18">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P18">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
         <v>1.3</v>
       </c>
       <c r="S18">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5130,88 +5130,88 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
       </c>
       <c r="AK18">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
         <v>1000</v>
       </c>
       <c r="AO18">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
         <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
         <v>1.01</v>
@@ -5241,7 +5241,7 @@
         <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5396,7 +5396,7 @@
         <v>7.4</v>
       </c>
       <c r="AD19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE19">
         <v>95</v>
@@ -5405,7 +5405,7 @@
         <v>12</v>
       </c>
       <c r="AG19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH19">
         <v>30</v>
@@ -5450,7 +5450,7 @@
         <v>6.6</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW19">
         <v>1.01</v>
@@ -5584,22 +5584,22 @@
         <v>4.9</v>
       </c>
       <c r="L20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
         <v>1.3</v>
       </c>
       <c r="P20">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q20">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="R20">
         <v>1.3</v>
@@ -5970,10 +5970,10 @@
         <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ21">
         <v>13.5</v>
@@ -6050,16 +6050,16 @@
         <v>175</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G22">
         <v>3.6</v>
       </c>
       <c r="H22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J22">
         <v>3.8</v>
@@ -6074,16 +6074,16 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>4.7</v>
+        <v>2.26</v>
       </c>
       <c r="O22">
         <v>1.2</v>
       </c>
       <c r="P22">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q22">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R22">
         <v>1.51</v>
@@ -6092,13 +6092,13 @@
         <v>2.52</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U22">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W22">
         <v>1.38</v>
@@ -6313,7 +6313,7 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
         <v>5.1</v>
@@ -6325,10 +6325,10 @@
         <v>2.42</v>
       </c>
       <c r="Q23">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S23">
         <v>2.42</v>
@@ -6558,16 +6558,16 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O24">
         <v>1.18</v>
       </c>
       <c r="P24">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="R24">
         <v>1.64</v>
@@ -6776,7 +6776,7 @@
         <v>178</v>
       </c>
       <c r="F25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G25">
         <v>1.72</v>
@@ -6806,13 +6806,13 @@
         <v>1.1</v>
       </c>
       <c r="P25">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q25">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R25">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S25">
         <v>1.94</v>
@@ -7054,10 +7054,10 @@
         <v>1.49</v>
       </c>
       <c r="R26">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S26">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7186,7 +7186,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK26">
         <v>5.3</v>
@@ -7290,22 +7290,22 @@
         <v>1.17</v>
       </c>
       <c r="P27">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R27">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="S27">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T27">
         <v>1.54</v>
       </c>
       <c r="U27">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="V27">
         <v>1.33</v>
@@ -7326,7 +7326,7 @@
         <v>85</v>
       </c>
       <c r="AB27">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC27">
         <v>13</v>
@@ -7341,13 +7341,13 @@
         <v>15.5</v>
       </c>
       <c r="AG27">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
         <v>17</v>
       </c>
       <c r="AI27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ27">
         <v>24</v>
@@ -7359,10 +7359,10 @@
         <v>26</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN27">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO27">
         <v>26</v>
@@ -7395,7 +7395,7 @@
         <v>11</v>
       </c>
       <c r="AY27">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ27">
         <v>11.5</v>
@@ -7410,10 +7410,10 @@
         <v>13</v>
       </c>
       <c r="BD27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE27">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BF27">
         <v>6</v>
@@ -7520,7 +7520,7 @@
         <v>4.1</v>
       </c>
       <c r="L28">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M28">
         <v>1.06</v>
@@ -7595,7 +7595,7 @@
         <v>80</v>
       </c>
       <c r="AK28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL28">
         <v>55</v>
@@ -7619,7 +7619,7 @@
         <v>12</v>
       </c>
       <c r="AS28">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28">
         <v>14</v>
@@ -7634,7 +7634,7 @@
         <v>18.5</v>
       </c>
       <c r="AX28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY28">
         <v>14</v>
@@ -7646,7 +7646,7 @@
         <v>23</v>
       </c>
       <c r="BB28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC28">
         <v>28</v>
@@ -7655,7 +7655,7 @@
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF28">
         <v>23</v>
@@ -7664,10 +7664,10 @@
         <v>11.5</v>
       </c>
       <c r="BH28">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BI28">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ28">
         <v>10.5</v>
@@ -7756,7 +7756,7 @@
         <v>110</v>
       </c>
       <c r="J29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K29">
         <v>1000</v>
@@ -7768,13 +7768,13 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O29">
         <v>1.02</v>
       </c>
       <c r="P29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q29">
         <v>1.51</v>
@@ -7792,10 +7792,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7986,13 +7986,13 @@
         <v>183</v>
       </c>
       <c r="F30">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H30">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I30">
         <v>4.1</v>
@@ -8007,25 +8007,25 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N30">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O30">
         <v>1.26</v>
       </c>
       <c r="P30">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q30">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="R30">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S30">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="T30">
         <v>1.63</v>
@@ -8037,7 +8037,7 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="X30">
         <v>20</v>
@@ -8052,7 +8052,7 @@
         <v>80</v>
       </c>
       <c r="AB30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC30">
         <v>9.6</v>
@@ -8115,7 +8115,7 @@
         <v>12.5</v>
       </c>
       <c r="AW30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX30">
         <v>12</v>
@@ -8127,7 +8127,7 @@
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB30">
         <v>20</v>
@@ -8136,16 +8136,16 @@
         <v>16.5</v>
       </c>
       <c r="BD30">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE30">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF30">
         <v>8.6</v>
       </c>
       <c r="BG30">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH30">
         <v>4.4</v>
@@ -8184,13 +8184,13 @@
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU30">
         <v>5.8</v>
       </c>
       <c r="BV30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
@@ -8234,7 +8234,7 @@
         <v>3.05</v>
       </c>
       <c r="H31">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I31">
         <v>2.72</v>
@@ -8258,16 +8258,16 @@
         <v>1.28</v>
       </c>
       <c r="P31">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q31">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R31">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T31">
         <v>1.64</v>
@@ -8288,10 +8288,10 @@
         <v>13.5</v>
       </c>
       <c r="Z31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA31">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB31">
         <v>14.5</v>
@@ -8300,28 +8300,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE31">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF31">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG31">
         <v>13</v>
       </c>
       <c r="AH31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI31">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ31">
         <v>48</v>
       </c>
       <c r="AK31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL31">
         <v>46</v>
@@ -8330,10 +8330,10 @@
         <v>90</v>
       </c>
       <c r="AN31">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO31">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP31">
         <v>14</v>
@@ -8345,7 +8345,7 @@
         <v>16.5</v>
       </c>
       <c r="AS31">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
@@ -8357,7 +8357,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX31">
         <v>18</v>
@@ -8369,19 +8369,19 @@
         <v>13.5</v>
       </c>
       <c r="BA31">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB31">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC31">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BD31">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BE31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF31">
         <v>18.5</v>
@@ -8476,13 +8476,13 @@
         <v>2.84</v>
       </c>
       <c r="H32">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I32">
         <v>2.84</v>
       </c>
       <c r="J32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
         <v>3.7</v>
@@ -8494,7 +8494,7 @@
         <v>1.06</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O32">
         <v>1.29</v>
@@ -8503,16 +8503,16 @@
         <v>2.02</v>
       </c>
       <c r="Q32">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R32">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S32">
         <v>3.2</v>
       </c>
       <c r="T32">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U32">
         <v>2.24</v>
@@ -8632,10 +8632,10 @@
         <v>18.5</v>
       </c>
       <c r="BH32">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BI32">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="BJ32">
         <v>10.5</v>
@@ -8874,10 +8874,10 @@
         <v>7.6</v>
       </c>
       <c r="BH33">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
         <v>13</v>
@@ -8957,7 +8957,7 @@
         <v>2</v>
       </c>
       <c r="G34">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H34">
         <v>4.1</v>
@@ -8975,25 +8975,25 @@
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
         <v>3.2</v>
       </c>
       <c r="O34">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P34">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q34">
         <v>2.12</v>
       </c>
       <c r="R34">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S34">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="T34">
         <v>1.89</v>
@@ -9005,7 +9005,7 @@
         <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X34">
         <v>14</v>
@@ -9122,7 +9122,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ34">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
         <v>1.01</v>
@@ -9134,43 +9134,43 @@
         <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP34">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV34">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
         <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
         <v>1.01</v>
       </c>
       <c r="BZ34">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA34">
         <v>1.01</v>
@@ -9199,7 +9199,7 @@
         <v>1.23</v>
       </c>
       <c r="G35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H35">
         <v>14</v>
@@ -9223,19 +9223,19 @@
         <v>7.4</v>
       </c>
       <c r="O35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P35">
         <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R35">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S35">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="T35">
         <v>1.87</v>
@@ -9247,7 +9247,7 @@
         <v>1.06</v>
       </c>
       <c r="W35">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="X35">
         <v>40</v>
@@ -9271,7 +9271,7 @@
         <v>55</v>
       </c>
       <c r="AE35">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF35">
         <v>10</v>
@@ -9283,7 +9283,7 @@
         <v>32</v>
       </c>
       <c r="AI35">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ35">
         <v>10.5</v>
@@ -9295,7 +9295,7 @@
         <v>34</v>
       </c>
       <c r="AM35">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN35">
         <v>3.45</v>
@@ -9444,7 +9444,7 @@
         <v>2.48</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I36">
         <v>3.35</v>
@@ -9477,7 +9477,7 @@
         <v>1.5</v>
       </c>
       <c r="S36">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T36">
         <v>1.52</v>
@@ -9507,7 +9507,7 @@
         <v>15</v>
       </c>
       <c r="AC36">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36">
         <v>17</v>
@@ -9555,7 +9555,7 @@
         <v>20</v>
       </c>
       <c r="AS36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT36">
         <v>10.5</v>
@@ -9582,7 +9582,7 @@
         <v>5</v>
       </c>
       <c r="BB36">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC36">
         <v>19.5</v>
@@ -9591,7 +9591,7 @@
         <v>4.9</v>
       </c>
       <c r="BE36">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF36">
         <v>12.5</v>
@@ -9698,7 +9698,7 @@
         <v>4.2</v>
       </c>
       <c r="L37">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M37">
         <v>1.05</v>
@@ -9719,7 +9719,7 @@
         <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T37">
         <v>1.7</v>
@@ -9755,7 +9755,7 @@
         <v>15.5</v>
       </c>
       <c r="AE37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF37">
         <v>14</v>
@@ -9770,7 +9770,7 @@
         <v>46</v>
       </c>
       <c r="AJ37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK37">
         <v>19.5</v>
@@ -9803,7 +9803,7 @@
         <v>10</v>
       </c>
       <c r="AU37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV37">
         <v>14</v>
@@ -9830,10 +9830,10 @@
         <v>17.5</v>
       </c>
       <c r="BD37">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE37">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF37">
         <v>10</v>
@@ -9928,7 +9928,7 @@
         <v>2.44</v>
       </c>
       <c r="H38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I38">
         <v>3.4</v>
@@ -9946,7 +9946,7 @@
         <v>1.07</v>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O38">
         <v>1.33</v>
@@ -9967,10 +9967,10 @@
         <v>1.78</v>
       </c>
       <c r="U38">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
         <v>1.69</v>
@@ -10039,7 +10039,7 @@
         <v>20</v>
       </c>
       <c r="AS38">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT38">
         <v>9.6</v>
@@ -10069,7 +10069,7 @@
         <v>29</v>
       </c>
       <c r="BC38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD38">
         <v>34</v>
@@ -10123,7 +10123,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU38">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV38">
         <v>36</v>
@@ -10164,13 +10164,13 @@
         <v>192</v>
       </c>
       <c r="F39">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G39">
         <v>1.86</v>
       </c>
       <c r="H39">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I39">
         <v>5.2</v>
@@ -10194,13 +10194,13 @@
         <v>1.38</v>
       </c>
       <c r="P39">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q39">
         <v>2.12</v>
       </c>
       <c r="R39">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S39">
         <v>3.95</v>
@@ -10326,22 +10326,22 @@
         <v>70</v>
       </c>
       <c r="BH39">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="BJ39">
         <v>15.5</v>
       </c>
       <c r="BK39">
-        <v>2.72</v>
+        <v>1.59</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="BN39">
         <v>6</v>
@@ -10353,13 +10353,13 @@
         <v>19</v>
       </c>
       <c r="BQ39">
-        <v>2.82</v>
+        <v>1.62</v>
       </c>
       <c r="BR39">
         <v>46</v>
       </c>
       <c r="BS39">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="BT39">
         <v>12.5</v>
@@ -10371,19 +10371,19 @@
         <v>70</v>
       </c>
       <c r="BW39">
-        <v>3.15</v>
+        <v>1.73</v>
       </c>
       <c r="BX39">
         <v>90</v>
       </c>
       <c r="BY39">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="BZ39">
         <v>40</v>
       </c>
       <c r="CA39">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="CB39" t="s">
         <v>200</v>
@@ -10442,16 +10442,16 @@
         <v>2.04</v>
       </c>
       <c r="R40">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S40">
         <v>3.7</v>
       </c>
       <c r="T40">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="U40">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V40">
         <v>1.46</v>
@@ -10556,7 +10556,7 @@
         <v>24</v>
       </c>
       <c r="BD40">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE40">
         <v>11.5</v>
@@ -10610,7 +10610,7 @@
         <v>4.9</v>
       </c>
       <c r="BV40">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BW40">
         <v>1.01</v>
@@ -10672,22 +10672,22 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O41">
         <v>1.01</v>
       </c>
       <c r="P41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R41">
         <v>1.18</v>
       </c>
       <c r="S41">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10890,7 +10890,7 @@
         <v>195</v>
       </c>
       <c r="F42">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G42">
         <v>1.64</v>
@@ -10905,25 +10905,25 @@
         <v>3.95</v>
       </c>
       <c r="K42">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L42">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N42">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
         <v>1.35</v>
       </c>
       <c r="P42">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q42">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R42">
         <v>1.26</v>
@@ -11132,16 +11132,16 @@
         <v>196</v>
       </c>
       <c r="F43">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G43">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I43">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J43">
         <v>3.65</v>
@@ -11180,7 +11180,7 @@
         <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W43">
         <v>1.5</v>
@@ -11222,7 +11222,7 @@
         <v>36</v>
       </c>
       <c r="AJ43">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AK43">
         <v>32</v>
@@ -11285,7 +11285,7 @@
         <v>32</v>
       </c>
       <c r="BE43">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF43">
         <v>20</v>
@@ -11419,7 +11419,7 @@
         <v>1.67</v>
       </c>
       <c r="U44">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V44">
         <v>1.36</v>
@@ -11640,22 +11640,22 @@
         <v>1.01</v>
       </c>
       <c r="N45">
+        <v>1.26</v>
+      </c>
+      <c r="O45">
+        <v>1.01</v>
+      </c>
+      <c r="P45">
         <v>1.25</v>
       </c>
-      <c r="O45">
-        <v>1.01</v>
-      </c>
-      <c r="P45">
-        <v>1.24</v>
-      </c>
       <c r="Q45">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R45">
         <v>1.18</v>
       </c>
       <c r="S45">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="T45">
         <v>1.01</v>
@@ -11861,7 +11861,7 @@
         <v>5.9</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H46">
         <v>1.61</v>
@@ -11879,7 +11879,7 @@
         <v>1.29</v>
       </c>
       <c r="M46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N46">
         <v>5.1</v>
@@ -11894,13 +11894,13 @@
         <v>1.6</v>
       </c>
       <c r="R46">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S46">
         <v>2.56</v>
       </c>
       <c r="T46">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U46">
         <v>2.24</v>
@@ -11909,10 +11909,10 @@
         <v>2.52</v>
       </c>
       <c r="W46">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X46">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y46">
         <v>12</v>
@@ -11924,7 +11924,7 @@
         <v>17</v>
       </c>
       <c r="AB46">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC46">
         <v>13</v>
@@ -11966,7 +11966,7 @@
         <v>7.2</v>
       </c>
       <c r="AP46">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="AQ46">
         <v>9.800000000000001</v>
@@ -11975,28 +11975,28 @@
         <v>10</v>
       </c>
       <c r="AS46">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT46">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU46">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV46">
         <v>9</v>
       </c>
       <c r="AW46">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AX46">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY46">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ46">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA46">
         <v>20</v>
@@ -12005,16 +12005,16 @@
         <v>6.4</v>
       </c>
       <c r="BC46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE46">
         <v>6.2</v>
       </c>
       <c r="BF46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG46">
         <v>5.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="218">
   <si>
     <t>League</t>
   </si>
@@ -310,6 +310,15 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
     <t>2026-09-02</t>
   </si>
   <si>
@@ -346,6 +355,18 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>LDU</t>
   </si>
   <si>
@@ -421,33 +442,33 @@
     <t>Thun</t>
   </si>
   <si>
+    <t>Siroki Brijeg</t>
+  </si>
+  <si>
+    <t>Sint Truiden</t>
+  </si>
+  <si>
     <t>Red Bull Salzburg</t>
   </si>
   <si>
-    <t>Sint Truiden</t>
-  </si>
-  <si>
-    <t>Siroki Brijeg</t>
-  </si>
-  <si>
     <t>Motherwell</t>
   </si>
   <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
+  </si>
+  <si>
     <t>Kilmarnock</t>
   </si>
   <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
     <t>Luton</t>
   </si>
   <si>
@@ -463,24 +484,39 @@
     <t>Wigan</t>
   </si>
   <si>
+    <t>Macara</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Club Sportivo Ameliano</t>
+  </si>
+  <si>
     <t>Nacional (Par)</t>
   </si>
   <si>
-    <t>Macara</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Club Sportivo Ameliano</t>
-  </si>
-  <si>
     <t>Falkirk</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Charleston Battery</t>
+  </si>
+  <si>
     <t>Mushuc Runa</t>
   </si>
   <si>
@@ -556,33 +592,33 @@
     <t>Lausanne</t>
   </si>
   <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Union St Gilloise</t>
+  </si>
+  <si>
     <t>Rapid Vienna</t>
   </si>
   <si>
-    <t>Union St Gilloise</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
     <t>Dundee Utd</t>
   </si>
   <si>
+    <t>St Johnstone</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
     <t>St Mirren</t>
   </si>
   <si>
-    <t>St Johnstone</t>
-  </si>
-  <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>AFC Wimbledon</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
     <t>Stockport</t>
   </si>
   <si>
@@ -598,25 +634,40 @@
     <t>MK Dons</t>
   </si>
   <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Mansfield</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>Manta FC</t>
-  </si>
-  <si>
-    <t>Middlesbrough</t>
-  </si>
-  <si>
-    <t>Mansfield</t>
-  </si>
-  <si>
-    <t>Sportivo Trinidense</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>2026-08-31 21:58:10</t>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>Guarani (Par)</t>
+  </si>
+  <si>
+    <t>Univ de Concepcion</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Hartford Athletic FC</t>
+  </si>
+  <si>
+    <t>2026-09-01 00:10:39</t>
   </si>
 </sst>
 </file>
@@ -948,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB46"/>
+  <dimension ref="A1:CB51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1198,19 +1249,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
         <v>1.72</v>
@@ -1225,7 +1276,7 @@
         <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -1237,7 +1288,7 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
         <v>1.9</v>
@@ -1249,16 +1300,16 @@
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
         <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
         <v>2.38</v>
@@ -1300,7 +1351,7 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>19.5</v>
@@ -1312,7 +1363,7 @@
         <v>160</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
         <v>150</v>
@@ -1324,22 +1375,22 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
         <v>7.4</v>
@@ -1351,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1360,16 +1411,16 @@
         <v>14</v>
       </c>
       <c r="BD2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
         <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
         <v>3.8</v>
@@ -1393,7 +1444,7 @@
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP2">
         <v>13</v>
@@ -1432,7 +1483,7 @@
         <v>4.7</v>
       </c>
       <c r="CB2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1440,22 +1491,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F3">
         <v>2.76</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H3">
         <v>2.82</v>
@@ -1464,13 +1515,13 @@
         <v>3.1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.09</v>
@@ -1479,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
         <v>1.76</v>
@@ -1494,7 +1545,7 @@
         <v>3.95</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
         <v>2.08</v>
@@ -1518,7 +1569,7 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
         <v>8.6</v>
@@ -1581,100 +1632,100 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX3">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC3">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1682,19 +1733,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G4">
         <v>1.59</v>
@@ -1703,7 +1754,7 @@
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>4.5</v>
@@ -1712,37 +1763,37 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
         <v>2.68</v>
@@ -1781,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1790,13 +1841,13 @@
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AM4">
         <v>110</v>
       </c>
       <c r="AN4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO4">
         <v>80</v>
@@ -1811,10 +1862,10 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU4">
         <v>9.6</v>
@@ -1823,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>9.4</v>
@@ -1835,7 +1886,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1847,13 +1898,13 @@
         <v>21</v>
       </c>
       <c r="BE4">
+        <v>11</v>
+      </c>
+      <c r="BF4">
+        <v>6</v>
+      </c>
+      <c r="BG4">
         <v>10.5</v>
-      </c>
-      <c r="BF4">
-        <v>5.1</v>
-      </c>
-      <c r="BG4">
-        <v>10</v>
       </c>
       <c r="BH4">
         <v>4.9</v>
@@ -1865,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL4">
         <v>130</v>
@@ -1895,10 +1946,10 @@
         <v>12</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
@@ -1916,7 +1967,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1924,22 +1975,22 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5">
         <v>2.08</v>
@@ -1960,7 +2011,7 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.37</v>
@@ -1969,13 +2020,13 @@
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
         <v>1.86</v>
@@ -2032,7 +2083,7 @@
         <v>65</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>130</v>
@@ -2068,7 +2119,7 @@
         <v>20</v>
       </c>
       <c r="AX5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY5">
         <v>14</v>
@@ -2080,19 +2131,19 @@
         <v>32</v>
       </c>
       <c r="BB5">
+        <v>6.8</v>
+      </c>
+      <c r="BC5">
+        <v>7.4</v>
+      </c>
+      <c r="BD5">
         <v>6.6</v>
       </c>
-      <c r="BC5">
-        <v>7.2</v>
-      </c>
-      <c r="BD5">
-        <v>6.4</v>
-      </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
         <v>15.5</v>
@@ -2158,7 +2209,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2166,31 +2217,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -2217,7 +2268,7 @@
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
         <v>1.63</v>
@@ -2226,7 +2277,7 @@
         <v>2.22</v>
       </c>
       <c r="V6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W6">
         <v>1.36</v>
@@ -2271,7 +2322,7 @@
         <v>80</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL6">
         <v>60</v>
@@ -2322,13 +2373,13 @@
         <v>6.6</v>
       </c>
       <c r="BB6">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BC6">
         <v>7</v>
       </c>
       <c r="BD6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE6">
         <v>7.6</v>
@@ -2400,7 +2451,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2408,22 +2459,22 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H7">
         <v>2.14</v>
@@ -2432,10 +2483,10 @@
         <v>2.28</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2453,7 +2504,7 @@
         <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R7">
         <v>1.19</v>
@@ -2468,7 +2519,7 @@
         <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W7">
         <v>1.29</v>
@@ -2480,19 +2531,19 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA7">
         <v>32</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
         <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
         <v>34</v>
@@ -2531,13 +2582,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
@@ -2549,10 +2600,10 @@
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY7">
         <v>16</v>
@@ -2561,26 +2612,26 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG7">
         <v>7.6</v>
       </c>
-      <c r="BC7">
-        <v>7.6</v>
-      </c>
-      <c r="BD7">
-        <v>7.4</v>
-      </c>
-      <c r="BE7">
-        <v>7.6</v>
-      </c>
-      <c r="BF7">
-        <v>7.6</v>
-      </c>
-      <c r="BG7">
-        <v>6.6</v>
-      </c>
       <c r="BH7">
         <v>1000</v>
       </c>
@@ -2642,7 +2693,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2650,16 +2701,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F8">
         <v>4.1</v>
@@ -2707,13 +2758,13 @@
         <v>1.83</v>
       </c>
       <c r="U8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
         <v>1.95</v>
       </c>
       <c r="W8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X8">
         <v>14.5</v>
@@ -2803,13 +2854,13 @@
         <v>16.5</v>
       </c>
       <c r="BA8">
+        <v>6.2</v>
+      </c>
+      <c r="BB8">
         <v>6.4</v>
       </c>
-      <c r="BB8">
+      <c r="BC8">
         <v>6.6</v>
-      </c>
-      <c r="BC8">
-        <v>6.4</v>
       </c>
       <c r="BD8">
         <v>6.6</v>
@@ -2884,7 +2935,7 @@
         <v>1.73</v>
       </c>
       <c r="CB8" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2892,19 +2943,19 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
         <v>2.38</v>
@@ -2919,43 +2970,43 @@
         <v>3.45</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R9">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.31</v>
       </c>
       <c r="W9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X9">
         <v>17.5</v>
@@ -2967,7 +3018,7 @@
         <v>30</v>
       </c>
       <c r="AA9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB9">
         <v>12.5</v>
@@ -2979,7 +3030,7 @@
         <v>18</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF9">
         <v>18</v>
@@ -2997,19 +3048,19 @@
         <v>36</v>
       </c>
       <c r="AK9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM9">
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO9">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP9">
         <v>12.5</v>
@@ -3021,7 +3072,7 @@
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT9">
         <v>9</v>
@@ -3030,10 +3081,10 @@
         <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX9">
         <v>13</v>
@@ -3045,31 +3096,31 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BB9">
+        <v>10</v>
+      </c>
+      <c r="BC9">
         <v>4.2</v>
       </c>
-      <c r="BC9">
-        <v>4.1</v>
-      </c>
       <c r="BD9">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BF9">
         <v>13.5</v>
       </c>
       <c r="BG9">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
@@ -3087,7 +3138,7 @@
         <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
         <v>20</v>
@@ -3105,7 +3156,7 @@
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>34</v>
@@ -3120,13 +3171,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3134,16 +3185,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F10">
         <v>4.1</v>
@@ -3161,10 +3212,10 @@
         <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.08</v>
@@ -3203,7 +3254,7 @@
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10">
         <v>13.5</v>
@@ -3212,22 +3263,22 @@
         <v>24</v>
       </c>
       <c r="AB10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF10">
         <v>32</v>
       </c>
       <c r="AG10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH10">
         <v>23</v>
@@ -3251,13 +3302,13 @@
         <v>70</v>
       </c>
       <c r="AO10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP10">
         <v>11</v>
       </c>
       <c r="AQ10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR10">
         <v>10.5</v>
@@ -3287,22 +3338,22 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>6.4</v>
       </c>
       <c r="BB10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE10">
         <v>6.2</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG10">
         <v>14.5</v>
@@ -3317,22 +3368,22 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL10">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
@@ -3365,10 +3416,10 @@
         <v>34</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB10" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3376,34 +3427,34 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F11">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
         <v>4</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11">
         <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3412,43 +3463,43 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
         <v>18.5</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z11">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AA11">
         <v>95</v>
@@ -3457,22 +3508,22 @@
         <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE11">
         <v>60</v>
       </c>
       <c r="AF11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
         <v>65</v>
@@ -3484,7 +3535,7 @@
         <v>22</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -3496,10 +3547,10 @@
         <v>60</v>
       </c>
       <c r="AP11">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR11">
         <v>23</v>
@@ -3508,28 +3559,28 @@
         <v>6.6</v>
       </c>
       <c r="AT11">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX11">
         <v>11</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB11">
         <v>20</v>
@@ -3538,16 +3589,16 @@
         <v>17.5</v>
       </c>
       <c r="BD11">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3610,7 +3661,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3618,34 +3669,34 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F12">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G12">
         <v>2.66</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3654,19 +3705,19 @@
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P12">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="Q12">
         <v>2.34</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S12">
         <v>4.7</v>
@@ -3675,7 +3726,7 @@
         <v>1.98</v>
       </c>
       <c r="U12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -3690,13 +3741,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AA12">
         <v>70</v>
       </c>
       <c r="AB12">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC12">
         <v>9.199999999999999</v>
@@ -3708,13 +3759,13 @@
         <v>55</v>
       </c>
       <c r="AF12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AI12">
         <v>75</v>
@@ -3741,13 +3792,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR12">
         <v>18</v>
       </c>
       <c r="AS12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3759,37 +3810,37 @@
         <v>12</v>
       </c>
       <c r="AW12">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY12">
         <v>11</v>
       </c>
       <c r="AZ12">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BA12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12">
-        <v>29</v>
+        <v>5.9</v>
       </c>
       <c r="BD12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BE12">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF12">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3852,7 +3903,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3860,31 +3911,31 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F13">
         <v>2.9</v>
       </c>
       <c r="G13">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="H13">
         <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="K13">
         <v>3.1</v>
@@ -3896,22 +3947,22 @@
         <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O13">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Q13">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S13">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="T13">
         <v>2.42</v>
@@ -3923,10 +3974,10 @@
         <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="X13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y13">
         <v>9.199999999999999</v>
@@ -3959,7 +4010,7 @@
         <v>36</v>
       </c>
       <c r="AI13">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ13">
         <v>75</v>
@@ -3971,7 +4022,7 @@
         <v>130</v>
       </c>
       <c r="AM13">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AN13">
         <v>110</v>
@@ -3980,10 +4031,10 @@
         <v>120</v>
       </c>
       <c r="AP13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR13">
         <v>14</v>
@@ -3992,13 +4043,13 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU13">
         <v>5.2</v>
       </c>
       <c r="AV13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -4094,7 +4145,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4102,16 +4153,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F14">
         <v>1.08</v>
@@ -4336,7 +4387,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4344,16 +4395,16 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F15">
         <v>1.09</v>
@@ -4578,7 +4629,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4586,16 +4637,16 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F16">
         <v>2.3</v>
@@ -4820,7 +4871,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4828,16 +4879,16 @@
         <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -4882,10 +4933,10 @@
         <v>3.2</v>
       </c>
       <c r="T17">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V17">
         <v>1.3</v>
@@ -4912,7 +4963,7 @@
         <v>8.6</v>
       </c>
       <c r="AD17">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE17">
         <v>48</v>
@@ -5032,7 +5083,7 @@
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
@@ -5056,13 +5107,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5070,19 +5121,19 @@
         <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>110</v>
@@ -5097,7 +5148,7 @@
         <v>4.9</v>
       </c>
       <c r="K18">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>1.3</v>
@@ -5112,7 +5163,7 @@
         <v>1.26</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
         <v>1.7</v>
@@ -5121,7 +5172,7 @@
         <v>1.3</v>
       </c>
       <c r="S18">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5130,7 +5181,7 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W18">
         <v>1.02</v>
@@ -5304,7 +5355,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5312,16 +5363,16 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F19">
         <v>2.1</v>
@@ -5342,7 +5393,7 @@
         <v>3.2</v>
       </c>
       <c r="L19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M19">
         <v>1.13</v>
@@ -5546,7 +5597,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5554,16 +5605,16 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F20">
         <v>2.38</v>
@@ -5788,7 +5839,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5796,58 +5847,58 @@
         <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F21">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G21">
         <v>3.05</v>
       </c>
       <c r="H21">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I21">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <v>3.35</v>
       </c>
       <c r="K21">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q21">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S21">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="T21">
         <v>1.74</v>
@@ -5856,7 +5907,7 @@
         <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
         <v>1.49</v>
@@ -5976,7 +6027,7 @@
         <v>2.72</v>
       </c>
       <c r="BJ21">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
@@ -5988,49 +6039,49 @@
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6038,34 +6089,34 @@
         <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F22">
         <v>3.25</v>
       </c>
       <c r="G22">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="H22">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6074,7 +6125,7 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>1.2</v>
@@ -6086,7 +6137,7 @@
         <v>1.63</v>
       </c>
       <c r="R22">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S22">
         <v>2.52</v>
@@ -6098,10 +6149,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W22">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6218,7 +6269,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
         <v>1.01</v>
@@ -6230,49 +6281,49 @@
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6280,16 +6331,16 @@
         <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F23">
         <v>4.6</v>
@@ -6325,10 +6376,10 @@
         <v>2.42</v>
       </c>
       <c r="Q23">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S23">
         <v>2.42</v>
@@ -6514,7 +6565,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6522,16 +6573,16 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F24">
         <v>4.3</v>
@@ -6558,28 +6609,28 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
         <v>1.18</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q24">
         <v>1.53</v>
       </c>
       <c r="R24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S24">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U24">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
         <v>2.16</v>
@@ -6594,7 +6645,7 @@
         <v>15.5</v>
       </c>
       <c r="Z24">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA24">
         <v>23</v>
@@ -6630,19 +6681,19 @@
         <v>55</v>
       </c>
       <c r="AL24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM24">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AN24">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO24">
         <v>7.4</v>
       </c>
       <c r="AP24">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
         <v>10</v>
@@ -6756,7 +6807,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6764,31 +6815,31 @@
         <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F25">
         <v>1.61</v>
       </c>
       <c r="G25">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I25">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="K25">
         <v>5.5</v>
@@ -6803,19 +6854,19 @@
         <v>3.25</v>
       </c>
       <c r="O25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P25">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q25">
         <v>1.34</v>
       </c>
       <c r="R25">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="S25">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6824,10 +6875,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W25">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6998,7 +7049,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7006,22 +7057,22 @@
         <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F26">
         <v>2.06</v>
       </c>
       <c r="G26">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H26">
         <v>3.5</v>
@@ -7033,7 +7084,7 @@
         <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7042,19 +7093,19 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O26">
         <v>1.13</v>
       </c>
       <c r="P26">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S26">
         <v>2.02</v>
@@ -7069,7 +7120,7 @@
         <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X26">
         <v>34</v>
@@ -7105,7 +7156,7 @@
         <v>18</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ26">
         <v>34</v>
@@ -7120,7 +7171,7 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO26">
         <v>1000</v>
@@ -7240,249 +7291,249 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F27">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="G27">
-        <v>1.96</v>
+        <v>110</v>
       </c>
       <c r="H27">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="I27">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="J27">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>1.26</v>
+      </c>
+      <c r="O27">
         <v>1.02</v>
       </c>
-      <c r="N27">
-        <v>6</v>
-      </c>
-      <c r="O27">
-        <v>1.17</v>
-      </c>
       <c r="P27">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q27">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="R27">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="T27">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="W27">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7490,16 +7541,16 @@
         <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F28">
         <v>3.7</v>
@@ -7619,7 +7670,7 @@
         <v>12</v>
       </c>
       <c r="AS28">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT28">
         <v>14</v>
@@ -7634,7 +7685,7 @@
         <v>18.5</v>
       </c>
       <c r="AX28">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY28">
         <v>14</v>
@@ -7646,7 +7697,7 @@
         <v>23</v>
       </c>
       <c r="BB28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC28">
         <v>28</v>
@@ -7655,7 +7706,7 @@
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF28">
         <v>23</v>
@@ -7673,7 +7724,7 @@
         <v>10.5</v>
       </c>
       <c r="BK28">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>120</v>
@@ -7682,7 +7733,7 @@
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BO28">
         <v>4.8</v>
@@ -7712,150 +7763,150 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX28">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA28">
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" t="s">
+        <v>194</v>
+      </c>
+      <c r="F29">
+        <v>1.88</v>
+      </c>
+      <c r="G29">
+        <v>1.96</v>
+      </c>
+      <c r="H29">
+        <v>3.75</v>
+      </c>
+      <c r="I29">
+        <v>4.2</v>
+      </c>
+      <c r="J29">
+        <v>4.3</v>
+      </c>
+      <c r="K29">
+        <v>4.6</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.02</v>
+      </c>
+      <c r="N29">
+        <v>6</v>
+      </c>
+      <c r="O29">
+        <v>1.17</v>
+      </c>
+      <c r="P29">
+        <v>2.8</v>
+      </c>
+      <c r="Q29">
+        <v>1.45</v>
+      </c>
+      <c r="R29">
+        <v>1.73</v>
+      </c>
+      <c r="S29">
+        <v>2.16</v>
+      </c>
+      <c r="T29">
+        <v>1.54</v>
+      </c>
+      <c r="U29">
+        <v>2.66</v>
+      </c>
+      <c r="V29">
+        <v>1.33</v>
+      </c>
+      <c r="W29">
+        <v>2.04</v>
+      </c>
+      <c r="X29">
+        <v>36</v>
+      </c>
+      <c r="Y29">
+        <v>28</v>
+      </c>
+      <c r="Z29">
+        <v>40</v>
+      </c>
+      <c r="AA29">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29">
-        <v>1.08</v>
-      </c>
-      <c r="G29">
-        <v>110</v>
-      </c>
-      <c r="H29">
-        <v>1.08</v>
-      </c>
-      <c r="I29">
-        <v>110</v>
-      </c>
-      <c r="J29">
-        <v>1.1</v>
-      </c>
-      <c r="K29">
-        <v>1000</v>
-      </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
-        <v>1.01</v>
-      </c>
-      <c r="N29">
-        <v>1.26</v>
-      </c>
-      <c r="O29">
-        <v>1.02</v>
-      </c>
-      <c r="P29">
-        <v>1.25</v>
-      </c>
-      <c r="Q29">
-        <v>1.51</v>
-      </c>
-      <c r="R29">
-        <v>1.18</v>
-      </c>
-      <c r="S29">
-        <v>1.52</v>
-      </c>
-      <c r="T29">
-        <v>1.01</v>
-      </c>
-      <c r="U29">
-        <v>1.01</v>
-      </c>
-      <c r="V29">
-        <v>1.05</v>
-      </c>
-      <c r="W29">
-        <v>1.05</v>
-      </c>
-      <c r="X29">
-        <v>1000</v>
-      </c>
-      <c r="Y29">
-        <v>1000</v>
-      </c>
-      <c r="Z29">
-        <v>1000</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP29">
         <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR29">
         <v>1.01</v>
@@ -7864,109 +7915,109 @@
         <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW29">
         <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA29">
         <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC29">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ29">
         <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS29">
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW29">
         <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY29">
         <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA29">
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7974,22 +8025,22 @@
         <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F30">
         <v>1.92</v>
       </c>
       <c r="G30">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H30">
         <v>3.7</v>
@@ -8016,28 +8067,28 @@
         <v>1.26</v>
       </c>
       <c r="P30">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q30">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="R30">
         <v>1.39</v>
       </c>
       <c r="S30">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="T30">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V30">
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X30">
         <v>20</v>
@@ -8208,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8216,34 +8267,34 @@
         <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F31">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="G31">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="H31">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="I31">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="J31">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8252,196 +8303,196 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P31">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="Q31">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="R31">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S31">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T31">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U31">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V31">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W31">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X31">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y31">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB31">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC31">
         <v>8.800000000000001</v>
       </c>
       <c r="AD31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE31">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF31">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG31">
         <v>13</v>
       </c>
       <c r="AH31">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ31">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK31">
         <v>32</v>
       </c>
       <c r="AL31">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM31">
         <v>90</v>
       </c>
       <c r="AN31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP31">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR31">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
       </c>
       <c r="AU31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV31">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW31">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AX31">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB31">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BC31">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD31">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE31">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF31">
+        <v>19.5</v>
+      </c>
+      <c r="BG31">
         <v>18.5</v>
       </c>
-      <c r="BG31">
-        <v>16</v>
-      </c>
       <c r="BH31">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI31">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK31">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
         <v>120</v>
       </c>
       <c r="BM31">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO31">
         <v>4.6</v>
       </c>
       <c r="BP31">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ31">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
         <v>6.8</v>
       </c>
       <c r="BU31">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW31">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
         <v>36</v>
       </c>
       <c r="BY31">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8450,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8458,229 +8509,229 @@
         <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F32">
-        <v>2.66</v>
+        <v>1.23</v>
       </c>
       <c r="G32">
-        <v>2.84</v>
+        <v>1.25</v>
       </c>
       <c r="H32">
-        <v>2.64</v>
+        <v>14</v>
       </c>
       <c r="I32">
-        <v>2.84</v>
+        <v>17</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>7.4</v>
+      </c>
+      <c r="O32">
+        <v>1.12</v>
+      </c>
+      <c r="P32">
+        <v>3.15</v>
+      </c>
+      <c r="Q32">
+        <v>1.38</v>
+      </c>
+      <c r="R32">
+        <v>1.86</v>
+      </c>
+      <c r="S32">
+        <v>1.94</v>
+      </c>
+      <c r="T32">
+        <v>1.87</v>
+      </c>
+      <c r="U32">
+        <v>1.94</v>
+      </c>
+      <c r="V32">
         <v>1.06</v>
       </c>
-      <c r="N32">
-        <v>3.95</v>
-      </c>
-      <c r="O32">
-        <v>1.29</v>
-      </c>
-      <c r="P32">
-        <v>2.02</v>
-      </c>
-      <c r="Q32">
-        <v>1.84</v>
-      </c>
-      <c r="R32">
-        <v>1.38</v>
-      </c>
-      <c r="S32">
-        <v>3.2</v>
-      </c>
-      <c r="T32">
-        <v>1.71</v>
-      </c>
-      <c r="U32">
-        <v>2.24</v>
-      </c>
-      <c r="V32">
-        <v>1.54</v>
-      </c>
       <c r="W32">
-        <v>1.54</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Y32">
+        <v>70</v>
+      </c>
+      <c r="Z32">
+        <v>160</v>
+      </c>
+      <c r="AA32">
+        <v>580</v>
+      </c>
+      <c r="AB32">
+        <v>13.5</v>
+      </c>
+      <c r="AC32">
+        <v>18.5</v>
+      </c>
+      <c r="AD32">
+        <v>55</v>
+      </c>
+      <c r="AE32">
+        <v>220</v>
+      </c>
+      <c r="AF32">
+        <v>10</v>
+      </c>
+      <c r="AG32">
+        <v>12</v>
+      </c>
+      <c r="AH32">
+        <v>32</v>
+      </c>
+      <c r="AI32">
+        <v>160</v>
+      </c>
+      <c r="AJ32">
+        <v>10.5</v>
+      </c>
+      <c r="AK32">
+        <v>13</v>
+      </c>
+      <c r="AL32">
+        <v>34</v>
+      </c>
+      <c r="AM32">
+        <v>150</v>
+      </c>
+      <c r="AN32">
+        <v>3.45</v>
+      </c>
+      <c r="AO32">
+        <v>240</v>
+      </c>
+      <c r="AP32">
+        <v>30</v>
+      </c>
+      <c r="AQ32">
+        <v>50</v>
+      </c>
+      <c r="AR32">
         <v>12.5</v>
       </c>
-      <c r="Z32">
+      <c r="AS32">
+        <v>13</v>
+      </c>
+      <c r="AT32">
+        <v>11.5</v>
+      </c>
+      <c r="AU32">
+        <v>15.5</v>
+      </c>
+      <c r="AV32">
+        <v>42</v>
+      </c>
+      <c r="AW32">
+        <v>12.5</v>
+      </c>
+      <c r="AX32">
+        <v>8.4</v>
+      </c>
+      <c r="AY32">
+        <v>10</v>
+      </c>
+      <c r="AZ32">
+        <v>26</v>
+      </c>
+      <c r="BA32">
+        <v>12.5</v>
+      </c>
+      <c r="BB32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC32">
+        <v>11.5</v>
+      </c>
+      <c r="BD32">
+        <v>10</v>
+      </c>
+      <c r="BE32">
+        <v>13</v>
+      </c>
+      <c r="BF32">
+        <v>2.98</v>
+      </c>
+      <c r="BG32">
+        <v>12.5</v>
+      </c>
+      <c r="BH32">
+        <v>6.2</v>
+      </c>
+      <c r="BI32">
+        <v>4.3</v>
+      </c>
+      <c r="BJ32">
+        <v>13.5</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>130</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>4.3</v>
+      </c>
+      <c r="BO32">
+        <v>3.6</v>
+      </c>
+      <c r="BP32">
+        <v>7.8</v>
+      </c>
+      <c r="BQ32">
+        <v>5.8</v>
+      </c>
+      <c r="BR32">
         <v>22</v>
       </c>
-      <c r="AA32">
-        <v>42</v>
-      </c>
-      <c r="AB32">
-        <v>13</v>
-      </c>
-      <c r="AC32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD32">
-        <v>13</v>
-      </c>
-      <c r="AE32">
-        <v>34</v>
-      </c>
-      <c r="AF32">
-        <v>20</v>
-      </c>
-      <c r="AG32">
-        <v>13</v>
-      </c>
-      <c r="AH32">
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
         <v>18</v>
       </c>
-      <c r="AI32">
-        <v>40</v>
-      </c>
-      <c r="AJ32">
-        <v>44</v>
-      </c>
-      <c r="AK32">
-        <v>32</v>
-      </c>
-      <c r="AL32">
-        <v>40</v>
-      </c>
-      <c r="AM32">
-        <v>90</v>
-      </c>
-      <c r="AN32">
-        <v>24</v>
-      </c>
-      <c r="AO32">
-        <v>24</v>
-      </c>
-      <c r="AP32">
-        <v>12.5</v>
-      </c>
-      <c r="AQ32">
-        <v>9.4</v>
-      </c>
-      <c r="AR32">
-        <v>15.5</v>
-      </c>
-      <c r="AS32">
-        <v>6.8</v>
-      </c>
-      <c r="AT32">
-        <v>10.5</v>
-      </c>
-      <c r="AU32">
-        <v>7.4</v>
-      </c>
-      <c r="AV32">
-        <v>9.4</v>
-      </c>
-      <c r="AW32">
-        <v>21</v>
-      </c>
-      <c r="AX32">
-        <v>16</v>
-      </c>
-      <c r="AY32">
-        <v>10.5</v>
-      </c>
-      <c r="AZ32">
-        <v>13</v>
-      </c>
-      <c r="BA32">
-        <v>6.8</v>
-      </c>
-      <c r="BB32">
-        <v>32</v>
-      </c>
-      <c r="BC32">
-        <v>6.6</v>
-      </c>
-      <c r="BD32">
-        <v>6.8</v>
-      </c>
-      <c r="BE32">
-        <v>7.6</v>
-      </c>
-      <c r="BF32">
-        <v>19.5</v>
-      </c>
-      <c r="BG32">
-        <v>18.5</v>
-      </c>
-      <c r="BH32">
-        <v>4.1</v>
-      </c>
-      <c r="BI32">
-        <v>2.96</v>
-      </c>
-      <c r="BJ32">
-        <v>10.5</v>
-      </c>
-      <c r="BK32">
-        <v>1.01</v>
-      </c>
-      <c r="BL32">
-        <v>120</v>
-      </c>
-      <c r="BM32">
-        <v>1.01</v>
-      </c>
-      <c r="BN32">
-        <v>6.8</v>
-      </c>
-      <c r="BO32">
-        <v>4.6</v>
-      </c>
-      <c r="BP32">
-        <v>24</v>
-      </c>
-      <c r="BQ32">
-        <v>1.01</v>
-      </c>
-      <c r="BR32">
-        <v>36</v>
-      </c>
-      <c r="BS32">
-        <v>1.01</v>
-      </c>
-      <c r="BT32">
-        <v>6.8</v>
-      </c>
       <c r="BU32">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="BW32">
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
@@ -8692,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8700,16 +8751,16 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F33">
         <v>2.3</v>
@@ -8751,7 +8802,7 @@
         <v>1.45</v>
       </c>
       <c r="S33">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T33">
         <v>1.64</v>
@@ -8934,7 +8985,7 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8942,16 +8993,16 @@
         <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -8969,7 +9020,7 @@
         <v>3.3</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -8981,25 +9032,25 @@
         <v>3.2</v>
       </c>
       <c r="O34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P34">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q34">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R34">
         <v>1.21</v>
       </c>
       <c r="S34">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="T34">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U34">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V34">
         <v>1.29</v>
@@ -9176,7 +9227,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9184,232 +9235,232 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F35">
-        <v>1.23</v>
+        <v>2.84</v>
       </c>
       <c r="G35">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="H35">
+        <v>2.54</v>
+      </c>
+      <c r="I35">
+        <v>2.7</v>
+      </c>
+      <c r="J35">
+        <v>3.5</v>
+      </c>
+      <c r="K35">
+        <v>3.6</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.06</v>
+      </c>
+      <c r="N35">
+        <v>4.1</v>
+      </c>
+      <c r="O35">
+        <v>1.28</v>
+      </c>
+      <c r="P35">
+        <v>2.08</v>
+      </c>
+      <c r="Q35">
+        <v>1.69</v>
+      </c>
+      <c r="R35">
+        <v>1.42</v>
+      </c>
+      <c r="S35">
+        <v>2.96</v>
+      </c>
+      <c r="T35">
+        <v>1.64</v>
+      </c>
+      <c r="U35">
+        <v>2.32</v>
+      </c>
+      <c r="V35">
+        <v>1.58</v>
+      </c>
+      <c r="W35">
+        <v>1.48</v>
+      </c>
+      <c r="X35">
+        <v>17.5</v>
+      </c>
+      <c r="Y35">
+        <v>13.5</v>
+      </c>
+      <c r="Z35">
+        <v>19.5</v>
+      </c>
+      <c r="AA35">
+        <v>38</v>
+      </c>
+      <c r="AB35">
+        <v>14.5</v>
+      </c>
+      <c r="AC35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD35">
+        <v>12.5</v>
+      </c>
+      <c r="AE35">
+        <v>28</v>
+      </c>
+      <c r="AF35">
+        <v>23</v>
+      </c>
+      <c r="AG35">
+        <v>13</v>
+      </c>
+      <c r="AH35">
+        <v>16.5</v>
+      </c>
+      <c r="AI35">
+        <v>38</v>
+      </c>
+      <c r="AJ35">
+        <v>48</v>
+      </c>
+      <c r="AK35">
+        <v>32</v>
+      </c>
+      <c r="AL35">
+        <v>40</v>
+      </c>
+      <c r="AM35">
+        <v>90</v>
+      </c>
+      <c r="AN35">
+        <v>25</v>
+      </c>
+      <c r="AO35">
+        <v>21</v>
+      </c>
+      <c r="AP35">
         <v>14</v>
       </c>
-      <c r="I35">
-        <v>17</v>
-      </c>
-      <c r="J35">
+      <c r="AQ35">
+        <v>10.5</v>
+      </c>
+      <c r="AR35">
+        <v>16.5</v>
+      </c>
+      <c r="AS35">
+        <v>7.2</v>
+      </c>
+      <c r="AT35">
+        <v>10.5</v>
+      </c>
+      <c r="AU35">
+        <v>7.2</v>
+      </c>
+      <c r="AV35">
+        <v>10.5</v>
+      </c>
+      <c r="AW35">
+        <v>6.8</v>
+      </c>
+      <c r="AX35">
+        <v>18</v>
+      </c>
+      <c r="AY35">
+        <v>10.5</v>
+      </c>
+      <c r="AZ35">
+        <v>13.5</v>
+      </c>
+      <c r="BA35">
+        <v>7.2</v>
+      </c>
+      <c r="BB35">
+        <v>32</v>
+      </c>
+      <c r="BC35">
         <v>7</v>
       </c>
-      <c r="K35">
-        <v>8.4</v>
-      </c>
-      <c r="L35">
-        <v>1.19</v>
-      </c>
-      <c r="M35">
-        <v>1.01</v>
-      </c>
-      <c r="N35">
-        <v>7.4</v>
-      </c>
-      <c r="O35">
-        <v>1.12</v>
-      </c>
-      <c r="P35">
-        <v>3.1</v>
-      </c>
-      <c r="Q35">
-        <v>1.38</v>
-      </c>
-      <c r="R35">
-        <v>1.84</v>
-      </c>
-      <c r="S35">
-        <v>1.94</v>
-      </c>
-      <c r="T35">
-        <v>1.87</v>
-      </c>
-      <c r="U35">
-        <v>1.94</v>
-      </c>
-      <c r="V35">
-        <v>1.06</v>
-      </c>
-      <c r="W35">
-        <v>5</v>
-      </c>
-      <c r="X35">
-        <v>40</v>
-      </c>
-      <c r="Y35">
-        <v>70</v>
-      </c>
-      <c r="Z35">
-        <v>180</v>
-      </c>
-      <c r="AA35">
-        <v>580</v>
-      </c>
-      <c r="AB35">
-        <v>13.5</v>
-      </c>
-      <c r="AC35">
-        <v>18.5</v>
-      </c>
-      <c r="AD35">
-        <v>55</v>
-      </c>
-      <c r="AE35">
-        <v>210</v>
-      </c>
-      <c r="AF35">
-        <v>10</v>
-      </c>
-      <c r="AG35">
-        <v>12</v>
-      </c>
-      <c r="AH35">
-        <v>32</v>
-      </c>
-      <c r="AI35">
-        <v>150</v>
-      </c>
-      <c r="AJ35">
-        <v>10.5</v>
-      </c>
-      <c r="AK35">
-        <v>13</v>
-      </c>
-      <c r="AL35">
-        <v>34</v>
-      </c>
-      <c r="AM35">
-        <v>140</v>
-      </c>
-      <c r="AN35">
-        <v>3.45</v>
-      </c>
-      <c r="AO35">
-        <v>240</v>
-      </c>
-      <c r="AP35">
+      <c r="BD35">
         <v>30</v>
       </c>
-      <c r="AQ35">
-        <v>50</v>
-      </c>
-      <c r="AR35">
-        <v>12.5</v>
-      </c>
-      <c r="AS35">
-        <v>13</v>
-      </c>
-      <c r="AT35">
-        <v>11.5</v>
-      </c>
-      <c r="AU35">
-        <v>15.5</v>
-      </c>
-      <c r="AV35">
-        <v>42</v>
-      </c>
-      <c r="AW35">
-        <v>12.5</v>
-      </c>
-      <c r="AX35">
-        <v>8.6</v>
-      </c>
-      <c r="AY35">
-        <v>10</v>
-      </c>
-      <c r="AZ35">
+      <c r="BE35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF35">
+        <v>20</v>
+      </c>
+      <c r="BG35">
+        <v>16</v>
+      </c>
+      <c r="BH35">
+        <v>4.3</v>
+      </c>
+      <c r="BI35">
+        <v>2.92</v>
+      </c>
+      <c r="BJ35">
+        <v>11</v>
+      </c>
+      <c r="BK35">
+        <v>3.3</v>
+      </c>
+      <c r="BL35">
+        <v>120</v>
+      </c>
+      <c r="BM35">
+        <v>4.5</v>
+      </c>
+      <c r="BN35">
+        <v>7.2</v>
+      </c>
+      <c r="BO35">
+        <v>4.6</v>
+      </c>
+      <c r="BP35">
         <v>26</v>
       </c>
-      <c r="BA35">
-        <v>12.5</v>
-      </c>
-      <c r="BB35">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC35">
-        <v>11.5</v>
-      </c>
-      <c r="BD35">
-        <v>10</v>
-      </c>
-      <c r="BE35">
-        <v>13</v>
-      </c>
-      <c r="BF35">
-        <v>2.98</v>
-      </c>
-      <c r="BG35">
-        <v>12.5</v>
-      </c>
-      <c r="BH35">
-        <v>6.2</v>
-      </c>
-      <c r="BI35">
+      <c r="BQ35">
+        <v>4</v>
+      </c>
+      <c r="BR35">
+        <v>38</v>
+      </c>
+      <c r="BS35">
+        <v>4.2</v>
+      </c>
+      <c r="BT35">
+        <v>6.8</v>
+      </c>
+      <c r="BU35">
         <v>4.3</v>
       </c>
-      <c r="BJ35">
-        <v>13.5</v>
-      </c>
-      <c r="BK35">
-        <v>1.01</v>
-      </c>
-      <c r="BL35">
-        <v>130</v>
-      </c>
-      <c r="BM35">
-        <v>1.01</v>
-      </c>
-      <c r="BN35">
-        <v>4.7</v>
-      </c>
-      <c r="BO35">
-        <v>3.35</v>
-      </c>
-      <c r="BP35">
-        <v>7.8</v>
-      </c>
-      <c r="BQ35">
-        <v>5.3</v>
-      </c>
-      <c r="BR35">
-        <v>22</v>
-      </c>
-      <c r="BS35">
-        <v>1.01</v>
-      </c>
-      <c r="BT35">
-        <v>18</v>
-      </c>
-      <c r="BU35">
-        <v>1.01</v>
-      </c>
       <c r="BV35">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BX35">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9418,7 +9469,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9426,16 +9477,16 @@
         <v>95</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E36" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F36">
         <v>2.3</v>
@@ -9459,7 +9510,7 @@
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N36">
         <v>4.3</v>
@@ -9477,7 +9528,7 @@
         <v>1.5</v>
       </c>
       <c r="S36">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="T36">
         <v>1.52</v>
@@ -9600,10 +9651,10 @@
         <v>21</v>
       </c>
       <c r="BH36">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36">
         <v>13</v>
@@ -9660,7 +9711,7 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9668,16 +9719,16 @@
         <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F37">
         <v>1.99</v>
@@ -9689,7 +9740,7 @@
         <v>3.85</v>
       </c>
       <c r="I37">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J37">
         <v>4.1</v>
@@ -9698,19 +9749,19 @@
         <v>4.2</v>
       </c>
       <c r="L37">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M37">
         <v>1.05</v>
       </c>
       <c r="N37">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O37">
         <v>1.25</v>
       </c>
       <c r="P37">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -9719,7 +9770,7 @@
         <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T37">
         <v>1.7</v>
@@ -9755,7 +9806,7 @@
         <v>15.5</v>
       </c>
       <c r="AE37">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF37">
         <v>14</v>
@@ -9764,7 +9815,7 @@
         <v>10.5</v>
       </c>
       <c r="AH37">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI37">
         <v>46</v>
@@ -9785,7 +9836,7 @@
         <v>11.5</v>
       </c>
       <c r="AO37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP37">
         <v>17.5</v>
@@ -9809,7 +9860,7 @@
         <v>14</v>
       </c>
       <c r="AW37">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AX37">
         <v>12.5</v>
@@ -9830,7 +9881,7 @@
         <v>17.5</v>
       </c>
       <c r="BD37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE37">
         <v>65</v>
@@ -9839,7 +9890,7 @@
         <v>10</v>
       </c>
       <c r="BG37">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9902,7 +9953,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9910,22 +9961,22 @@
         <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F38">
         <v>2.4</v>
       </c>
       <c r="G38">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H38">
         <v>3.3</v>
@@ -9961,7 +10012,7 @@
         <v>1.36</v>
       </c>
       <c r="S38">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T38">
         <v>1.78</v>
@@ -9973,7 +10024,7 @@
         <v>1.41</v>
       </c>
       <c r="W38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X38">
         <v>14.5</v>
@@ -10009,7 +10060,7 @@
         <v>17.5</v>
       </c>
       <c r="AI38">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AJ38">
         <v>34</v>
@@ -10144,7 +10195,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10152,19 +10203,19 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E39" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F39">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G39">
         <v>1.86</v>
@@ -10173,7 +10224,7 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J39">
         <v>3.75</v>
@@ -10194,13 +10245,13 @@
         <v>1.38</v>
       </c>
       <c r="P39">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q39">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R39">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S39">
         <v>3.95</v>
@@ -10212,7 +10263,7 @@
         <v>1.94</v>
       </c>
       <c r="V39">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W39">
         <v>2.16</v>
@@ -10224,10 +10275,10 @@
         <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA39">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
         <v>7.8</v>
@@ -10308,7 +10359,7 @@
         <v>55</v>
       </c>
       <c r="BB39">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC39">
         <v>18.5</v>
@@ -10386,7 +10437,7 @@
         <v>1.7</v>
       </c>
       <c r="CB39" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10394,16 +10445,16 @@
         <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E40" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F40">
         <v>2.48</v>
@@ -10412,7 +10463,7 @@
         <v>2.5</v>
       </c>
       <c r="H40">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I40">
         <v>3.2</v>
@@ -10421,13 +10472,13 @@
         <v>3.5</v>
       </c>
       <c r="K40">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L40">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N40">
         <v>3.4</v>
@@ -10547,7 +10598,7 @@
         <v>16.5</v>
       </c>
       <c r="BA40">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BB40">
         <v>32</v>
@@ -10589,7 +10640,7 @@
         <v>6.2</v>
       </c>
       <c r="BO40">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP40">
         <v>23</v>
@@ -10607,7 +10658,7 @@
         <v>7</v>
       </c>
       <c r="BU40">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV40">
         <v>29</v>
@@ -10628,78 +10679,78 @@
         <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M41">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N41">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O41">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P41">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q41">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="R41">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V41">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W41">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10708,37 +10759,37 @@
         <v>1000</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA41">
         <v>1000</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC41">
         <v>1000</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE41">
         <v>1000</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG41">
         <v>1000</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI41">
         <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK41">
         <v>1000</v>
@@ -10756,7 +10807,7 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ41">
         <v>1.01</v>
@@ -10768,7 +10819,7 @@
         <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU41">
         <v>1.01</v>
@@ -10780,19 +10831,19 @@
         <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA41">
         <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC41">
         <v>1.01</v>
@@ -10804,7 +10855,7 @@
         <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG41">
         <v>1.01</v>
@@ -10816,7 +10867,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BK41">
         <v>1.01</v>
@@ -10828,25 +10879,25 @@
         <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ41">
         <v>1.01</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS41">
         <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU41">
         <v>1.01</v>
@@ -10864,192 +10915,192 @@
         <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA41">
         <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F42">
-        <v>1.53</v>
+        <v>2.98</v>
       </c>
       <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42">
+        <v>2.52</v>
+      </c>
+      <c r="I42">
+        <v>2.56</v>
+      </c>
+      <c r="J42">
+        <v>3.65</v>
+      </c>
+      <c r="K42">
+        <v>3.7</v>
+      </c>
+      <c r="L42">
+        <v>1.01</v>
+      </c>
+      <c r="M42">
+        <v>1.05</v>
+      </c>
+      <c r="N42">
+        <v>4.4</v>
+      </c>
+      <c r="O42">
+        <v>1.26</v>
+      </c>
+      <c r="P42">
+        <v>2.16</v>
+      </c>
+      <c r="Q42">
+        <v>1.8</v>
+      </c>
+      <c r="R42">
+        <v>1.46</v>
+      </c>
+      <c r="S42">
+        <v>3</v>
+      </c>
+      <c r="T42">
+        <v>1.66</v>
+      </c>
+      <c r="U42">
+        <v>2.4</v>
+      </c>
+      <c r="V42">
         <v>1.64</v>
       </c>
-      <c r="H42">
-        <v>7.2</v>
-      </c>
-      <c r="I42">
-        <v>9</v>
-      </c>
-      <c r="J42">
-        <v>3.95</v>
-      </c>
-      <c r="K42">
-        <v>4.9</v>
-      </c>
-      <c r="L42">
-        <v>1.01</v>
-      </c>
-      <c r="M42">
-        <v>1.06</v>
-      </c>
-      <c r="N42">
-        <v>3.1</v>
-      </c>
-      <c r="O42">
-        <v>1.35</v>
-      </c>
-      <c r="P42">
-        <v>1.78</v>
-      </c>
-      <c r="Q42">
-        <v>2.02</v>
-      </c>
-      <c r="R42">
-        <v>1.26</v>
-      </c>
-      <c r="S42">
-        <v>3.6</v>
-      </c>
-      <c r="T42">
-        <v>1.89</v>
-      </c>
-      <c r="U42">
-        <v>1.58</v>
-      </c>
-      <c r="V42">
-        <v>1.12</v>
-      </c>
       <c r="W42">
-        <v>2.56</v>
+        <v>1.5</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z42">
-        <v>90</v>
+        <v>18.5</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB42">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AC42">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD42">
+        <v>12</v>
+      </c>
+      <c r="AE42">
+        <v>26</v>
+      </c>
+      <c r="AF42">
+        <v>22</v>
+      </c>
+      <c r="AG42">
+        <v>13.5</v>
+      </c>
+      <c r="AH42">
+        <v>16</v>
+      </c>
+      <c r="AI42">
+        <v>36</v>
+      </c>
+      <c r="AJ42">
+        <v>48</v>
+      </c>
+      <c r="AK42">
+        <v>32</v>
+      </c>
+      <c r="AL42">
         <v>40</v>
       </c>
-      <c r="AE42">
-        <v>1000</v>
-      </c>
-      <c r="AF42">
+      <c r="AM42">
+        <v>75</v>
+      </c>
+      <c r="AN42">
+        <v>24</v>
+      </c>
+      <c r="AO42">
+        <v>18</v>
+      </c>
+      <c r="AP42">
+        <v>14.5</v>
+      </c>
+      <c r="AQ42">
+        <v>11.5</v>
+      </c>
+      <c r="AR42">
+        <v>16</v>
+      </c>
+      <c r="AS42">
+        <v>32</v>
+      </c>
+      <c r="AT42">
+        <v>13</v>
+      </c>
+      <c r="AU42">
+        <v>7.6</v>
+      </c>
+      <c r="AV42">
         <v>10.5</v>
       </c>
-      <c r="AG42">
-        <v>1000</v>
-      </c>
-      <c r="AH42">
-        <v>36</v>
-      </c>
-      <c r="AI42">
-        <v>1000</v>
-      </c>
-      <c r="AJ42">
+      <c r="AW42">
+        <v>22</v>
+      </c>
+      <c r="AX42">
         <v>18.5</v>
       </c>
-      <c r="AK42">
-        <v>1000</v>
-      </c>
-      <c r="AL42">
-        <v>1000</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>1000</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
-        <v>9</v>
-      </c>
-      <c r="AQ42">
-        <v>1.01</v>
-      </c>
-      <c r="AR42">
-        <v>1.01</v>
-      </c>
-      <c r="AS42">
-        <v>1.01</v>
-      </c>
-      <c r="AT42">
-        <v>5</v>
-      </c>
-      <c r="AU42">
-        <v>1.01</v>
-      </c>
-      <c r="AV42">
-        <v>1.01</v>
-      </c>
-      <c r="AW42">
-        <v>1.01</v>
-      </c>
-      <c r="AX42">
-        <v>5.9</v>
-      </c>
       <c r="AY42">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AZ42">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB42">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE42">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BF42">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11058,7 +11109,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ42">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK42">
         <v>1.01</v>
@@ -11070,25 +11121,25 @@
         <v>1.01</v>
       </c>
       <c r="BN42">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO42">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BP42">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ42">
         <v>1.01</v>
       </c>
       <c r="BR42">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS42">
         <v>1.01</v>
       </c>
       <c r="BT42">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU42">
         <v>1.01</v>
@@ -11106,48 +11157,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ42">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA42">
         <v>1.01</v>
       </c>
       <c r="CB42" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F43">
-        <v>2.98</v>
+        <v>2.08</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="H43">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="I43">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="J43">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K43">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11156,384 +11207,384 @@
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O43">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P43">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q43">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R43">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S43">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T43">
         <v>1.67</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="X43">
+        <v>17</v>
+      </c>
+      <c r="Y43">
+        <v>16</v>
+      </c>
+      <c r="Z43">
+        <v>32</v>
+      </c>
+      <c r="AA43">
+        <v>70</v>
+      </c>
+      <c r="AB43">
+        <v>11.5</v>
+      </c>
+      <c r="AC43">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD43">
         <v>17.5</v>
       </c>
-      <c r="Y43">
+      <c r="AE43">
+        <v>42</v>
+      </c>
+      <c r="AF43">
+        <v>14.5</v>
+      </c>
+      <c r="AG43">
+        <v>11.5</v>
+      </c>
+      <c r="AH43">
+        <v>17.5</v>
+      </c>
+      <c r="AI43">
+        <v>48</v>
+      </c>
+      <c r="AJ43">
+        <v>28</v>
+      </c>
+      <c r="AK43">
+        <v>22</v>
+      </c>
+      <c r="AL43">
+        <v>34</v>
+      </c>
+      <c r="AM43">
+        <v>85</v>
+      </c>
+      <c r="AN43">
+        <v>14.5</v>
+      </c>
+      <c r="AO43">
+        <v>38</v>
+      </c>
+      <c r="AP43">
+        <v>15</v>
+      </c>
+      <c r="AQ43">
         <v>13</v>
       </c>
-      <c r="Z43">
-        <v>18.5</v>
-      </c>
-      <c r="AA43">
+      <c r="AR43">
+        <v>23</v>
+      </c>
+      <c r="AS43">
+        <v>11.5</v>
+      </c>
+      <c r="AT43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU43">
+        <v>7.8</v>
+      </c>
+      <c r="AV43">
+        <v>13</v>
+      </c>
+      <c r="AW43">
+        <v>34</v>
+      </c>
+      <c r="AX43">
+        <v>12.5</v>
+      </c>
+      <c r="AY43">
+        <v>9.6</v>
+      </c>
+      <c r="AZ43">
+        <v>15</v>
+      </c>
+      <c r="BA43">
+        <v>38</v>
+      </c>
+      <c r="BB43">
+        <v>22</v>
+      </c>
+      <c r="BC43">
+        <v>19</v>
+      </c>
+      <c r="BD43">
+        <v>29</v>
+      </c>
+      <c r="BE43">
+        <v>12</v>
+      </c>
+      <c r="BF43">
+        <v>12</v>
+      </c>
+      <c r="BG43">
+        <v>24</v>
+      </c>
+      <c r="BH43">
+        <v>1000</v>
+      </c>
+      <c r="BI43">
+        <v>1.01</v>
+      </c>
+      <c r="BJ43">
+        <v>12.5</v>
+      </c>
+      <c r="BK43">
+        <v>1.01</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>1.01</v>
+      </c>
+      <c r="BN43">
+        <v>6.6</v>
+      </c>
+      <c r="BO43">
+        <v>3.45</v>
+      </c>
+      <c r="BP43">
+        <v>20</v>
+      </c>
+      <c r="BQ43">
+        <v>1.01</v>
+      </c>
+      <c r="BR43">
+        <v>36</v>
+      </c>
+      <c r="BS43">
+        <v>1.01</v>
+      </c>
+      <c r="BT43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU43">
+        <v>4.8</v>
+      </c>
+      <c r="BV43">
         <v>40</v>
       </c>
-      <c r="AB43">
-        <v>14.5</v>
-      </c>
-      <c r="AC43">
-        <v>8.4</v>
-      </c>
-      <c r="AD43">
-        <v>12</v>
-      </c>
-      <c r="AE43">
-        <v>26</v>
-      </c>
-      <c r="AF43">
-        <v>22</v>
-      </c>
-      <c r="AG43">
-        <v>13.5</v>
-      </c>
-      <c r="AH43">
-        <v>16</v>
-      </c>
-      <c r="AI43">
-        <v>36</v>
-      </c>
-      <c r="AJ43">
-        <v>48</v>
-      </c>
-      <c r="AK43">
-        <v>32</v>
-      </c>
-      <c r="AL43">
-        <v>40</v>
-      </c>
-      <c r="AM43">
-        <v>75</v>
-      </c>
-      <c r="AN43">
-        <v>24</v>
-      </c>
-      <c r="AO43">
-        <v>18.5</v>
-      </c>
-      <c r="AP43">
-        <v>14.5</v>
-      </c>
-      <c r="AQ43">
-        <v>11.5</v>
-      </c>
-      <c r="AR43">
-        <v>16</v>
-      </c>
-      <c r="AS43">
-        <v>32</v>
-      </c>
-      <c r="AT43">
-        <v>13</v>
-      </c>
-      <c r="AU43">
-        <v>7.6</v>
-      </c>
-      <c r="AV43">
-        <v>10.5</v>
-      </c>
-      <c r="AW43">
-        <v>22</v>
-      </c>
-      <c r="AX43">
-        <v>18.5</v>
-      </c>
-      <c r="AY43">
-        <v>11.5</v>
-      </c>
-      <c r="AZ43">
-        <v>14.5</v>
-      </c>
-      <c r="BA43">
+      <c r="BW43">
+        <v>1.01</v>
+      </c>
+      <c r="BX43">
+        <v>50</v>
+      </c>
+      <c r="BY43">
+        <v>1.01</v>
+      </c>
+      <c r="BZ43">
         <v>30</v>
       </c>
-      <c r="BB43">
-        <v>40</v>
-      </c>
-      <c r="BC43">
-        <v>26</v>
-      </c>
-      <c r="BD43">
-        <v>32</v>
-      </c>
-      <c r="BE43">
-        <v>34</v>
-      </c>
-      <c r="BF43">
-        <v>20</v>
-      </c>
-      <c r="BG43">
-        <v>16.5</v>
-      </c>
-      <c r="BH43">
-        <v>1000</v>
-      </c>
-      <c r="BI43">
-        <v>1.01</v>
-      </c>
-      <c r="BJ43">
-        <v>1000</v>
-      </c>
-      <c r="BK43">
-        <v>1.01</v>
-      </c>
-      <c r="BL43">
-        <v>1000</v>
-      </c>
-      <c r="BM43">
-        <v>1.01</v>
-      </c>
-      <c r="BN43">
-        <v>1000</v>
-      </c>
-      <c r="BO43">
-        <v>1.01</v>
-      </c>
-      <c r="BP43">
-        <v>1000</v>
-      </c>
-      <c r="BQ43">
-        <v>1.01</v>
-      </c>
-      <c r="BR43">
-        <v>1000</v>
-      </c>
-      <c r="BS43">
-        <v>1.01</v>
-      </c>
-      <c r="BT43">
-        <v>1000</v>
-      </c>
-      <c r="BU43">
-        <v>1.01</v>
-      </c>
-      <c r="BV43">
-        <v>1000</v>
-      </c>
-      <c r="BW43">
-        <v>1.01</v>
-      </c>
-      <c r="BX43">
-        <v>1000</v>
-      </c>
-      <c r="BY43">
-        <v>1.01</v>
-      </c>
-      <c r="BZ43">
-        <v>1000</v>
-      </c>
       <c r="CA43">
         <v>1.01</v>
       </c>
       <c r="CB43" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L44">
         <v>1.01</v>
       </c>
       <c r="M44">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N44">
-        <v>4.1</v>
+        <v>1.26</v>
       </c>
       <c r="O44">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P44">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q44">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="R44">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S44">
-        <v>2.96</v>
+        <v>1.45</v>
       </c>
       <c r="T44">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U44">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W44">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y44">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z44">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA44">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB44">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC44">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD44">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE44">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF44">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG44">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH44">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI44">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ44">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK44">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL44">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM44">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN44">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO44">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP44">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR44">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS44">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT44">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU44">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV44">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW44">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX44">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY44">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA44">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB44">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC44">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD44">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE44">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF44">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG44">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11542,7 +11593,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ44">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK44">
         <v>1.01</v>
@@ -11554,49 +11605,49 @@
         <v>1.01</v>
       </c>
       <c r="BN44">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO44">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP44">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ44">
         <v>1.01</v>
       </c>
       <c r="BR44">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS44">
         <v>1.01</v>
       </c>
       <c r="BT44">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU44">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV44">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW44">
         <v>1.01</v>
       </c>
       <c r="BX44">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY44">
         <v>1.01</v>
       </c>
       <c r="BZ44">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA44">
         <v>1.01</v>
       </c>
       <c r="CB44" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11604,16 +11655,16 @@
         <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -11640,7 +11691,7 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O45">
         <v>1.01</v>
@@ -11838,7 +11889,7 @@
         <v>1.01</v>
       </c>
       <c r="CB45" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11846,16 +11897,16 @@
         <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F46">
         <v>5.9</v>
@@ -11888,7 +11939,7 @@
         <v>1.21</v>
       </c>
       <c r="P46">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q46">
         <v>1.6</v>
@@ -11912,19 +11963,19 @@
         <v>1.19</v>
       </c>
       <c r="X46">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y46">
         <v>12</v>
       </c>
       <c r="Z46">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AA46">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AB46">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AC46">
         <v>13</v>
@@ -11933,13 +11984,13 @@
         <v>12.5</v>
       </c>
       <c r="AE46">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AF46">
         <v>48</v>
       </c>
       <c r="AG46">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH46">
         <v>23</v>
@@ -11975,10 +12026,10 @@
         <v>10</v>
       </c>
       <c r="AS46">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT46">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AU46">
         <v>9.6</v>
@@ -11990,10 +12041,10 @@
         <v>13.5</v>
       </c>
       <c r="AX46">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY46">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ46">
         <v>13.5</v>
@@ -12002,19 +12053,19 @@
         <v>20</v>
       </c>
       <c r="BB46">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BC46">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD46">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE46">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF46">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG46">
         <v>5.4</v>
@@ -12080,7 +12131,1217 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>200</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:80">
+      <c r="A47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47">
+        <v>1.82</v>
+      </c>
+      <c r="G47">
+        <v>1.99</v>
+      </c>
+      <c r="H47">
+        <v>4.8</v>
+      </c>
+      <c r="I47">
+        <v>5.7</v>
+      </c>
+      <c r="J47">
+        <v>3.25</v>
+      </c>
+      <c r="K47">
+        <v>3.8</v>
+      </c>
+      <c r="L47">
+        <v>1.38</v>
+      </c>
+      <c r="M47">
+        <v>1.09</v>
+      </c>
+      <c r="N47">
+        <v>1.01</v>
+      </c>
+      <c r="O47">
+        <v>1.42</v>
+      </c>
+      <c r="P47">
+        <v>1.64</v>
+      </c>
+      <c r="Q47">
+        <v>2.24</v>
+      </c>
+      <c r="R47">
+        <v>1.22</v>
+      </c>
+      <c r="S47">
+        <v>4.1</v>
+      </c>
+      <c r="T47">
+        <v>1.96</v>
+      </c>
+      <c r="U47">
+        <v>1.77</v>
+      </c>
+      <c r="V47">
+        <v>1.21</v>
+      </c>
+      <c r="W47">
+        <v>2</v>
+      </c>
+      <c r="X47">
+        <v>1000</v>
+      </c>
+      <c r="Y47">
+        <v>1000</v>
+      </c>
+      <c r="Z47">
+        <v>1000</v>
+      </c>
+      <c r="AA47">
+        <v>1000</v>
+      </c>
+      <c r="AB47">
+        <v>1000</v>
+      </c>
+      <c r="AC47">
+        <v>1000</v>
+      </c>
+      <c r="AD47">
+        <v>1000</v>
+      </c>
+      <c r="AE47">
+        <v>1000</v>
+      </c>
+      <c r="AF47">
+        <v>1000</v>
+      </c>
+      <c r="AG47">
+        <v>1000</v>
+      </c>
+      <c r="AH47">
+        <v>1000</v>
+      </c>
+      <c r="AI47">
+        <v>1000</v>
+      </c>
+      <c r="AJ47">
+        <v>1000</v>
+      </c>
+      <c r="AK47">
+        <v>1000</v>
+      </c>
+      <c r="AL47">
+        <v>1000</v>
+      </c>
+      <c r="AM47">
+        <v>1000</v>
+      </c>
+      <c r="AN47">
+        <v>1000</v>
+      </c>
+      <c r="AO47">
+        <v>1000</v>
+      </c>
+      <c r="AP47">
+        <v>1.01</v>
+      </c>
+      <c r="AQ47">
+        <v>1.01</v>
+      </c>
+      <c r="AR47">
+        <v>1.01</v>
+      </c>
+      <c r="AS47">
+        <v>1.01</v>
+      </c>
+      <c r="AT47">
+        <v>1.01</v>
+      </c>
+      <c r="AU47">
+        <v>1.01</v>
+      </c>
+      <c r="AV47">
+        <v>1.01</v>
+      </c>
+      <c r="AW47">
+        <v>1.01</v>
+      </c>
+      <c r="AX47">
+        <v>1.01</v>
+      </c>
+      <c r="AY47">
+        <v>1.01</v>
+      </c>
+      <c r="AZ47">
+        <v>1.01</v>
+      </c>
+      <c r="BA47">
+        <v>1.01</v>
+      </c>
+      <c r="BB47">
+        <v>1.01</v>
+      </c>
+      <c r="BC47">
+        <v>1.01</v>
+      </c>
+      <c r="BD47">
+        <v>1.01</v>
+      </c>
+      <c r="BE47">
+        <v>1.01</v>
+      </c>
+      <c r="BF47">
+        <v>1.01</v>
+      </c>
+      <c r="BG47">
+        <v>1.01</v>
+      </c>
+      <c r="BH47">
+        <v>1000</v>
+      </c>
+      <c r="BI47">
+        <v>1.01</v>
+      </c>
+      <c r="BJ47">
+        <v>1000</v>
+      </c>
+      <c r="BK47">
+        <v>1.01</v>
+      </c>
+      <c r="BL47">
+        <v>1000</v>
+      </c>
+      <c r="BM47">
+        <v>1.01</v>
+      </c>
+      <c r="BN47">
+        <v>1000</v>
+      </c>
+      <c r="BO47">
+        <v>1.01</v>
+      </c>
+      <c r="BP47">
+        <v>1000</v>
+      </c>
+      <c r="BQ47">
+        <v>1.01</v>
+      </c>
+      <c r="BR47">
+        <v>1000</v>
+      </c>
+      <c r="BS47">
+        <v>1.01</v>
+      </c>
+      <c r="BT47">
+        <v>1000</v>
+      </c>
+      <c r="BU47">
+        <v>1.01</v>
+      </c>
+      <c r="BV47">
+        <v>1000</v>
+      </c>
+      <c r="BW47">
+        <v>1.01</v>
+      </c>
+      <c r="BX47">
+        <v>1000</v>
+      </c>
+      <c r="BY47">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47">
+        <v>1000</v>
+      </c>
+      <c r="CA47">
+        <v>1.01</v>
+      </c>
+      <c r="CB47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:80">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E48" t="s">
+        <v>213</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>1.01</v>
+      </c>
+      <c r="M48">
+        <v>1.01</v>
+      </c>
+      <c r="N48">
+        <v>1.26</v>
+      </c>
+      <c r="O48">
+        <v>1.32</v>
+      </c>
+      <c r="P48">
+        <v>1.25</v>
+      </c>
+      <c r="Q48">
+        <v>1.32</v>
+      </c>
+      <c r="R48">
+        <v>1.18</v>
+      </c>
+      <c r="S48">
+        <v>1.33</v>
+      </c>
+      <c r="T48">
+        <v>1.01</v>
+      </c>
+      <c r="U48">
+        <v>1.01</v>
+      </c>
+      <c r="V48">
+        <v>1.01</v>
+      </c>
+      <c r="W48">
+        <v>1.01</v>
+      </c>
+      <c r="X48">
+        <v>1000</v>
+      </c>
+      <c r="Y48">
+        <v>1000</v>
+      </c>
+      <c r="Z48">
+        <v>1000</v>
+      </c>
+      <c r="AA48">
+        <v>1000</v>
+      </c>
+      <c r="AB48">
+        <v>1000</v>
+      </c>
+      <c r="AC48">
+        <v>1000</v>
+      </c>
+      <c r="AD48">
+        <v>1000</v>
+      </c>
+      <c r="AE48">
+        <v>1000</v>
+      </c>
+      <c r="AF48">
+        <v>1000</v>
+      </c>
+      <c r="AG48">
+        <v>1000</v>
+      </c>
+      <c r="AH48">
+        <v>1000</v>
+      </c>
+      <c r="AI48">
+        <v>1000</v>
+      </c>
+      <c r="AJ48">
+        <v>1000</v>
+      </c>
+      <c r="AK48">
+        <v>1000</v>
+      </c>
+      <c r="AL48">
+        <v>1000</v>
+      </c>
+      <c r="AM48">
+        <v>1000</v>
+      </c>
+      <c r="AN48">
+        <v>1000</v>
+      </c>
+      <c r="AO48">
+        <v>1000</v>
+      </c>
+      <c r="AP48">
+        <v>1.01</v>
+      </c>
+      <c r="AQ48">
+        <v>1.01</v>
+      </c>
+      <c r="AR48">
+        <v>1.01</v>
+      </c>
+      <c r="AS48">
+        <v>1.01</v>
+      </c>
+      <c r="AT48">
+        <v>1.01</v>
+      </c>
+      <c r="AU48">
+        <v>1.01</v>
+      </c>
+      <c r="AV48">
+        <v>1.01</v>
+      </c>
+      <c r="AW48">
+        <v>1.01</v>
+      </c>
+      <c r="AX48">
+        <v>1.01</v>
+      </c>
+      <c r="AY48">
+        <v>1.01</v>
+      </c>
+      <c r="AZ48">
+        <v>1.01</v>
+      </c>
+      <c r="BA48">
+        <v>1.01</v>
+      </c>
+      <c r="BB48">
+        <v>1.01</v>
+      </c>
+      <c r="BC48">
+        <v>1.01</v>
+      </c>
+      <c r="BD48">
+        <v>1.01</v>
+      </c>
+      <c r="BE48">
+        <v>1.01</v>
+      </c>
+      <c r="BF48">
+        <v>1.01</v>
+      </c>
+      <c r="BG48">
+        <v>1.01</v>
+      </c>
+      <c r="BH48">
+        <v>1000</v>
+      </c>
+      <c r="BI48">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48">
+        <v>1000</v>
+      </c>
+      <c r="BK48">
+        <v>1.01</v>
+      </c>
+      <c r="BL48">
+        <v>1000</v>
+      </c>
+      <c r="BM48">
+        <v>1.01</v>
+      </c>
+      <c r="BN48">
+        <v>1000</v>
+      </c>
+      <c r="BO48">
+        <v>1.01</v>
+      </c>
+      <c r="BP48">
+        <v>1000</v>
+      </c>
+      <c r="BQ48">
+        <v>1.01</v>
+      </c>
+      <c r="BR48">
+        <v>1000</v>
+      </c>
+      <c r="BS48">
+        <v>1.01</v>
+      </c>
+      <c r="BT48">
+        <v>1000</v>
+      </c>
+      <c r="BU48">
+        <v>1.01</v>
+      </c>
+      <c r="BV48">
+        <v>1000</v>
+      </c>
+      <c r="BW48">
+        <v>1.01</v>
+      </c>
+      <c r="BX48">
+        <v>1000</v>
+      </c>
+      <c r="BY48">
+        <v>1.01</v>
+      </c>
+      <c r="BZ48">
+        <v>1000</v>
+      </c>
+      <c r="CA48">
+        <v>1.01</v>
+      </c>
+      <c r="CB48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:80">
+      <c r="A49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" t="s">
+        <v>214</v>
+      </c>
+      <c r="F49">
+        <v>1.61</v>
+      </c>
+      <c r="G49">
+        <v>1.69</v>
+      </c>
+      <c r="H49">
+        <v>5.8</v>
+      </c>
+      <c r="I49">
+        <v>6.6</v>
+      </c>
+      <c r="J49">
+        <v>4.1</v>
+      </c>
+      <c r="K49">
+        <v>4.5</v>
+      </c>
+      <c r="L49">
+        <v>1.27</v>
+      </c>
+      <c r="M49">
+        <v>1.05</v>
+      </c>
+      <c r="N49">
+        <v>4.2</v>
+      </c>
+      <c r="O49">
+        <v>1.26</v>
+      </c>
+      <c r="P49">
+        <v>2.1</v>
+      </c>
+      <c r="Q49">
+        <v>1.79</v>
+      </c>
+      <c r="R49">
+        <v>1.42</v>
+      </c>
+      <c r="S49">
+        <v>2.94</v>
+      </c>
+      <c r="T49">
+        <v>1.01</v>
+      </c>
+      <c r="U49">
+        <v>1.01</v>
+      </c>
+      <c r="V49">
+        <v>1.17</v>
+      </c>
+      <c r="W49">
+        <v>2.44</v>
+      </c>
+      <c r="X49">
+        <v>21</v>
+      </c>
+      <c r="Y49">
+        <v>25</v>
+      </c>
+      <c r="Z49">
+        <v>60</v>
+      </c>
+      <c r="AA49">
+        <v>190</v>
+      </c>
+      <c r="AB49">
+        <v>10.5</v>
+      </c>
+      <c r="AC49">
+        <v>11.5</v>
+      </c>
+      <c r="AD49">
+        <v>27</v>
+      </c>
+      <c r="AE49">
+        <v>95</v>
+      </c>
+      <c r="AF49">
+        <v>12</v>
+      </c>
+      <c r="AG49">
+        <v>11.5</v>
+      </c>
+      <c r="AH49">
+        <v>24</v>
+      </c>
+      <c r="AI49">
+        <v>90</v>
+      </c>
+      <c r="AJ49">
+        <v>19</v>
+      </c>
+      <c r="AK49">
+        <v>19.5</v>
+      </c>
+      <c r="AL49">
+        <v>40</v>
+      </c>
+      <c r="AM49">
+        <v>130</v>
+      </c>
+      <c r="AN49">
+        <v>10.5</v>
+      </c>
+      <c r="AO49">
+        <v>110</v>
+      </c>
+      <c r="AP49">
+        <v>13.5</v>
+      </c>
+      <c r="AQ49">
+        <v>16.5</v>
+      </c>
+      <c r="AR49">
+        <v>1.01</v>
+      </c>
+      <c r="AS49">
+        <v>1.01</v>
+      </c>
+      <c r="AT49">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU49">
+        <v>7.6</v>
+      </c>
+      <c r="AV49">
+        <v>17.5</v>
+      </c>
+      <c r="AW49">
+        <v>1.01</v>
+      </c>
+      <c r="AX49">
+        <v>8</v>
+      </c>
+      <c r="AY49">
+        <v>9</v>
+      </c>
+      <c r="AZ49">
+        <v>15.5</v>
+      </c>
+      <c r="BA49">
+        <v>1.01</v>
+      </c>
+      <c r="BB49">
+        <v>14</v>
+      </c>
+      <c r="BC49">
+        <v>13</v>
+      </c>
+      <c r="BD49">
+        <v>1.01</v>
+      </c>
+      <c r="BE49">
+        <v>1.01</v>
+      </c>
+      <c r="BF49">
+        <v>6.8</v>
+      </c>
+      <c r="BG49">
+        <v>1.01</v>
+      </c>
+      <c r="BH49">
+        <v>1000</v>
+      </c>
+      <c r="BI49">
+        <v>1.01</v>
+      </c>
+      <c r="BJ49">
+        <v>1000</v>
+      </c>
+      <c r="BK49">
+        <v>1.01</v>
+      </c>
+      <c r="BL49">
+        <v>1000</v>
+      </c>
+      <c r="BM49">
+        <v>1.01</v>
+      </c>
+      <c r="BN49">
+        <v>1000</v>
+      </c>
+      <c r="BO49">
+        <v>1.01</v>
+      </c>
+      <c r="BP49">
+        <v>1000</v>
+      </c>
+      <c r="BQ49">
+        <v>1.01</v>
+      </c>
+      <c r="BR49">
+        <v>1000</v>
+      </c>
+      <c r="BS49">
+        <v>1.01</v>
+      </c>
+      <c r="BT49">
+        <v>1000</v>
+      </c>
+      <c r="BU49">
+        <v>1.01</v>
+      </c>
+      <c r="BV49">
+        <v>1000</v>
+      </c>
+      <c r="BW49">
+        <v>1.01</v>
+      </c>
+      <c r="BX49">
+        <v>1000</v>
+      </c>
+      <c r="BY49">
+        <v>1.01</v>
+      </c>
+      <c r="BZ49">
+        <v>1000</v>
+      </c>
+      <c r="CA49">
+        <v>1.01</v>
+      </c>
+      <c r="CB49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:80">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50" t="s">
+        <v>215</v>
+      </c>
+      <c r="F50">
+        <v>1.28</v>
+      </c>
+      <c r="G50">
+        <v>1.3</v>
+      </c>
+      <c r="H50">
+        <v>12.5</v>
+      </c>
+      <c r="I50">
+        <v>15</v>
+      </c>
+      <c r="J50">
+        <v>6.6</v>
+      </c>
+      <c r="K50">
+        <v>6.8</v>
+      </c>
+      <c r="L50">
+        <v>1.01</v>
+      </c>
+      <c r="M50">
+        <v>1.04</v>
+      </c>
+      <c r="N50">
+        <v>4.9</v>
+      </c>
+      <c r="O50">
+        <v>1.21</v>
+      </c>
+      <c r="P50">
+        <v>2.38</v>
+      </c>
+      <c r="Q50">
+        <v>1.53</v>
+      </c>
+      <c r="R50">
+        <v>1.58</v>
+      </c>
+      <c r="S50">
+        <v>2.56</v>
+      </c>
+      <c r="T50">
+        <v>2.18</v>
+      </c>
+      <c r="U50">
+        <v>1.7</v>
+      </c>
+      <c r="V50">
+        <v>1.07</v>
+      </c>
+      <c r="W50">
+        <v>4.3</v>
+      </c>
+      <c r="X50">
+        <v>23</v>
+      </c>
+      <c r="Y50">
+        <v>40</v>
+      </c>
+      <c r="Z50">
+        <v>140</v>
+      </c>
+      <c r="AA50">
+        <v>750</v>
+      </c>
+      <c r="AB50">
+        <v>9</v>
+      </c>
+      <c r="AC50">
+        <v>14.5</v>
+      </c>
+      <c r="AD50">
+        <v>48</v>
+      </c>
+      <c r="AE50">
+        <v>260</v>
+      </c>
+      <c r="AF50">
+        <v>8</v>
+      </c>
+      <c r="AG50">
+        <v>11.5</v>
+      </c>
+      <c r="AH50">
+        <v>36</v>
+      </c>
+      <c r="AI50">
+        <v>230</v>
+      </c>
+      <c r="AJ50">
+        <v>10</v>
+      </c>
+      <c r="AK50">
+        <v>15</v>
+      </c>
+      <c r="AL50">
+        <v>42</v>
+      </c>
+      <c r="AM50">
+        <v>240</v>
+      </c>
+      <c r="AN50">
+        <v>4.9</v>
+      </c>
+      <c r="AO50">
+        <v>440</v>
+      </c>
+      <c r="AP50">
+        <v>19.5</v>
+      </c>
+      <c r="AQ50">
+        <v>34</v>
+      </c>
+      <c r="AR50">
+        <v>12.5</v>
+      </c>
+      <c r="AS50">
+        <v>14</v>
+      </c>
+      <c r="AT50">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU50">
+        <v>12.5</v>
+      </c>
+      <c r="AV50">
+        <v>40</v>
+      </c>
+      <c r="AW50">
+        <v>13</v>
+      </c>
+      <c r="AX50">
+        <v>6.8</v>
+      </c>
+      <c r="AY50">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ50">
+        <v>30</v>
+      </c>
+      <c r="BA50">
+        <v>13</v>
+      </c>
+      <c r="BB50">
+        <v>8.6</v>
+      </c>
+      <c r="BC50">
+        <v>13</v>
+      </c>
+      <c r="BD50">
+        <v>36</v>
+      </c>
+      <c r="BE50">
+        <v>13</v>
+      </c>
+      <c r="BF50">
+        <v>4.4</v>
+      </c>
+      <c r="BG50">
+        <v>13.5</v>
+      </c>
+      <c r="BH50">
+        <v>1000</v>
+      </c>
+      <c r="BI50">
+        <v>1.01</v>
+      </c>
+      <c r="BJ50">
+        <v>1000</v>
+      </c>
+      <c r="BK50">
+        <v>1.01</v>
+      </c>
+      <c r="BL50">
+        <v>1000</v>
+      </c>
+      <c r="BM50">
+        <v>1.01</v>
+      </c>
+      <c r="BN50">
+        <v>1000</v>
+      </c>
+      <c r="BO50">
+        <v>1.01</v>
+      </c>
+      <c r="BP50">
+        <v>1000</v>
+      </c>
+      <c r="BQ50">
+        <v>1.01</v>
+      </c>
+      <c r="BR50">
+        <v>1000</v>
+      </c>
+      <c r="BS50">
+        <v>1.01</v>
+      </c>
+      <c r="BT50">
+        <v>1000</v>
+      </c>
+      <c r="BU50">
+        <v>1.01</v>
+      </c>
+      <c r="BV50">
+        <v>1000</v>
+      </c>
+      <c r="BW50">
+        <v>1.01</v>
+      </c>
+      <c r="BX50">
+        <v>1000</v>
+      </c>
+      <c r="BY50">
+        <v>1.01</v>
+      </c>
+      <c r="BZ50">
+        <v>1000</v>
+      </c>
+      <c r="CA50">
+        <v>1.01</v>
+      </c>
+      <c r="CB50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:80">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" t="s">
+        <v>216</v>
+      </c>
+      <c r="F51">
+        <v>1.54</v>
+      </c>
+      <c r="G51">
+        <v>1.65</v>
+      </c>
+      <c r="H51">
+        <v>5.9</v>
+      </c>
+      <c r="I51">
+        <v>7.8</v>
+      </c>
+      <c r="J51">
+        <v>4.2</v>
+      </c>
+      <c r="K51">
+        <v>5.5</v>
+      </c>
+      <c r="L51">
+        <v>1.01</v>
+      </c>
+      <c r="M51">
+        <v>1.01</v>
+      </c>
+      <c r="N51">
+        <v>2.52</v>
+      </c>
+      <c r="O51">
+        <v>1.21</v>
+      </c>
+      <c r="P51">
+        <v>2.18</v>
+      </c>
+      <c r="Q51">
+        <v>1.65</v>
+      </c>
+      <c r="R51">
+        <v>1.43</v>
+      </c>
+      <c r="S51">
+        <v>2.66</v>
+      </c>
+      <c r="T51">
+        <v>1.01</v>
+      </c>
+      <c r="U51">
+        <v>1.01</v>
+      </c>
+      <c r="V51">
+        <v>1.15</v>
+      </c>
+      <c r="W51">
+        <v>2.52</v>
+      </c>
+      <c r="X51">
+        <v>1000</v>
+      </c>
+      <c r="Y51">
+        <v>1000</v>
+      </c>
+      <c r="Z51">
+        <v>1000</v>
+      </c>
+      <c r="AA51">
+        <v>1000</v>
+      </c>
+      <c r="AB51">
+        <v>1000</v>
+      </c>
+      <c r="AC51">
+        <v>1000</v>
+      </c>
+      <c r="AD51">
+        <v>1000</v>
+      </c>
+      <c r="AE51">
+        <v>1000</v>
+      </c>
+      <c r="AF51">
+        <v>1000</v>
+      </c>
+      <c r="AG51">
+        <v>1000</v>
+      </c>
+      <c r="AH51">
+        <v>1000</v>
+      </c>
+      <c r="AI51">
+        <v>1000</v>
+      </c>
+      <c r="AJ51">
+        <v>1000</v>
+      </c>
+      <c r="AK51">
+        <v>1000</v>
+      </c>
+      <c r="AL51">
+        <v>1000</v>
+      </c>
+      <c r="AM51">
+        <v>1000</v>
+      </c>
+      <c r="AN51">
+        <v>1000</v>
+      </c>
+      <c r="AO51">
+        <v>1000</v>
+      </c>
+      <c r="AP51">
+        <v>1.01</v>
+      </c>
+      <c r="AQ51">
+        <v>1.01</v>
+      </c>
+      <c r="AR51">
+        <v>1.01</v>
+      </c>
+      <c r="AS51">
+        <v>1.01</v>
+      </c>
+      <c r="AT51">
+        <v>1.01</v>
+      </c>
+      <c r="AU51">
+        <v>1.01</v>
+      </c>
+      <c r="AV51">
+        <v>1.01</v>
+      </c>
+      <c r="AW51">
+        <v>1.01</v>
+      </c>
+      <c r="AX51">
+        <v>1.01</v>
+      </c>
+      <c r="AY51">
+        <v>1.01</v>
+      </c>
+      <c r="AZ51">
+        <v>1.01</v>
+      </c>
+      <c r="BA51">
+        <v>1.01</v>
+      </c>
+      <c r="BB51">
+        <v>1.01</v>
+      </c>
+      <c r="BC51">
+        <v>1.01</v>
+      </c>
+      <c r="BD51">
+        <v>1.01</v>
+      </c>
+      <c r="BE51">
+        <v>1.01</v>
+      </c>
+      <c r="BF51">
+        <v>1.01</v>
+      </c>
+      <c r="BG51">
+        <v>1.01</v>
+      </c>
+      <c r="BH51">
+        <v>1000</v>
+      </c>
+      <c r="BI51">
+        <v>1.01</v>
+      </c>
+      <c r="BJ51">
+        <v>1000</v>
+      </c>
+      <c r="BK51">
+        <v>1.01</v>
+      </c>
+      <c r="BL51">
+        <v>1000</v>
+      </c>
+      <c r="BM51">
+        <v>1.01</v>
+      </c>
+      <c r="BN51">
+        <v>1000</v>
+      </c>
+      <c r="BO51">
+        <v>1.01</v>
+      </c>
+      <c r="BP51">
+        <v>1000</v>
+      </c>
+      <c r="BQ51">
+        <v>1.01</v>
+      </c>
+      <c r="BR51">
+        <v>1000</v>
+      </c>
+      <c r="BS51">
+        <v>1.01</v>
+      </c>
+      <c r="BT51">
+        <v>1000</v>
+      </c>
+      <c r="BU51">
+        <v>1.01</v>
+      </c>
+      <c r="BV51">
+        <v>1000</v>
+      </c>
+      <c r="BW51">
+        <v>1.01</v>
+      </c>
+      <c r="BX51">
+        <v>1000</v>
+      </c>
+      <c r="BY51">
+        <v>1.01</v>
+      </c>
+      <c r="BZ51">
+        <v>0</v>
+      </c>
+      <c r="CA51">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -667,7 +667,7 @@
     <t>Hartford Athletic FC</t>
   </si>
   <si>
-    <t>2026-09-01 00:10:39</t>
+    <t>2026-09-01 02:23:02</t>
   </si>
 </sst>
 </file>
@@ -1261,46 +1261,46 @@
         <v>167</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
         <v>5.8</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
+        <v>3.75</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.92</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>1.36</v>
+      </c>
+      <c r="S2">
         <v>3.6</v>
-      </c>
-      <c r="O2">
-        <v>1.31</v>
-      </c>
-      <c r="P2">
-        <v>1.9</v>
-      </c>
-      <c r="Q2">
-        <v>1.84</v>
-      </c>
-      <c r="R2">
-        <v>1.33</v>
-      </c>
-      <c r="S2">
-        <v>3.4</v>
       </c>
       <c r="T2">
         <v>1.96</v>
@@ -1309,13 +1309,13 @@
         <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
         <v>23</v>
@@ -1363,7 +1363,7 @@
         <v>160</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO2">
         <v>150</v>
@@ -1375,10 +1375,10 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1390,7 +1390,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
         <v>7.4</v>
@@ -1399,10 +1399,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1411,16 +1411,16 @@
         <v>14</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>3.8</v>
@@ -1432,7 +1432,7 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>180</v>
@@ -1450,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="BQ2">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>32</v>
@@ -1503,58 +1503,58 @@
         <v>168</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
         <v>13.5</v>
@@ -1572,7 +1572,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
         <v>15</v>
@@ -1632,10 +1632,10 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1644,25 +1644,25 @@
         <v>16</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1748,16 +1748,16 @@
         <v>1.54</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -1775,13 +1775,13 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
         <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S4">
         <v>2.6</v>
@@ -1793,10 +1793,10 @@
         <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X4">
         <v>28</v>
@@ -1832,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1901,16 +1901,16 @@
         <v>11</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG4">
         <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4">
         <v>12</v>
@@ -2011,13 +2011,13 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
         <v>2.08</v>
@@ -2026,7 +2026,7 @@
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
         <v>1.86</v>
@@ -2065,7 +2065,7 @@
         <v>28</v>
       </c>
       <c r="AF5">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AG5">
         <v>17</v>
@@ -2131,19 +2131,19 @@
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC5">
         <v>7.4</v>
       </c>
       <c r="BD5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
         <v>15.5</v>
@@ -2232,10 +2232,10 @@
         <v>3.55</v>
       </c>
       <c r="G6">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H6">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="I6">
         <v>2.24</v>
@@ -2244,7 +2244,7 @@
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2253,22 +2253,22 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R6">
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
         <v>1.63</v>
@@ -2280,7 +2280,7 @@
         <v>1.81</v>
       </c>
       <c r="W6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X6">
         <v>18.5</v>
@@ -2379,7 +2379,7 @@
         <v>7</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE6">
         <v>7.6</v>
@@ -2474,13 +2474,13 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H7">
         <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J7">
         <v>3.2</v>
@@ -2495,7 +2495,7 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
         <v>1.54</v>
@@ -2507,7 +2507,7 @@
         <v>2.52</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
         <v>5.3</v>
@@ -2525,7 +2525,7 @@
         <v>1.29</v>
       </c>
       <c r="X7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -2576,7 +2576,7 @@
         <v>130</v>
       </c>
       <c r="AO7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP7">
         <v>7.6</v>
@@ -2588,22 +2588,22 @@
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
         <v>16</v>
@@ -2612,22 +2612,22 @@
         <v>20</v>
       </c>
       <c r="BA7">
+        <v>28</v>
+      </c>
+      <c r="BB7">
+        <v>9</v>
+      </c>
+      <c r="BC7">
+        <v>8.6</v>
+      </c>
+      <c r="BD7">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC7">
-        <v>9</v>
-      </c>
-      <c r="BD7">
-        <v>9.199999999999999</v>
       </c>
       <c r="BE7">
         <v>9.199999999999999</v>
       </c>
       <c r="BF7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG7">
         <v>7.6</v>
@@ -2722,13 +2722,13 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J8">
         <v>3.7</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2737,40 +2737,40 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T8">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
         <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W8">
         <v>1.29</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Z8">
         <v>12.5</v>
@@ -2782,13 +2782,13 @@
         <v>15.5</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AF8">
         <v>32</v>
@@ -2797,19 +2797,19 @@
         <v>17</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
         <v>110</v>
       </c>
       <c r="AK8">
+        <v>55</v>
+      </c>
+      <c r="AL8">
         <v>70</v>
-      </c>
-      <c r="AL8">
-        <v>75</v>
       </c>
       <c r="AM8">
         <v>120</v>
@@ -2818,13 +2818,13 @@
         <v>70</v>
       </c>
       <c r="AO8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
         <v>13</v>
       </c>
       <c r="AQ8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR8">
         <v>11</v>
@@ -2836,7 +2836,7 @@
         <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV8">
         <v>9.6</v>
@@ -2845,7 +2845,7 @@
         <v>19</v>
       </c>
       <c r="AX8">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AY8">
         <v>15</v>
@@ -2854,25 +2854,25 @@
         <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB8">
         <v>6.4</v>
       </c>
       <c r="BC8">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BD8">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE8">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BF8">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2967,52 +2967,52 @@
         <v>3.85</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P9">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q9">
         <v>1.89</v>
       </c>
       <c r="R9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
         <v>3.25</v>
       </c>
       <c r="T9">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z9">
         <v>30</v>
@@ -3021,19 +3021,19 @@
         <v>75</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>8.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
         <v>48</v>
       </c>
       <c r="AF9">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG9">
         <v>13.5</v>
@@ -3048,43 +3048,43 @@
         <v>36</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM9">
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO9">
         <v>44</v>
       </c>
       <c r="AP9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR9">
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AW9">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX9">
         <v>13</v>
@@ -3096,31 +3096,31 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="BB9">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BC9">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG9">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI9">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
@@ -3138,10 +3138,10 @@
         <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
@@ -3156,13 +3156,13 @@
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV9">
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX9">
         <v>46</v>
@@ -3171,7 +3171,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3197,70 +3197,70 @@
         <v>175</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G10">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="I10">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U10">
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="W10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X10">
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB10">
         <v>16.5</v>
@@ -3269,19 +3269,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE10">
         <v>26</v>
       </c>
       <c r="AF10">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AG10">
         <v>21</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10">
         <v>48</v>
@@ -3290,28 +3290,28 @@
         <v>110</v>
       </c>
       <c r="AK10">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM10">
         <v>140</v>
       </c>
       <c r="AN10">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AO10">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP10">
         <v>11</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS10">
         <v>18.5</v>
@@ -3320,10 +3320,10 @@
         <v>12</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10">
         <v>17.5</v>
@@ -3338,25 +3338,25 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BB10">
+        <v>7.2</v>
+      </c>
+      <c r="BC10">
         <v>7</v>
       </c>
-      <c r="BC10">
-        <v>6.8</v>
-      </c>
       <c r="BD10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE10">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG10">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BH10">
         <v>3.6</v>
@@ -3368,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL10">
         <v>170</v>
@@ -3377,13 +3377,13 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
@@ -3395,13 +3395,13 @@
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU10">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
@@ -3410,13 +3410,13 @@
         <v>36</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>217</v>
@@ -3448,7 +3448,7 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
         <v>3.65</v>
@@ -3472,16 +3472,16 @@
         <v>2.02</v>
       </c>
       <c r="Q11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
         <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U11">
         <v>2.16</v>
@@ -3496,10 +3496,10 @@
         <v>18.5</v>
       </c>
       <c r="Y11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA11">
         <v>95</v>
@@ -3508,22 +3508,22 @@
         <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE11">
         <v>60</v>
       </c>
       <c r="AF11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>65</v>
@@ -3541,7 +3541,7 @@
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO11">
         <v>60</v>
@@ -3556,19 +3556,19 @@
         <v>23</v>
       </c>
       <c r="AS11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT11">
         <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV11">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AX11">
         <v>11</v>
@@ -3577,28 +3577,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB11">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BC11">
         <v>17.5</v>
       </c>
       <c r="BD11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF11">
         <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3681,22 +3681,22 @@
         <v>177</v>
       </c>
       <c r="F12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G12">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H12">
         <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3714,19 +3714,19 @@
         <v>1.69</v>
       </c>
       <c r="Q12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R12">
         <v>1.26</v>
       </c>
       <c r="S12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T12">
         <v>1.98</v>
       </c>
       <c r="U12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -3753,7 +3753,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE12">
         <v>55</v>
@@ -3783,22 +3783,22 @@
         <v>180</v>
       </c>
       <c r="AN12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO12">
         <v>60</v>
       </c>
       <c r="AP12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12">
         <v>18</v>
       </c>
       <c r="AS12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3822,25 +3822,25 @@
         <v>10</v>
       </c>
       <c r="BA12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB12">
         <v>6</v>
       </c>
       <c r="BC12">
+        <v>5.8</v>
+      </c>
+      <c r="BD12">
+        <v>5.8</v>
+      </c>
+      <c r="BE12">
+        <v>6.2</v>
+      </c>
+      <c r="BF12">
+        <v>5.8</v>
+      </c>
+      <c r="BG12">
         <v>5.9</v>
-      </c>
-      <c r="BD12">
-        <v>6</v>
-      </c>
-      <c r="BE12">
-        <v>6.4</v>
-      </c>
-      <c r="BF12">
-        <v>6</v>
-      </c>
-      <c r="BG12">
-        <v>6</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3867,7 +3867,7 @@
         <v>3.85</v>
       </c>
       <c r="BP12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ12">
         <v>1.01</v>
@@ -3885,7 +3885,7 @@
         <v>4.4</v>
       </c>
       <c r="BV12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW12">
         <v>1.01</v>
@@ -3926,34 +3926,34 @@
         <v>2.9</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I13">
         <v>3.5</v>
       </c>
       <c r="J13">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
         <v>2.18</v>
       </c>
       <c r="O13">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3965,43 +3965,43 @@
         <v>6.4</v>
       </c>
       <c r="T13">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9.199999999999999</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE13">
         <v>75</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13">
         <v>19</v>
@@ -4010,7 +4010,7 @@
         <v>36</v>
       </c>
       <c r="AI13">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ13">
         <v>75</v>
@@ -4022,34 +4022,34 @@
         <v>130</v>
       </c>
       <c r="AM13">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AN13">
+        <v>100</v>
+      </c>
+      <c r="AO13">
         <v>110</v>
       </c>
-      <c r="AO13">
-        <v>120</v>
-      </c>
       <c r="AP13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ13">
+        <v>5.8</v>
+      </c>
+      <c r="AR13">
+        <v>16</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
         <v>5.7</v>
-      </c>
-      <c r="AR13">
-        <v>14</v>
-      </c>
-      <c r="AS13">
-        <v>1.01</v>
-      </c>
-      <c r="AT13">
-        <v>5.5</v>
       </c>
       <c r="AU13">
         <v>5.2</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -4058,10 +4058,10 @@
         <v>13</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13">
         <v>1.01</v>
@@ -4165,13 +4165,13 @@
         <v>179</v>
       </c>
       <c r="F14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
         <v>970</v>
@@ -4180,7 +4180,7 @@
         <v>1.1</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4192,13 +4192,13 @@
         <v>1.26</v>
       </c>
       <c r="O14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P14">
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="R14">
         <v>1.18</v>
@@ -4213,10 +4213,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4407,7 +4407,7 @@
         <v>180</v>
       </c>
       <c r="F15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
         <v>110</v>
@@ -4422,7 +4422,7 @@
         <v>1.1</v>
       </c>
       <c r="K15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4455,10 +4455,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4652,7 +4652,7 @@
         <v>2.3</v>
       </c>
       <c r="G16">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
         <v>3.15</v>
@@ -4682,7 +4682,7 @@
         <v>1.89</v>
       </c>
       <c r="Q16">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R16">
         <v>1.32</v>
@@ -4700,7 +4700,7 @@
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4891,22 +4891,22 @@
         <v>182</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K17">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4915,40 +4915,40 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q17">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T17">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="U17">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W17">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="X17">
         <v>19</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Z17">
         <v>32</v>
@@ -4960,19 +4960,19 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD17">
         <v>970</v>
       </c>
       <c r="AE17">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AF17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH17">
         <v>18</v>
@@ -4981,19 +4981,19 @@
         <v>55</v>
       </c>
       <c r="AJ17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM17">
         <v>110</v>
       </c>
       <c r="AN17">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO17">
         <v>48</v>
@@ -5002,7 +5002,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ17">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
         <v>1.01</v>
@@ -5014,7 +5014,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV17">
         <v>14.5</v>
@@ -5038,7 +5038,7 @@
         <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD17">
         <v>1.01</v>
@@ -5047,7 +5047,7 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG17">
         <v>1.01</v>
@@ -5139,7 +5139,7 @@
         <v>110</v>
       </c>
       <c r="H18">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="I18">
         <v>1.37</v>
@@ -5148,7 +5148,7 @@
         <v>4.9</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="L18">
         <v>1.3</v>
@@ -5160,13 +5160,13 @@
         <v>1.01</v>
       </c>
       <c r="O18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
         <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="R18">
         <v>1.3</v>
@@ -5181,10 +5181,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5313,7 +5313,7 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
@@ -5381,10 +5381,10 @@
         <v>2.24</v>
       </c>
       <c r="H19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J19">
         <v>3.05</v>
@@ -5396,34 +5396,34 @@
         <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O19">
         <v>1.54</v>
       </c>
       <c r="P19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T19">
         <v>1.96</v>
       </c>
       <c r="U19">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W19">
         <v>1.8</v>
@@ -5441,7 +5441,7 @@
         <v>140</v>
       </c>
       <c r="AB19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>7.4</v>
@@ -5480,7 +5480,7 @@
         <v>36</v>
       </c>
       <c r="AO19">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP19">
         <v>6.6</v>
@@ -5617,10 +5617,10 @@
         <v>185</v>
       </c>
       <c r="F20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H20">
         <v>2.66</v>
@@ -5632,7 +5632,7 @@
         <v>3.55</v>
       </c>
       <c r="K20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L20">
         <v>1.32</v>
@@ -5859,7 +5859,7 @@
         <v>186</v>
       </c>
       <c r="F21">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="G21">
         <v>3.05</v>
@@ -5868,13 +5868,13 @@
         <v>2.56</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J21">
         <v>3.35</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>270</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5883,7 +5883,7 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O21">
         <v>1.31</v>
@@ -5898,7 +5898,7 @@
         <v>1.27</v>
       </c>
       <c r="S21">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T21">
         <v>1.74</v>
@@ -5907,7 +5907,7 @@
         <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
         <v>1.49</v>
@@ -5925,7 +5925,7 @@
         <v>55</v>
       </c>
       <c r="AB21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC21">
         <v>9.4</v>
@@ -5940,7 +5940,7 @@
         <v>23</v>
       </c>
       <c r="AG21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH21">
         <v>18</v>
@@ -5949,7 +5949,7 @@
         <v>55</v>
       </c>
       <c r="AJ21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK21">
         <v>42</v>
@@ -6104,19 +6104,19 @@
         <v>3.25</v>
       </c>
       <c r="G22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="H22">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I22">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6128,7 +6128,7 @@
         <v>4</v>
       </c>
       <c r="O22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P22">
         <v>2.26</v>
@@ -6149,10 +6149,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="W22">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6346,19 +6346,19 @@
         <v>4.6</v>
       </c>
       <c r="G23">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I23">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="J23">
         <v>4.1</v>
       </c>
       <c r="K23">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6370,16 +6370,16 @@
         <v>5.1</v>
       </c>
       <c r="O23">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q23">
         <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S23">
         <v>2.42</v>
@@ -6388,16 +6388,16 @@
         <v>1.54</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="W23">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y23">
         <v>14.5</v>
@@ -6406,49 +6406,49 @@
         <v>15.5</v>
       </c>
       <c r="AA23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC23">
+        <v>12.5</v>
+      </c>
+      <c r="AD23">
         <v>13</v>
-      </c>
-      <c r="AD23">
-        <v>12.5</v>
       </c>
       <c r="AE23">
         <v>20</v>
       </c>
       <c r="AF23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI23">
         <v>34</v>
       </c>
       <c r="AJ23">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK23">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL23">
         <v>65</v>
       </c>
       <c r="AM23">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO23">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP23">
         <v>17.5</v>
@@ -6457,19 +6457,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU23">
         <v>7.8</v>
       </c>
       <c r="AV23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW23">
         <v>12</v>
@@ -6478,7 +6478,7 @@
         <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ23">
         <v>12.5</v>
@@ -6502,7 +6502,7 @@
         <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6585,7 +6585,7 @@
         <v>189</v>
       </c>
       <c r="F24">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G24">
         <v>4.9</v>
@@ -6594,13 +6594,13 @@
         <v>1.76</v>
       </c>
       <c r="I24">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="J24">
         <v>4.2</v>
       </c>
       <c r="K24">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6609,10 +6609,10 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="O24">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P24">
         <v>2.62</v>
@@ -6624,16 +6624,16 @@
         <v>1.65</v>
       </c>
       <c r="S24">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T24">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U24">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W24">
         <v>1.26</v>
@@ -6645,7 +6645,7 @@
         <v>15.5</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AA24">
         <v>23</v>
@@ -6684,7 +6684,7 @@
         <v>50</v>
       </c>
       <c r="AM24">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN24">
         <v>34</v>
@@ -6732,7 +6732,7 @@
         <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BD24">
         <v>1.01</v>
@@ -6827,22 +6827,22 @@
         <v>190</v>
       </c>
       <c r="F25">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="G25">
         <v>1.85</v>
       </c>
       <c r="H25">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I25">
-        <v>8.6</v>
+        <v>110</v>
       </c>
       <c r="J25">
         <v>2.92</v>
       </c>
       <c r="K25">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6863,7 +6863,7 @@
         <v>1.34</v>
       </c>
       <c r="R25">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="S25">
         <v>1.78</v>
@@ -6875,7 +6875,7 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="W25">
         <v>2.16</v>
@@ -7084,7 +7084,7 @@
         <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7231,61 +7231,61 @@
         <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
         <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
@@ -7311,22 +7311,22 @@
         <v>192</v>
       </c>
       <c r="F27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G27">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J27">
         <v>1.1</v>
       </c>
       <c r="K27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7359,10 +7359,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7553,16 +7553,16 @@
         <v>193</v>
       </c>
       <c r="F28">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H28">
         <v>2.02</v>
       </c>
       <c r="I28">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J28">
         <v>3.7</v>
@@ -7571,7 +7571,7 @@
         <v>4.1</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M28">
         <v>1.06</v>
@@ -7583,28 +7583,28 @@
         <v>1.27</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q28">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R28">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S28">
         <v>3</v>
       </c>
       <c r="T28">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U28">
         <v>2.26</v>
       </c>
       <c r="V28">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W28">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X28">
         <v>17.5</v>
@@ -7616,10 +7616,10 @@
         <v>14</v>
       </c>
       <c r="AA28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC28">
         <v>8.800000000000001</v>
@@ -7631,7 +7631,7 @@
         <v>21</v>
       </c>
       <c r="AF28">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AG28">
         <v>16</v>
@@ -7640,10 +7640,10 @@
         <v>17</v>
       </c>
       <c r="AI28">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ28">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK28">
         <v>55</v>
@@ -7658,7 +7658,7 @@
         <v>50</v>
       </c>
       <c r="AO28">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP28">
         <v>15</v>
@@ -7670,7 +7670,7 @@
         <v>12</v>
       </c>
       <c r="AS28">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AT28">
         <v>14</v>
@@ -7682,10 +7682,10 @@
         <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX28">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY28">
         <v>14</v>
@@ -7712,16 +7712,16 @@
         <v>23</v>
       </c>
       <c r="BG28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH28">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ28">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK28">
         <v>1.01</v>
@@ -7733,13 +7733,13 @@
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BO28">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BQ28">
         <v>1.01</v>
@@ -7751,25 +7751,25 @@
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU28">
         <v>4.4</v>
       </c>
       <c r="BV28">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BW28">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CA28">
         <v>1.01</v>
@@ -7798,10 +7798,10 @@
         <v>1.88</v>
       </c>
       <c r="G29">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I29">
         <v>4.2</v>
@@ -7810,7 +7810,7 @@
         <v>4.3</v>
       </c>
       <c r="K29">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7819,34 +7819,34 @@
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O29">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q29">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R29">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S29">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T29">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U29">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X29">
         <v>36</v>
@@ -7861,7 +7861,7 @@
         <v>85</v>
       </c>
       <c r="AB29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC29">
         <v>13</v>
@@ -7873,7 +7873,7 @@
         <v>46</v>
       </c>
       <c r="AF29">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7897,7 +7897,7 @@
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO29">
         <v>26</v>
@@ -7960,7 +7960,7 @@
         <v>6.6</v>
       </c>
       <c r="BI29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ29">
         <v>12.5</v>
@@ -7969,7 +7969,7 @@
         <v>5.4</v>
       </c>
       <c r="BL29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
@@ -8061,7 +8061,7 @@
         <v>1.03</v>
       </c>
       <c r="N30">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O30">
         <v>1.26</v>
@@ -8070,19 +8070,19 @@
         <v>2.16</v>
       </c>
       <c r="Q30">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="R30">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="S30">
         <v>2.22</v>
       </c>
       <c r="T30">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="U30">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V30">
         <v>1.32</v>
@@ -8291,7 +8291,7 @@
         <v>2.84</v>
       </c>
       <c r="J31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
         <v>3.7</v>
@@ -8312,7 +8312,7 @@
         <v>2.02</v>
       </c>
       <c r="Q31">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
         <v>1.38</v>
@@ -8521,82 +8521,82 @@
         <v>197</v>
       </c>
       <c r="F32">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G32">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I32">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="K32">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="L32">
         <v>1.2</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N32">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="O32">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P32">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="Q32">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="R32">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="S32">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="T32">
         <v>1.87</v>
       </c>
       <c r="U32">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="X32">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y32">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z32">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AA32">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="AB32">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC32">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD32">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE32">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AF32">
         <v>10</v>
@@ -8605,94 +8605,94 @@
         <v>12</v>
       </c>
       <c r="AH32">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI32">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ32">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK32">
         <v>13</v>
       </c>
       <c r="AL32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM32">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN32">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="AO32">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AP32">
         <v>30</v>
       </c>
       <c r="AQ32">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AR32">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AS32">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AT32">
         <v>11.5</v>
       </c>
       <c r="AU32">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AV32">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AW32">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY32">
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BA32">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BB32">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC32">
         <v>11.5</v>
       </c>
       <c r="BD32">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BE32">
+        <v>9</v>
+      </c>
+      <c r="BF32">
+        <v>3.25</v>
+      </c>
+      <c r="BG32">
+        <v>8.6</v>
+      </c>
+      <c r="BH32">
+        <v>5.8</v>
+      </c>
+      <c r="BI32">
+        <v>4</v>
+      </c>
+      <c r="BJ32">
         <v>13</v>
       </c>
-      <c r="BF32">
-        <v>2.98</v>
-      </c>
-      <c r="BG32">
-        <v>12.5</v>
-      </c>
-      <c r="BH32">
-        <v>6.2</v>
-      </c>
-      <c r="BI32">
-        <v>4.3</v>
-      </c>
-      <c r="BJ32">
-        <v>13.5</v>
-      </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL32">
         <v>130</v>
@@ -8707,31 +8707,31 @@
         <v>3.6</v>
       </c>
       <c r="BP32">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ32">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR32">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BW32">
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
@@ -8772,7 +8772,7 @@
         <v>3.25</v>
       </c>
       <c r="I33">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J33">
         <v>3.6</v>
@@ -8802,7 +8802,7 @@
         <v>1.45</v>
       </c>
       <c r="S33">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T33">
         <v>1.64</v>
@@ -9014,7 +9014,7 @@
         <v>4.1</v>
       </c>
       <c r="I34">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J34">
         <v>3.3</v>
@@ -9029,22 +9029,22 @@
         <v>1.06</v>
       </c>
       <c r="N34">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P34">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q34">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S34">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -9247,16 +9247,16 @@
         <v>200</v>
       </c>
       <c r="F35">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="G35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H35">
         <v>2.54</v>
       </c>
       <c r="I35">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -9268,34 +9268,34 @@
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>1.28</v>
       </c>
       <c r="P35">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.96</v>
+        <v>2.42</v>
       </c>
       <c r="T35">
         <v>1.64</v>
       </c>
       <c r="U35">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
         <v>1.48</v>
@@ -9328,7 +9328,7 @@
         <v>23</v>
       </c>
       <c r="AG35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH35">
         <v>16.5</v>
@@ -9349,7 +9349,7 @@
         <v>90</v>
       </c>
       <c r="AN35">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO35">
         <v>21</v>
@@ -9361,10 +9361,10 @@
         <v>10.5</v>
       </c>
       <c r="AR35">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -9373,10 +9373,10 @@
         <v>7.2</v>
       </c>
       <c r="AV35">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW35">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AX35">
         <v>18</v>
@@ -9388,19 +9388,19 @@
         <v>13.5</v>
       </c>
       <c r="BA35">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB35">
         <v>32</v>
       </c>
       <c r="BC35">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD35">
         <v>30</v>
       </c>
       <c r="BE35">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF35">
         <v>20</v>
@@ -9412,49 +9412,49 @@
         <v>4.3</v>
       </c>
       <c r="BI35">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ35">
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BL35">
         <v>120</v>
       </c>
       <c r="BM35">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN35">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP35">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ35">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS35">
+        <v>4.1</v>
+      </c>
+      <c r="BT35">
+        <v>6.6</v>
+      </c>
+      <c r="BU35">
         <v>4.2</v>
       </c>
-      <c r="BT35">
-        <v>6.8</v>
-      </c>
-      <c r="BU35">
-        <v>4.3</v>
-      </c>
       <c r="BV35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW35">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BX35">
         <v>36</v>
@@ -9498,7 +9498,7 @@
         <v>2.98</v>
       </c>
       <c r="I36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J36">
         <v>3.8</v>
@@ -9510,10 +9510,10 @@
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="O36">
         <v>1.23</v>
@@ -9528,13 +9528,13 @@
         <v>1.5</v>
       </c>
       <c r="S36">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="T36">
         <v>1.52</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V36">
         <v>1.43</v>
@@ -9758,22 +9758,22 @@
         <v>4.6</v>
       </c>
       <c r="O37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P37">
         <v>2.3</v>
       </c>
       <c r="Q37">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R37">
         <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U37">
         <v>2.3</v>
@@ -9830,7 +9830,7 @@
         <v>30</v>
       </c>
       <c r="AM37">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN37">
         <v>11.5</v>
@@ -9860,7 +9860,7 @@
         <v>14</v>
       </c>
       <c r="AW37">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AX37">
         <v>12.5</v>
@@ -9884,13 +9884,13 @@
         <v>26</v>
       </c>
       <c r="BE37">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF37">
         <v>10</v>
       </c>
       <c r="BG37">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9997,7 +9997,7 @@
         <v>1.07</v>
       </c>
       <c r="N38">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O38">
         <v>1.33</v>
@@ -10054,13 +10054,13 @@
         <v>15.5</v>
       </c>
       <c r="AG38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH38">
         <v>17.5</v>
       </c>
       <c r="AI38">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AJ38">
         <v>34</v>
@@ -10227,7 +10227,7 @@
         <v>5.3</v>
       </c>
       <c r="J39">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K39">
         <v>3.8</v>
@@ -10248,7 +10248,7 @@
         <v>1.83</v>
       </c>
       <c r="Q39">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R39">
         <v>1.31</v>
@@ -10272,7 +10272,7 @@
         <v>13</v>
       </c>
       <c r="Y39">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z39">
         <v>40</v>
@@ -10317,7 +10317,7 @@
         <v>1000</v>
       </c>
       <c r="AN39">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO39">
         <v>100</v>
@@ -10353,7 +10353,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ39">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA39">
         <v>55</v>
@@ -10371,7 +10371,7 @@
         <v>42</v>
       </c>
       <c r="BF39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG39">
         <v>70</v>
@@ -10481,7 +10481,7 @@
         <v>1.08</v>
       </c>
       <c r="N40">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O40">
         <v>1.36</v>
@@ -10493,7 +10493,7 @@
         <v>2.04</v>
       </c>
       <c r="R40">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S40">
         <v>3.7</v>
@@ -10517,25 +10517,25 @@
         <v>11.5</v>
       </c>
       <c r="Z40">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA40">
         <v>55</v>
       </c>
       <c r="AB40">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC40">
         <v>8.199999999999999</v>
       </c>
       <c r="AD40">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE40">
         <v>38</v>
       </c>
       <c r="AF40">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG40">
         <v>13.5</v>
@@ -10571,10 +10571,10 @@
         <v>10.5</v>
       </c>
       <c r="AR40">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS40">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT40">
         <v>8.800000000000001</v>
@@ -10598,10 +10598,10 @@
         <v>16.5</v>
       </c>
       <c r="BA40">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BB40">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC40">
         <v>24</v>
@@ -10610,7 +10610,7 @@
         <v>36</v>
       </c>
       <c r="BE40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF40">
         <v>18.5</v>
@@ -10625,7 +10625,7 @@
         <v>2.68</v>
       </c>
       <c r="BJ40">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK40">
         <v>1.01</v>
@@ -10640,7 +10640,7 @@
         <v>6.2</v>
       </c>
       <c r="BO40">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP40">
         <v>23</v>
@@ -10655,19 +10655,19 @@
         <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU40">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW40">
         <v>1.01</v>
       </c>
       <c r="BX40">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY40">
         <v>1.01</v>
@@ -10708,7 +10708,7 @@
         <v>7.2</v>
       </c>
       <c r="I41">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J41">
         <v>3.95</v>
@@ -10744,7 +10744,7 @@
         <v>1.89</v>
       </c>
       <c r="U41">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V41">
         <v>1.12</v>
@@ -10807,7 +10807,7 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
         <v>1.01</v>
@@ -10819,7 +10819,7 @@
         <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU41">
         <v>1.01</v>
@@ -10882,7 +10882,7 @@
         <v>5.3</v>
       </c>
       <c r="BO41">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BP41">
         <v>15</v>
@@ -10897,7 +10897,7 @@
         <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU41">
         <v>1.01</v>
@@ -10941,16 +10941,16 @@
         <v>207</v>
       </c>
       <c r="F42">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G42">
         <v>3</v>
       </c>
       <c r="H42">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I42">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J42">
         <v>3.65</v>
@@ -10962,10 +10962,10 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N42">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O42">
         <v>1.26</v>
@@ -10974,13 +10974,13 @@
         <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R42">
         <v>1.46</v>
       </c>
       <c r="S42">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T42">
         <v>1.66</v>
@@ -11016,7 +11016,7 @@
         <v>12</v>
       </c>
       <c r="AE42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF42">
         <v>22</v>
@@ -11025,13 +11025,13 @@
         <v>13.5</v>
       </c>
       <c r="AH42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI42">
         <v>36</v>
       </c>
       <c r="AJ42">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AK42">
         <v>32</v>
@@ -11049,7 +11049,7 @@
         <v>18</v>
       </c>
       <c r="AP42">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ42">
         <v>11.5</v>
@@ -11073,13 +11073,13 @@
         <v>22</v>
       </c>
       <c r="AX42">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY42">
         <v>11.5</v>
       </c>
       <c r="AZ42">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA42">
         <v>30</v>
@@ -11094,13 +11094,13 @@
         <v>32</v>
       </c>
       <c r="BE42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF42">
         <v>20</v>
       </c>
       <c r="BG42">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11183,7 +11183,7 @@
         <v>208</v>
       </c>
       <c r="F43">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G43">
         <v>2.2</v>
@@ -11192,7 +11192,7 @@
         <v>3.5</v>
       </c>
       <c r="I43">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J43">
         <v>3.75</v>
@@ -11207,19 +11207,19 @@
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O43">
         <v>1.27</v>
       </c>
       <c r="P43">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
         <v>1.79</v>
       </c>
       <c r="R43">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S43">
         <v>2.96</v>
@@ -11231,7 +11231,7 @@
         <v>2.18</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
         <v>1.83</v>
@@ -11267,13 +11267,13 @@
         <v>11.5</v>
       </c>
       <c r="AH43">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI43">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ43">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK43">
         <v>22</v>
@@ -11288,7 +11288,7 @@
         <v>14.5</v>
       </c>
       <c r="AO43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP43">
         <v>15</v>
@@ -11300,7 +11300,7 @@
         <v>23</v>
       </c>
       <c r="AS43">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AT43">
         <v>9.800000000000001</v>
@@ -11336,7 +11336,7 @@
         <v>29</v>
       </c>
       <c r="BE43">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF43">
         <v>12</v>
@@ -12068,7 +12068,7 @@
         <v>4.9</v>
       </c>
       <c r="BG46">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH46">
         <v>5</v>
@@ -12151,7 +12151,7 @@
         <v>212</v>
       </c>
       <c r="F47">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G47">
         <v>1.99</v>
@@ -12163,10 +12163,10 @@
         <v>5.7</v>
       </c>
       <c r="J47">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K47">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L47">
         <v>1.38</v>
@@ -12184,19 +12184,19 @@
         <v>1.64</v>
       </c>
       <c r="Q47">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R47">
         <v>1.22</v>
       </c>
       <c r="S47">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T47">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U47">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V47">
         <v>1.21</v>
@@ -12650,7 +12650,7 @@
         <v>4.1</v>
       </c>
       <c r="K49">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L49">
         <v>1.27</v>
@@ -12659,28 +12659,28 @@
         <v>1.05</v>
       </c>
       <c r="N49">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O49">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P49">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R49">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S49">
         <v>2.94</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V49">
         <v>1.17</v>
@@ -12701,7 +12701,7 @@
         <v>190</v>
       </c>
       <c r="AB49">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC49">
         <v>11.5</v>
@@ -12725,19 +12725,19 @@
         <v>90</v>
       </c>
       <c r="AJ49">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK49">
         <v>19.5</v>
       </c>
       <c r="AL49">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM49">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN49">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO49">
         <v>110</v>
@@ -12749,34 +12749,34 @@
         <v>16.5</v>
       </c>
       <c r="AR49">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS49">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT49">
         <v>8.199999999999999</v>
       </c>
       <c r="AU49">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV49">
         <v>17.5</v>
       </c>
       <c r="AW49">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX49">
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ49">
         <v>15.5</v>
       </c>
       <c r="BA49">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB49">
         <v>14</v>
@@ -12785,16 +12785,16 @@
         <v>13</v>
       </c>
       <c r="BD49">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE49">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF49">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG49">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12883,16 +12883,16 @@
         <v>1.3</v>
       </c>
       <c r="H50">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I50">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J50">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K50">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -12901,13 +12901,13 @@
         <v>1.04</v>
       </c>
       <c r="N50">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O50">
         <v>1.21</v>
       </c>
       <c r="P50">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q50">
         <v>1.53</v>
@@ -12916,7 +12916,7 @@
         <v>1.58</v>
       </c>
       <c r="S50">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T50">
         <v>2.18</v>
@@ -12934,7 +12934,7 @@
         <v>23</v>
       </c>
       <c r="Y50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Z50">
         <v>140</v>
@@ -12943,10 +12943,10 @@
         <v>750</v>
       </c>
       <c r="AB50">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC50">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD50">
         <v>48</v>
@@ -12979,7 +12979,7 @@
         <v>240</v>
       </c>
       <c r="AN50">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AO50">
         <v>440</v>
@@ -12991,7 +12991,7 @@
         <v>34</v>
       </c>
       <c r="AR50">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS50">
         <v>14</v>
@@ -13006,7 +13006,7 @@
         <v>40</v>
       </c>
       <c r="AW50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX50">
         <v>6.8</v>
@@ -13018,7 +13018,7 @@
         <v>30</v>
       </c>
       <c r="BA50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB50">
         <v>8.6</v>
@@ -13027,10 +13027,10 @@
         <v>13</v>
       </c>
       <c r="BD50">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF50">
         <v>4.4</v>
@@ -13119,7 +13119,7 @@
         <v>216</v>
       </c>
       <c r="F51">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G51">
         <v>1.65</v>
@@ -13128,13 +13128,13 @@
         <v>5.9</v>
       </c>
       <c r="I51">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J51">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K51">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13149,7 +13149,7 @@
         <v>1.21</v>
       </c>
       <c r="P51">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q51">
         <v>1.65</v>
@@ -13158,7 +13158,7 @@
         <v>1.43</v>
       </c>
       <c r="S51">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13167,7 +13167,7 @@
         <v>1.01</v>
       </c>
       <c r="V51">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W51">
         <v>2.52</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -667,7 +667,7 @@
     <t>Hartford Athletic FC</t>
   </si>
   <si>
-    <t>2026-09-01 02:23:02</t>
+    <t>2026-09-01 03:53:20</t>
   </si>
 </sst>
 </file>
@@ -1264,16 +1264,16 @@
         <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6.8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
         <v>4.4</v>
@@ -1291,13 +1291,13 @@
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
         <v>3.6</v>
@@ -1312,7 +1312,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1333,7 +1333,7 @@
         <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE2">
         <v>110</v>
@@ -1372,13 +1372,13 @@
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1387,10 +1387,10 @@
         <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX2">
         <v>7.4</v>
@@ -1399,10 +1399,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1411,10 +1411,10 @@
         <v>14</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
         <v>8.4</v>
@@ -1432,55 +1432,55 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>180</v>
       </c>
       <c r="BM2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>11</v>
       </c>
       <c r="BU2">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BZ2">
         <v>25</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="s">
         <v>217</v>
@@ -1503,19 +1503,19 @@
         <v>168</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="I3">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.4</v>
@@ -1527,19 +1527,19 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
         <v>4.2</v>
@@ -1551,19 +1551,19 @@
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3">
         <v>70</v>
@@ -1575,10 +1575,10 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF3">
         <v>21</v>
@@ -1596,7 +1596,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL3">
         <v>70</v>
@@ -1632,10 +1632,10 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX3">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1644,85 +1644,85 @@
         <v>16</v>
       </c>
       <c r="BA3">
+        <v>8</v>
+      </c>
+      <c r="BB3">
+        <v>38</v>
+      </c>
+      <c r="BC3">
+        <v>29</v>
+      </c>
+      <c r="BD3">
+        <v>8</v>
+      </c>
+      <c r="BE3">
+        <v>8.6</v>
+      </c>
+      <c r="BF3">
+        <v>24</v>
+      </c>
+      <c r="BG3">
+        <v>23</v>
+      </c>
+      <c r="BH3">
+        <v>3.5</v>
+      </c>
+      <c r="BI3">
+        <v>2.62</v>
+      </c>
+      <c r="BJ3">
+        <v>11.5</v>
+      </c>
+      <c r="BK3">
+        <v>3.95</v>
+      </c>
+      <c r="BL3">
+        <v>160</v>
+      </c>
+      <c r="BM3">
+        <v>5.9</v>
+      </c>
+      <c r="BN3">
+        <v>6.6</v>
+      </c>
+      <c r="BO3">
+        <v>4.6</v>
+      </c>
+      <c r="BP3">
+        <v>26</v>
+      </c>
+      <c r="BQ3">
+        <v>4.9</v>
+      </c>
+      <c r="BR3">
+        <v>44</v>
+      </c>
+      <c r="BS3">
+        <v>5.3</v>
+      </c>
+      <c r="BT3">
         <v>6.4</v>
       </c>
-      <c r="BB3">
-        <v>6.2</v>
-      </c>
-      <c r="BC3">
-        <v>6</v>
-      </c>
-      <c r="BD3">
-        <v>6.2</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
-      </c>
-      <c r="BF3">
-        <v>6</v>
-      </c>
-      <c r="BG3">
-        <v>6</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB3" t="s">
         <v>217</v>
@@ -1748,7 +1748,7 @@
         <v>1.54</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
         <v>6.2</v>
@@ -1760,43 +1760,43 @@
         <v>4.6</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
         <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X4">
         <v>28</v>
@@ -1811,7 +1811,7 @@
         <v>200</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
         <v>11</v>
@@ -1832,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ4">
         <v>15</v>
@@ -1841,13 +1841,13 @@
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AM4">
         <v>110</v>
       </c>
       <c r="AN4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO4">
         <v>80</v>
@@ -1862,7 +1862,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>9.4</v>
@@ -1874,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>9.4</v>
@@ -1898,22 +1898,22 @@
         <v>21</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
         <v>5.8</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>5</v>
       </c>
       <c r="BI4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK4">
         <v>7.4</v>
@@ -1925,13 +1925,13 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
         <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
         <v>5.9</v>
@@ -1961,7 +1961,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -2011,7 +2011,7 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
         <v>1.37</v>
@@ -2035,7 +2035,7 @@
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W5">
         <v>1.32</v>
@@ -2229,22 +2229,22 @@
         <v>171</v>
       </c>
       <c r="F6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G6">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J6">
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2259,25 +2259,25 @@
         <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
         <v>1.87</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W6">
         <v>1.37</v>
@@ -2298,7 +2298,7 @@
         <v>16</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
         <v>11.5</v>
@@ -2334,28 +2334,28 @@
         <v>42</v>
       </c>
       <c r="AO6">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP6">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6">
+        <v>9.4</v>
+      </c>
+      <c r="AR6">
         <v>12</v>
-      </c>
-      <c r="AQ6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR6">
-        <v>10.5</v>
       </c>
       <c r="AS6">
         <v>20</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW6">
         <v>18.5</v>
@@ -2367,25 +2367,25 @@
         <v>13</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB6">
+        <v>8</v>
+      </c>
+      <c r="BC6">
         <v>7.4</v>
       </c>
-      <c r="BC6">
-        <v>7</v>
-      </c>
       <c r="BD6">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG6">
         <v>12.5</v>
@@ -2501,10 +2501,10 @@
         <v>1.54</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q7">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
         <v>1.2</v>
@@ -2561,7 +2561,7 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK7">
         <v>85</v>
@@ -2576,7 +2576,7 @@
         <v>130</v>
       </c>
       <c r="AO7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP7">
         <v>7.6</v>
@@ -2588,7 +2588,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
@@ -2600,10 +2600,10 @@
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AX7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY7">
         <v>16</v>
@@ -2615,22 +2615,22 @@
         <v>28</v>
       </c>
       <c r="BB7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC7">
         <v>9</v>
       </c>
-      <c r="BC7">
-        <v>8.6</v>
-      </c>
       <c r="BD7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2639,7 +2639,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK7">
         <v>1.01</v>
@@ -2651,43 +2651,43 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2719,16 +2719,16 @@
         <v>4.4</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="I8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J8">
         <v>3.7</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2737,13 +2737,13 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O8">
         <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q8">
         <v>1.93</v>
@@ -2755,13 +2755,13 @@
         <v>3.35</v>
       </c>
       <c r="T8">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W8">
         <v>1.29</v>
@@ -2958,7 +2958,7 @@
         <v>2.2</v>
       </c>
       <c r="G9">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H9">
         <v>3.3</v>
@@ -2967,13 +2967,13 @@
         <v>3.85</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -2985,13 +2985,13 @@
         <v>1.3</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>1.89</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S9">
         <v>3.25</v>
@@ -3057,7 +3057,7 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -3072,7 +3072,7 @@
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="AT9">
         <v>9.4</v>
@@ -3099,13 +3099,13 @@
         <v>5.4</v>
       </c>
       <c r="BB9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC9">
         <v>4.8</v>
       </c>
       <c r="BD9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE9">
         <v>32</v>
@@ -3117,10 +3117,10 @@
         <v>5.3</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
@@ -3141,7 +3141,7 @@
         <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
@@ -3156,13 +3156,13 @@
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>46</v>
@@ -3171,7 +3171,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3203,7 +3203,7 @@
         <v>4.7</v>
       </c>
       <c r="H10">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I10">
         <v>2.02</v>
@@ -3212,10 +3212,10 @@
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
         <v>1.08</v>
@@ -3227,10 +3227,10 @@
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
         <v>1.33</v>
@@ -3239,7 +3239,7 @@
         <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U10">
         <v>2</v>
@@ -3302,7 +3302,7 @@
         <v>85</v>
       </c>
       <c r="AO10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP10">
         <v>11</v>
@@ -3323,7 +3323,7 @@
         <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW10">
         <v>17.5</v>
@@ -3338,13 +3338,13 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD10">
         <v>7</v>
@@ -3368,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL10">
         <v>170</v>
@@ -3380,10 +3380,10 @@
         <v>9</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
@@ -3395,10 +3395,10 @@
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU10">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
         <v>16.5</v>
@@ -3410,7 +3410,7 @@
         <v>36</v>
       </c>
       <c r="BY10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>32</v>
@@ -3487,7 +3487,7 @@
         <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
         <v>1.94</v>
@@ -3541,7 +3541,7 @@
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO11">
         <v>60</v>
@@ -3681,22 +3681,22 @@
         <v>177</v>
       </c>
       <c r="F12">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G12">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H12">
         <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J12">
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3747,13 +3747,13 @@
         <v>70</v>
       </c>
       <c r="AB12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>9.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE12">
         <v>55</v>
@@ -3765,7 +3765,7 @@
         <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI12">
         <v>75</v>
@@ -3789,7 +3789,7 @@
         <v>60</v>
       </c>
       <c r="AP12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12">
         <v>8.800000000000001</v>
@@ -3798,7 +3798,7 @@
         <v>18</v>
       </c>
       <c r="AS12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3810,7 +3810,7 @@
         <v>12</v>
       </c>
       <c r="AW12">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AX12">
         <v>14</v>
@@ -3819,28 +3819,28 @@
         <v>11</v>
       </c>
       <c r="AZ12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD12">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE12">
+        <v>6.8</v>
+      </c>
+      <c r="BF12">
         <v>6.2</v>
       </c>
-      <c r="BF12">
-        <v>5.8</v>
-      </c>
       <c r="BG12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3929,79 +3929,79 @@
         <v>3.25</v>
       </c>
       <c r="H13">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P13">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
         <v>1.12</v>
       </c>
       <c r="S13">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y13">
         <v>9.199999999999999</v>
       </c>
       <c r="Z13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE13">
         <v>75</v>
       </c>
       <c r="AF13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13">
         <v>19</v>
@@ -4010,7 +4010,7 @@
         <v>36</v>
       </c>
       <c r="AI13">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ13">
         <v>75</v>
@@ -4022,34 +4022,34 @@
         <v>130</v>
       </c>
       <c r="AM13">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AN13">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP13">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS13">
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU13">
         <v>5.2</v>
       </c>
       <c r="AV13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -4058,10 +4058,10 @@
         <v>13</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA13">
         <v>1.01</v>
@@ -4091,7 +4091,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BK13">
         <v>1.01</v>
@@ -4103,37 +4103,37 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW13">
         <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY13">
         <v>1.01</v>
@@ -4165,13 +4165,13 @@
         <v>179</v>
       </c>
       <c r="F14">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="G14">
         <v>970</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="I14">
         <v>970</v>
@@ -4180,7 +4180,7 @@
         <v>1.1</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4891,7 +4891,7 @@
         <v>182</v>
       </c>
       <c r="F17">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="G17">
         <v>2.02</v>
@@ -4900,13 +4900,13 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
         <v>3.75</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4921,7 +4921,7 @@
         <v>1.28</v>
       </c>
       <c r="P17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
         <v>1.83</v>
@@ -4930,7 +4930,7 @@
         <v>1.42</v>
       </c>
       <c r="S17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T17">
         <v>1.74</v>
@@ -4939,7 +4939,7 @@
         <v>2.18</v>
       </c>
       <c r="V17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
         <v>1.98</v>
@@ -4948,19 +4948,19 @@
         <v>19</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z17">
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17">
         <v>970</v>
@@ -5035,7 +5035,7 @@
         <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC17">
         <v>14.5</v>
@@ -5092,7 +5092,7 @@
         <v>10.5</v>
       </c>
       <c r="BU17">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV17">
         <v>46</v>
@@ -5133,136 +5133,136 @@
         <v>183</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="H18">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I18">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J18">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K18">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="L18">
         <v>1.3</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q18">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S18">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN18">
         <v>1000</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT18">
         <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX18">
         <v>1.01</v>
@@ -5292,7 +5292,7 @@
         <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5301,7 +5301,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5334,7 +5334,7 @@
         <v>4.8</v>
       </c>
       <c r="BU18">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BV18">
         <v>11</v>
@@ -5381,7 +5381,7 @@
         <v>2.24</v>
       </c>
       <c r="H19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19">
         <v>4.7</v>
@@ -5393,13 +5393,13 @@
         <v>3.2</v>
       </c>
       <c r="L19">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="M19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N19">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
         <v>1.54</v>
@@ -5408,7 +5408,7 @@
         <v>1.55</v>
       </c>
       <c r="Q19">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
         <v>1.2</v>
@@ -5474,7 +5474,7 @@
         <v>75</v>
       </c>
       <c r="AM19">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN19">
         <v>36</v>
@@ -5537,31 +5537,31 @@
         <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ19">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO19">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BP19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
@@ -5573,10 +5573,10 @@
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU19">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>65</v>
@@ -5641,16 +5641,16 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q20">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
         <v>1.3</v>
@@ -5859,22 +5859,22 @@
         <v>186</v>
       </c>
       <c r="F21">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G21">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H21">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I21">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J21">
         <v>3.35</v>
       </c>
       <c r="K21">
-        <v>270</v>
+        <v>4.3</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5883,7 +5883,7 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O21">
         <v>1.31</v>
@@ -5898,19 +5898,19 @@
         <v>1.27</v>
       </c>
       <c r="S21">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T21">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X21">
         <v>17</v>
@@ -6104,163 +6104,163 @@
         <v>3.25</v>
       </c>
       <c r="G22">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="H22">
         <v>2.12</v>
       </c>
       <c r="I22">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R22">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S22">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T22">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W22">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA22">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB22">
+        <v>18</v>
+      </c>
+      <c r="AC22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>12</v>
+      </c>
+      <c r="AE22">
+        <v>25</v>
+      </c>
+      <c r="AF22">
+        <v>28</v>
+      </c>
+      <c r="AG22">
+        <v>15.5</v>
+      </c>
+      <c r="AH22">
+        <v>16.5</v>
+      </c>
+      <c r="AI22">
+        <v>32</v>
+      </c>
+      <c r="AJ22">
+        <v>65</v>
+      </c>
+      <c r="AK22">
+        <v>36</v>
+      </c>
+      <c r="AL22">
+        <v>44</v>
+      </c>
+      <c r="AM22">
+        <v>75</v>
+      </c>
+      <c r="AN22">
+        <v>29</v>
+      </c>
+      <c r="AO22">
+        <v>14</v>
+      </c>
+      <c r="AP22">
+        <v>18</v>
+      </c>
+      <c r="AQ22">
+        <v>11</v>
+      </c>
+      <c r="AR22">
+        <v>13.5</v>
+      </c>
+      <c r="AS22">
+        <v>5.9</v>
+      </c>
+      <c r="AT22">
+        <v>14.5</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>9.6</v>
+      </c>
+      <c r="AW22">
+        <v>17.5</v>
+      </c>
+      <c r="AX22">
+        <v>5.9</v>
+      </c>
+      <c r="AY22">
+        <v>12.5</v>
+      </c>
+      <c r="AZ22">
+        <v>13</v>
+      </c>
+      <c r="BA22">
+        <v>6</v>
+      </c>
+      <c r="BB22">
+        <v>6.6</v>
+      </c>
+      <c r="BC22">
+        <v>6</v>
+      </c>
+      <c r="BD22">
+        <v>6.2</v>
+      </c>
+      <c r="BE22">
+        <v>6.8</v>
+      </c>
+      <c r="BF22">
         <v>21</v>
       </c>
-      <c r="AC22">
-        <v>11.5</v>
-      </c>
-      <c r="AD22">
-        <v>1000</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>18</v>
-      </c>
-      <c r="AH22">
-        <v>19</v>
-      </c>
-      <c r="AI22">
-        <v>36</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>40</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.59</v>
-      </c>
-      <c r="AQ22">
+      <c r="BG22">
         <v>10</v>
-      </c>
-      <c r="AR22">
-        <v>1.48</v>
-      </c>
-      <c r="AS22">
-        <v>1.52</v>
-      </c>
-      <c r="AT22">
-        <v>1.48</v>
-      </c>
-      <c r="AU22">
-        <v>7</v>
-      </c>
-      <c r="AV22">
-        <v>1.59</v>
-      </c>
-      <c r="AW22">
-        <v>1.59</v>
-      </c>
-      <c r="AX22">
-        <v>19</v>
-      </c>
-      <c r="AY22">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22">
-        <v>11</v>
-      </c>
-      <c r="BA22">
-        <v>1.53</v>
-      </c>
-      <c r="BB22">
-        <v>1.59</v>
-      </c>
-      <c r="BC22">
-        <v>1.53</v>
-      </c>
-      <c r="BD22">
-        <v>1.59</v>
-      </c>
-      <c r="BE22">
-        <v>1.59</v>
-      </c>
-      <c r="BF22">
-        <v>16.5</v>
-      </c>
-      <c r="BG22">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6343,13 +6343,13 @@
         <v>188</v>
       </c>
       <c r="F23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="H23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I23">
         <v>1.84</v>
@@ -6367,7 +6367,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>1.17</v>
@@ -6376,13 +6376,13 @@
         <v>2.4</v>
       </c>
       <c r="Q23">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R23">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S23">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T23">
         <v>1.54</v>
@@ -6394,7 +6394,7 @@
         <v>2.18</v>
       </c>
       <c r="W23">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
         <v>29</v>
@@ -6409,16 +6409,16 @@
         <v>23</v>
       </c>
       <c r="AB23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC23">
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF23">
         <v>50</v>
@@ -6442,16 +6442,16 @@
         <v>65</v>
       </c>
       <c r="AM23">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN23">
         <v>55</v>
       </c>
       <c r="AO23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ23">
         <v>8.800000000000001</v>
@@ -6463,10 +6463,10 @@
         <v>13.5</v>
       </c>
       <c r="AT23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
         <v>7.8</v>
@@ -6484,7 +6484,7 @@
         <v>12.5</v>
       </c>
       <c r="BA23">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB23">
         <v>1.01</v>
@@ -6502,7 +6502,7 @@
         <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6585,19 +6585,19 @@
         <v>189</v>
       </c>
       <c r="F24">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H24">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I24">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K24">
         <v>5.3</v>
@@ -6609,31 +6609,31 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q24">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R24">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S24">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="V24">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W24">
         <v>1.26</v>
@@ -6645,7 +6645,7 @@
         <v>15.5</v>
       </c>
       <c r="Z24">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AA24">
         <v>23</v>
@@ -6690,10 +6690,10 @@
         <v>34</v>
       </c>
       <c r="AO24">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP24">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
         <v>10</v>
@@ -6744,7 +6744,7 @@
         <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6830,20 +6830,20 @@
         <v>1.7</v>
       </c>
       <c r="G25">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>5.3</v>
+      </c>
+      <c r="J25">
+        <v>4.5</v>
+      </c>
+      <c r="K25">
         <v>4.8</v>
       </c>
-      <c r="I25">
-        <v>110</v>
-      </c>
-      <c r="J25">
-        <v>2.92</v>
-      </c>
-      <c r="K25">
-        <v>4.9</v>
-      </c>
       <c r="L25">
         <v>1.01</v>
       </c>
@@ -6851,142 +6851,142 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="O25">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P25">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q25">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R25">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S25">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
         <v>1.23</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7084,7 +7084,7 @@
         <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7093,28 +7093,28 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q26">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="R26">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S26">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V26">
         <v>1.34</v>
@@ -7123,64 +7123,64 @@
         <v>1.89</v>
       </c>
       <c r="X26">
+        <v>30</v>
+      </c>
+      <c r="Y26">
+        <v>28</v>
+      </c>
+      <c r="Z26">
         <v>34</v>
       </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>40</v>
-      </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB26">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE26">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF26">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH26">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI26">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ26">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN26">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP26">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
         <v>1.01</v>
@@ -7189,46 +7189,46 @@
         <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AU26">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW26">
         <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY26">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA26">
         <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD26">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BE26">
         <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7553,13 +7553,13 @@
         <v>193</v>
       </c>
       <c r="F28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I28">
         <v>2.1</v>
@@ -7568,10 +7568,10 @@
         <v>3.7</v>
       </c>
       <c r="K28">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L28">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M28">
         <v>1.06</v>
@@ -7586,7 +7586,7 @@
         <v>2.12</v>
       </c>
       <c r="Q28">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R28">
         <v>1.44</v>
@@ -7595,16 +7595,16 @@
         <v>3</v>
       </c>
       <c r="T28">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U28">
         <v>2.26</v>
       </c>
       <c r="V28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W28">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X28">
         <v>17.5</v>
@@ -7631,7 +7631,7 @@
         <v>21</v>
       </c>
       <c r="AF28">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG28">
         <v>16</v>
@@ -7658,7 +7658,7 @@
         <v>50</v>
       </c>
       <c r="AO28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP28">
         <v>15</v>
@@ -7685,7 +7685,7 @@
         <v>18</v>
       </c>
       <c r="AX28">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AY28">
         <v>14</v>
@@ -7715,10 +7715,10 @@
         <v>11</v>
       </c>
       <c r="BH28">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI28">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ28">
         <v>9.199999999999999</v>
@@ -7733,7 +7733,7 @@
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO28">
         <v>5.9</v>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
@@ -7804,7 +7804,7 @@
         <v>3.8</v>
       </c>
       <c r="I29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J29">
         <v>4.3</v>
@@ -7825,16 +7825,16 @@
         <v>1.16</v>
       </c>
       <c r="P29">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q29">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R29">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S29">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T29">
         <v>1.52</v>
@@ -7852,7 +7852,7 @@
         <v>36</v>
       </c>
       <c r="Y29">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z29">
         <v>40</v>
@@ -7864,7 +7864,7 @@
         <v>16</v>
       </c>
       <c r="AC29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD29">
         <v>21</v>
@@ -7873,7 +7873,7 @@
         <v>46</v>
       </c>
       <c r="AF29">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7897,7 +7897,7 @@
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO29">
         <v>26</v>
@@ -7951,7 +7951,7 @@
         <v>42</v>
       </c>
       <c r="BF29">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG29">
         <v>21</v>
@@ -8037,10 +8037,10 @@
         <v>195</v>
       </c>
       <c r="F30">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G30">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H30">
         <v>3.7</v>
@@ -8049,46 +8049,46 @@
         <v>4.1</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
         <v>4.7</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
         <v>1.26</v>
       </c>
       <c r="P30">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="R30">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S30">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="T30">
         <v>1.57</v>
       </c>
       <c r="U30">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X30">
         <v>20</v>
@@ -8205,10 +8205,10 @@
         <v>3.2</v>
       </c>
       <c r="BJ30">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL30">
         <v>110</v>
@@ -8217,31 +8217,31 @@
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BO30">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS30">
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BU30">
         <v>5.8</v>
       </c>
       <c r="BV30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
@@ -8282,7 +8282,7 @@
         <v>2.66</v>
       </c>
       <c r="G31">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H31">
         <v>2.66</v>
@@ -8303,28 +8303,28 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>1.29</v>
       </c>
       <c r="P31">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q31">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R31">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
         <v>3.2</v>
       </c>
       <c r="T31">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U31">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
         <v>1.54</v>
@@ -8396,7 +8396,7 @@
         <v>15.5</v>
       </c>
       <c r="AS31">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
@@ -8420,19 +8420,19 @@
         <v>13</v>
       </c>
       <c r="BA31">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB31">
         <v>32</v>
       </c>
       <c r="BC31">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD31">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF31">
         <v>19.5</v>
@@ -8441,7 +8441,7 @@
         <v>18.5</v>
       </c>
       <c r="BH31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI31">
         <v>2.96</v>
@@ -8524,40 +8524,40 @@
         <v>1.26</v>
       </c>
       <c r="G32">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="H32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J32">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K32">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P32">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R32">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="S32">
         <v>2.08</v>
@@ -8566,25 +8566,25 @@
         <v>1.87</v>
       </c>
       <c r="U32">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V32">
         <v>1.07</v>
       </c>
       <c r="W32">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="X32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y32">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Z32">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA32">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="AB32">
         <v>12.5</v>
@@ -8593,7 +8593,7 @@
         <v>16.5</v>
       </c>
       <c r="AD32">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AE32">
         <v>190</v>
@@ -8602,16 +8602,16 @@
         <v>10</v>
       </c>
       <c r="AG32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI32">
         <v>140</v>
       </c>
       <c r="AJ32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK32">
         <v>13</v>
@@ -8620,49 +8620,49 @@
         <v>32</v>
       </c>
       <c r="AM32">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AN32">
         <v>4.3</v>
       </c>
       <c r="AO32">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP32">
         <v>30</v>
       </c>
       <c r="AQ32">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS32">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT32">
         <v>11.5</v>
       </c>
       <c r="AU32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV32">
         <v>38</v>
       </c>
       <c r="AW32">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX32">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY32">
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB32">
         <v>9.4</v>
@@ -8671,28 +8671,28 @@
         <v>11.5</v>
       </c>
       <c r="BD32">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE32">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG32">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH32">
         <v>5.8</v>
       </c>
       <c r="BI32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ32">
         <v>13</v>
       </c>
       <c r="BK32">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL32">
         <v>130</v>
@@ -8707,19 +8707,19 @@
         <v>3.6</v>
       </c>
       <c r="BP32">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ32">
         <v>6</v>
       </c>
       <c r="BR32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
@@ -8731,7 +8731,7 @@
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
@@ -8775,7 +8775,7 @@
         <v>3.35</v>
       </c>
       <c r="J33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K33">
         <v>3.9</v>
@@ -8796,13 +8796,13 @@
         <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R33">
         <v>1.45</v>
       </c>
       <c r="S33">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T33">
         <v>1.64</v>
@@ -8829,10 +8829,10 @@
         <v>65</v>
       </c>
       <c r="AB33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC33">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD33">
         <v>15</v>
@@ -8841,7 +8841,7 @@
         <v>42</v>
       </c>
       <c r="AF33">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
@@ -8880,7 +8880,7 @@
         <v>21</v>
       </c>
       <c r="AS33">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT33">
         <v>10</v>
@@ -8892,7 +8892,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX33">
         <v>13.5</v>
@@ -8904,25 +8904,25 @@
         <v>14</v>
       </c>
       <c r="BA33">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BB33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC33">
         <v>19</v>
       </c>
       <c r="BD33">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE33">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF33">
         <v>12.5</v>
       </c>
       <c r="BG33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8967,7 +8967,7 @@
         <v>4.3</v>
       </c>
       <c r="BV33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
         <v>1.01</v>
@@ -9005,7 +9005,7 @@
         <v>199</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
         <v>2.16</v>
@@ -9014,22 +9014,22 @@
         <v>4.1</v>
       </c>
       <c r="I34">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J34">
         <v>3.3</v>
       </c>
       <c r="K34">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L34">
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O34">
         <v>1.37</v>
@@ -9038,7 +9038,7 @@
         <v>1.74</v>
       </c>
       <c r="Q34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R34">
         <v>1.28</v>
@@ -9047,16 +9047,16 @@
         <v>3.85</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V34">
         <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X34">
         <v>14</v>
@@ -9247,7 +9247,7 @@
         <v>200</v>
       </c>
       <c r="F35">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="G35">
         <v>3.15</v>
@@ -9256,7 +9256,7 @@
         <v>2.54</v>
       </c>
       <c r="I35">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -9265,40 +9265,40 @@
         <v>3.6</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M35">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O35">
         <v>1.28</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q35">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
         <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="T35">
         <v>1.64</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X35">
         <v>17.5</v>
@@ -9307,10 +9307,10 @@
         <v>13.5</v>
       </c>
       <c r="Z35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB35">
         <v>14.5</v>
@@ -9322,13 +9322,13 @@
         <v>12.5</v>
       </c>
       <c r="AE35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF35">
         <v>23</v>
       </c>
       <c r="AG35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH35">
         <v>16.5</v>
@@ -9349,112 +9349,112 @@
         <v>90</v>
       </c>
       <c r="AN35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO35">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP35">
         <v>14</v>
       </c>
       <c r="AQ35">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR35">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS35">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AT35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU35">
         <v>7.2</v>
       </c>
       <c r="AV35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW35">
         <v>21</v>
       </c>
       <c r="AX35">
+        <v>16</v>
+      </c>
+      <c r="AY35">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35">
+        <v>13</v>
+      </c>
+      <c r="BA35">
+        <v>25</v>
+      </c>
+      <c r="BB35">
+        <v>7.6</v>
+      </c>
+      <c r="BC35">
+        <v>22</v>
+      </c>
+      <c r="BD35">
+        <v>7.4</v>
+      </c>
+      <c r="BE35">
+        <v>8.4</v>
+      </c>
+      <c r="BF35">
         <v>18</v>
       </c>
-      <c r="AY35">
-        <v>10.5</v>
-      </c>
-      <c r="AZ35">
+      <c r="BG35">
         <v>13.5</v>
-      </c>
-      <c r="BA35">
-        <v>6.8</v>
-      </c>
-      <c r="BB35">
-        <v>32</v>
-      </c>
-      <c r="BC35">
-        <v>6.6</v>
-      </c>
-      <c r="BD35">
-        <v>30</v>
-      </c>
-      <c r="BE35">
-        <v>7.6</v>
-      </c>
-      <c r="BF35">
-        <v>20</v>
-      </c>
-      <c r="BG35">
-        <v>16</v>
       </c>
       <c r="BH35">
         <v>4.3</v>
       </c>
       <c r="BI35">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ35">
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BL35">
         <v>120</v>
       </c>
       <c r="BM35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO35">
         <v>4.7</v>
       </c>
       <c r="BP35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ35">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR35">
         <v>40</v>
       </c>
       <c r="BS35">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT35">
         <v>6.6</v>
       </c>
       <c r="BU35">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV35">
         <v>22</v>
       </c>
       <c r="BW35">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BX35">
         <v>36</v>
@@ -9513,7 +9513,7 @@
         <v>1.05</v>
       </c>
       <c r="N36">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O36">
         <v>1.23</v>
@@ -9528,10 +9528,10 @@
         <v>1.5</v>
       </c>
       <c r="S36">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="T36">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="U36">
         <v>2.32</v>
@@ -9558,7 +9558,7 @@
         <v>15</v>
       </c>
       <c r="AC36">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD36">
         <v>17</v>
@@ -9606,7 +9606,7 @@
         <v>20</v>
       </c>
       <c r="AS36">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT36">
         <v>10.5</v>
@@ -9618,7 +9618,7 @@
         <v>11.5</v>
       </c>
       <c r="AW36">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX36">
         <v>14</v>
@@ -9630,19 +9630,19 @@
         <v>13</v>
       </c>
       <c r="BA36">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB36">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC36">
         <v>19.5</v>
       </c>
       <c r="BD36">
+        <v>5.2</v>
+      </c>
+      <c r="BE36">
         <v>4.9</v>
-      </c>
-      <c r="BE36">
-        <v>5.4</v>
       </c>
       <c r="BF36">
         <v>12.5</v>
@@ -9746,10 +9746,10 @@
         <v>4.1</v>
       </c>
       <c r="K37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M37">
         <v>1.05</v>
@@ -9770,19 +9770,19 @@
         <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T37">
         <v>1.69</v>
       </c>
       <c r="U37">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
         <v>1.34</v>
       </c>
       <c r="W37">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X37">
         <v>19.5</v>
@@ -9884,7 +9884,7 @@
         <v>26</v>
       </c>
       <c r="BE37">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BF37">
         <v>10</v>
@@ -9973,7 +9973,7 @@
         <v>203</v>
       </c>
       <c r="F38">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G38">
         <v>2.42</v>
@@ -9985,10 +9985,10 @@
         <v>3.4</v>
       </c>
       <c r="J38">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K38">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9997,19 +9997,19 @@
         <v>1.07</v>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O38">
         <v>1.33</v>
       </c>
       <c r="P38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S38">
         <v>3.55</v>
@@ -10024,7 +10024,7 @@
         <v>1.41</v>
       </c>
       <c r="W38">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X38">
         <v>14.5</v>
@@ -10033,7 +10033,7 @@
         <v>13</v>
       </c>
       <c r="Z38">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA38">
         <v>60</v>
@@ -10054,16 +10054,16 @@
         <v>15.5</v>
       </c>
       <c r="AG38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH38">
         <v>17.5</v>
       </c>
       <c r="AI38">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AJ38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK38">
         <v>26</v>
@@ -10075,10 +10075,10 @@
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO38">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP38">
         <v>12.5</v>
@@ -10102,7 +10102,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AX38">
         <v>13.5</v>
@@ -10114,7 +10114,7 @@
         <v>15</v>
       </c>
       <c r="BA38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB38">
         <v>29</v>
@@ -10129,7 +10129,7 @@
         <v>36</v>
       </c>
       <c r="BF38">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG38">
         <v>30</v>
@@ -10150,7 +10150,7 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BN38">
         <v>7</v>
@@ -10159,7 +10159,7 @@
         <v>3.6</v>
       </c>
       <c r="BP38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ38">
         <v>1.01</v>
@@ -10183,13 +10183,13 @@
         <v>1.01</v>
       </c>
       <c r="BX38">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY38">
         <v>1.01</v>
       </c>
       <c r="BZ38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA38">
         <v>1.01</v>
@@ -10239,10 +10239,10 @@
         <v>1.08</v>
       </c>
       <c r="N39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O39">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P39">
         <v>1.83</v>
@@ -10251,7 +10251,7 @@
         <v>2.12</v>
       </c>
       <c r="R39">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S39">
         <v>3.95</v>
@@ -10278,7 +10278,7 @@
         <v>40</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB39">
         <v>7.8</v>
@@ -10287,7 +10287,7 @@
         <v>8.4</v>
       </c>
       <c r="AD39">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE39">
         <v>80</v>
@@ -10302,7 +10302,7 @@
         <v>22</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ39">
         <v>20</v>
@@ -10350,7 +10350,7 @@
         <v>9.4</v>
       </c>
       <c r="AY39">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39">
         <v>19</v>
@@ -10380,34 +10380,34 @@
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BJ39">
         <v>15.5</v>
       </c>
       <c r="BK39">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BN39">
         <v>6</v>
       </c>
       <c r="BO39">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BP39">
         <v>19</v>
       </c>
       <c r="BQ39">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BR39">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BS39">
         <v>1.71</v>
@@ -10422,19 +10422,19 @@
         <v>70</v>
       </c>
       <c r="BW39">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BX39">
         <v>90</v>
       </c>
       <c r="BY39">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BZ39">
         <v>40</v>
       </c>
       <c r="CA39">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CB39" t="s">
         <v>217</v>
@@ -10460,28 +10460,28 @@
         <v>2.48</v>
       </c>
       <c r="G40">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H40">
         <v>3.05</v>
       </c>
       <c r="I40">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J40">
         <v>3.5</v>
       </c>
       <c r="K40">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M40">
         <v>1.08</v>
       </c>
       <c r="N40">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O40">
         <v>1.36</v>
@@ -10517,7 +10517,7 @@
         <v>11.5</v>
       </c>
       <c r="Z40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA40">
         <v>55</v>
@@ -10529,7 +10529,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD40">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE40">
         <v>38</v>
@@ -10571,10 +10571,10 @@
         <v>10.5</v>
       </c>
       <c r="AR40">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS40">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT40">
         <v>8.800000000000001</v>
@@ -10601,7 +10601,7 @@
         <v>42</v>
       </c>
       <c r="BB40">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC40">
         <v>24</v>
@@ -10625,7 +10625,7 @@
         <v>2.68</v>
       </c>
       <c r="BJ40">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK40">
         <v>1.01</v>
@@ -10655,19 +10655,19 @@
         <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU40">
         <v>4.9</v>
       </c>
       <c r="BV40">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW40">
         <v>1.01</v>
       </c>
       <c r="BX40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY40">
         <v>1.01</v>
@@ -10699,154 +10699,154 @@
         <v>206</v>
       </c>
       <c r="F41">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="G41">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="H41">
         <v>7.2</v>
       </c>
       <c r="I41">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J41">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K41">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="L41">
         <v>1.33</v>
       </c>
       <c r="M41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N41">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P41">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q41">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R41">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S41">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T41">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="U41">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V41">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z41">
         <v>90</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB41">
+        <v>7.2</v>
+      </c>
+      <c r="AC41">
+        <v>11.5</v>
+      </c>
+      <c r="AD41">
+        <v>36</v>
+      </c>
+      <c r="AE41">
+        <v>190</v>
+      </c>
+      <c r="AF41">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG41">
+        <v>12.5</v>
+      </c>
+      <c r="AH41">
+        <v>29</v>
+      </c>
+      <c r="AI41">
+        <v>170</v>
+      </c>
+      <c r="AJ41">
+        <v>14.5</v>
+      </c>
+      <c r="AK41">
+        <v>22</v>
+      </c>
+      <c r="AL41">
+        <v>60</v>
+      </c>
+      <c r="AM41">
+        <v>240</v>
+      </c>
+      <c r="AN41">
+        <v>11.5</v>
+      </c>
+      <c r="AO41">
+        <v>300</v>
+      </c>
+      <c r="AP41">
+        <v>10</v>
+      </c>
+      <c r="AQ41">
+        <v>15.5</v>
+      </c>
+      <c r="AR41">
+        <v>1.01</v>
+      </c>
+      <c r="AS41">
+        <v>1.01</v>
+      </c>
+      <c r="AT41">
+        <v>5.9</v>
+      </c>
+      <c r="AU41">
+        <v>7.4</v>
+      </c>
+      <c r="AV41">
+        <v>1.01</v>
+      </c>
+      <c r="AW41">
+        <v>1.01</v>
+      </c>
+      <c r="AX41">
+        <v>7.2</v>
+      </c>
+      <c r="AY41">
         <v>8.6</v>
       </c>
-      <c r="AC41">
-        <v>1000</v>
-      </c>
-      <c r="AD41">
-        <v>40</v>
-      </c>
-      <c r="AE41">
-        <v>1000</v>
-      </c>
-      <c r="AF41">
-        <v>10.5</v>
-      </c>
-      <c r="AG41">
-        <v>1000</v>
-      </c>
-      <c r="AH41">
-        <v>36</v>
-      </c>
-      <c r="AI41">
-        <v>1000</v>
-      </c>
-      <c r="AJ41">
-        <v>18.5</v>
-      </c>
-      <c r="AK41">
-        <v>1000</v>
-      </c>
-      <c r="AL41">
-        <v>1000</v>
-      </c>
-      <c r="AM41">
-        <v>1000</v>
-      </c>
-      <c r="AN41">
-        <v>1000</v>
-      </c>
-      <c r="AO41">
-        <v>1000</v>
-      </c>
-      <c r="AP41">
-        <v>1.01</v>
-      </c>
-      <c r="AQ41">
-        <v>1.01</v>
-      </c>
-      <c r="AR41">
-        <v>1.01</v>
-      </c>
-      <c r="AS41">
-        <v>1.01</v>
-      </c>
-      <c r="AT41">
-        <v>5.1</v>
-      </c>
-      <c r="AU41">
-        <v>1.01</v>
-      </c>
-      <c r="AV41">
-        <v>1.01</v>
-      </c>
-      <c r="AW41">
-        <v>1.01</v>
-      </c>
-      <c r="AX41">
-        <v>5.9</v>
-      </c>
-      <c r="AY41">
-        <v>7.2</v>
-      </c>
       <c r="AZ41">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
         <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD41">
         <v>1.01</v>
@@ -10855,7 +10855,7 @@
         <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BG41">
         <v>1.01</v>
@@ -10882,16 +10882,16 @@
         <v>5.3</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BP41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ41">
         <v>1.01</v>
       </c>
       <c r="BR41">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS41">
         <v>1.01</v>
@@ -10915,7 +10915,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA41">
         <v>1.01</v>
@@ -10950,7 +10950,7 @@
         <v>2.54</v>
       </c>
       <c r="I42">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J42">
         <v>3.65</v>
@@ -10962,7 +10962,7 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N42">
         <v>4.5</v>
@@ -10971,7 +10971,7 @@
         <v>1.26</v>
       </c>
       <c r="P42">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q42">
         <v>1.79</v>
@@ -10980,13 +10980,13 @@
         <v>1.46</v>
       </c>
       <c r="S42">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V42">
         <v>1.64</v>
@@ -11073,13 +11073,13 @@
         <v>22</v>
       </c>
       <c r="AX42">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY42">
         <v>11.5</v>
       </c>
       <c r="AZ42">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA42">
         <v>30</v>
@@ -11183,22 +11183,22 @@
         <v>208</v>
       </c>
       <c r="F43">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G43">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H43">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I43">
         <v>3.65</v>
       </c>
       <c r="J43">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K43">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11219,31 +11219,31 @@
         <v>1.79</v>
       </c>
       <c r="R43">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S43">
         <v>2.96</v>
       </c>
       <c r="T43">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W43">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="X43">
         <v>17</v>
       </c>
       <c r="Y43">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z43">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA43">
         <v>70</v>
@@ -11252,31 +11252,31 @@
         <v>11.5</v>
       </c>
       <c r="AC43">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE43">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF43">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG43">
         <v>11.5</v>
       </c>
       <c r="AH43">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI43">
         <v>46</v>
       </c>
       <c r="AJ43">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL43">
         <v>34</v>
@@ -11297,10 +11297,10 @@
         <v>13</v>
       </c>
       <c r="AR43">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS43">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AT43">
         <v>9.800000000000001</v>
@@ -11309,10 +11309,10 @@
         <v>7.8</v>
       </c>
       <c r="AV43">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW43">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX43">
         <v>12.5</v>
@@ -11327,7 +11327,7 @@
         <v>38</v>
       </c>
       <c r="BB43">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC43">
         <v>19</v>
@@ -11336,7 +11336,7 @@
         <v>29</v>
       </c>
       <c r="BE43">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF43">
         <v>12</v>
@@ -12175,10 +12175,10 @@
         <v>1.09</v>
       </c>
       <c r="N47">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="O47">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P47">
         <v>1.64</v>
@@ -12187,16 +12187,16 @@
         <v>2.22</v>
       </c>
       <c r="R47">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S47">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T47">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U47">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V47">
         <v>1.21</v>
@@ -12650,7 +12650,7 @@
         <v>4.1</v>
       </c>
       <c r="K49">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L49">
         <v>1.27</v>
@@ -12662,19 +12662,19 @@
         <v>4.3</v>
       </c>
       <c r="O49">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P49">
         <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R49">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S49">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T49">
         <v>1.72</v>
@@ -12725,7 +12725,7 @@
         <v>90</v>
       </c>
       <c r="AJ49">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK49">
         <v>19.5</v>
@@ -12752,13 +12752,13 @@
         <v>5.4</v>
       </c>
       <c r="AS49">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT49">
         <v>8.199999999999999</v>
       </c>
       <c r="AU49">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV49">
         <v>17.5</v>
@@ -12770,13 +12770,13 @@
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ49">
         <v>15.5</v>
       </c>
       <c r="BA49">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB49">
         <v>14</v>
@@ -12788,13 +12788,13 @@
         <v>5.3</v>
       </c>
       <c r="BE49">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF49">
         <v>7.4</v>
       </c>
       <c r="BG49">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12886,7 +12886,7 @@
         <v>13</v>
       </c>
       <c r="I50">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J50">
         <v>6.4</v>
@@ -12901,13 +12901,13 @@
         <v>1.04</v>
       </c>
       <c r="N50">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>1.21</v>
       </c>
       <c r="P50">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q50">
         <v>1.53</v>
@@ -12916,13 +12916,13 @@
         <v>1.58</v>
       </c>
       <c r="S50">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T50">
         <v>2.18</v>
       </c>
       <c r="U50">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V50">
         <v>1.07</v>
@@ -12937,7 +12937,7 @@
         <v>44</v>
       </c>
       <c r="Z50">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AA50">
         <v>750</v>
@@ -12946,13 +12946,13 @@
         <v>9.4</v>
       </c>
       <c r="AC50">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD50">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AE50">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AF50">
         <v>8</v>
@@ -12973,7 +12973,7 @@
         <v>15</v>
       </c>
       <c r="AL50">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM50">
         <v>240</v>
@@ -12982,7 +12982,7 @@
         <v>4.7</v>
       </c>
       <c r="AO50">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AP50">
         <v>19.5</v>
@@ -12991,10 +12991,10 @@
         <v>34</v>
       </c>
       <c r="AR50">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS50">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT50">
         <v>8.199999999999999</v>
@@ -13018,7 +13018,7 @@
         <v>30</v>
       </c>
       <c r="BA50">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB50">
         <v>8.6</v>
@@ -13030,7 +13030,7 @@
         <v>34</v>
       </c>
       <c r="BE50">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF50">
         <v>4.4</v>
@@ -13119,7 +13119,7 @@
         <v>216</v>
       </c>
       <c r="F51">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G51">
         <v>1.65</v>
@@ -13128,43 +13128,43 @@
         <v>5.9</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J51">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K51">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L51">
         <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N51">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="O51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P51">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q51">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R51">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S51">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T51">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U51">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V51">
         <v>1.16</v>
@@ -13173,112 +13173,112 @@
         <v>2.52</v>
       </c>
       <c r="X51">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y51">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z51">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA51">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB51">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC51">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD51">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE51">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF51">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG51">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH51">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI51">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ51">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK51">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL51">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM51">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN51">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO51">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP51">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ51">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR51">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AS51">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="AT51">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU51">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV51">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW51">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AX51">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY51">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ51">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA51">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB51">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC51">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD51">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE51">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF51">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG51">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH51">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -667,7 +667,7 @@
     <t>Hartford Athletic FC</t>
   </si>
   <si>
-    <t>2026-09-01 03:53:20</t>
+    <t>2026-09-01 06:05:44</t>
   </si>
 </sst>
 </file>
@@ -1261,226 +1261,226 @@
         <v>167</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="G2">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
+        <v>1.34</v>
+      </c>
+      <c r="P2">
+        <v>1.89</v>
+      </c>
+      <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
         <v>1.33</v>
       </c>
-      <c r="P2">
-        <v>1.93</v>
-      </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>1.35</v>
-      </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AB2">
         <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP2">
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC2">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="BL2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CA2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>217</v>
@@ -1503,22 +1503,22 @@
         <v>168</v>
       </c>
       <c r="F3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G3">
         <v>3.1</v>
       </c>
       <c r="H3">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
         <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.46</v>
@@ -1530,19 +1530,19 @@
         <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q3">
         <v>2.2</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
         <v>1.86</v>
@@ -1551,16 +1551,16 @@
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X3">
         <v>13</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>21</v>
@@ -1575,16 +1575,16 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF3">
         <v>21</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
         <v>970</v>
@@ -1593,7 +1593,7 @@
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK3">
         <v>42</v>
@@ -1605,7 +1605,7 @@
         <v>130</v>
       </c>
       <c r="AN3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AO3">
         <v>50</v>
@@ -1617,7 +1617,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS3">
         <v>32</v>
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
@@ -1644,19 +1644,19 @@
         <v>16</v>
       </c>
       <c r="BA3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3">
         <v>29</v>
       </c>
       <c r="BD3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
         <v>24</v>
@@ -1671,10 +1671,10 @@
         <v>2.62</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>160</v>
@@ -1686,25 +1686,25 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV3">
         <v>25</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="BY3">
+        <v>5.4</v>
+      </c>
+      <c r="BZ3">
+        <v>40</v>
+      </c>
+      <c r="CA3">
         <v>5.3</v>
-      </c>
-      <c r="BZ3">
-        <v>38</v>
-      </c>
-      <c r="CA3">
-        <v>5.2</v>
       </c>
       <c r="CB3" t="s">
         <v>217</v>
@@ -1745,16 +1745,16 @@
         <v>169</v>
       </c>
       <c r="F4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G4">
         <v>1.59</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>4.6</v>
@@ -1763,13 +1763,13 @@
         <v>5.1</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
         <v>1.21</v>
@@ -1790,19 +1790,19 @@
         <v>1.76</v>
       </c>
       <c r="U4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
         <v>2.7</v>
       </c>
       <c r="X4">
+        <v>29</v>
+      </c>
+      <c r="Y4">
         <v>28</v>
-      </c>
-      <c r="Y4">
-        <v>27</v>
       </c>
       <c r="Z4">
         <v>60</v>
@@ -1820,7 +1820,7 @@
         <v>25</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AF4">
         <v>11</v>
@@ -1832,16 +1832,16 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
         <v>15</v>
       </c>
       <c r="AK4">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AL4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AM4">
         <v>110</v>
@@ -1853,28 +1853,28 @@
         <v>80</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>18.5</v>
       </c>
       <c r="AR4">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4">
+        <v>18.5</v>
+      </c>
+      <c r="AW4">
         <v>9.6</v>
-      </c>
-      <c r="AV4">
-        <v>18</v>
-      </c>
-      <c r="AW4">
-        <v>11</v>
       </c>
       <c r="AX4">
         <v>9.4</v>
@@ -1886,7 +1886,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1898,13 +1898,13 @@
         <v>21</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH4">
         <v>5</v>
@@ -1913,28 +1913,28 @@
         <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BP4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>26</v>
@@ -1946,7 +1946,7 @@
         <v>12</v>
       </c>
       <c r="BU4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>60</v>
@@ -1961,7 +1961,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1993,10 +1993,10 @@
         <v>4.1</v>
       </c>
       <c r="H5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J5">
         <v>3.45</v>
@@ -2005,13 +2005,13 @@
         <v>3.65</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.37</v>
@@ -2026,7 +2026,7 @@
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
         <v>1.86</v>
@@ -2035,7 +2035,7 @@
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W5">
         <v>1.32</v>
@@ -2065,13 +2065,13 @@
         <v>28</v>
       </c>
       <c r="AF5">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AG5">
         <v>17</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI5">
         <v>48</v>
@@ -2083,16 +2083,16 @@
         <v>65</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM5">
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -2104,7 +2104,7 @@
         <v>11</v>
       </c>
       <c r="AS5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -2119,7 +2119,7 @@
         <v>20</v>
       </c>
       <c r="AX5">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AY5">
         <v>14</v>
@@ -2128,82 +2128,82 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="BB5">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BC5">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD5">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
         <v>15.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -2232,13 +2232,13 @@
         <v>3.6</v>
       </c>
       <c r="G6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
         <v>3.7</v>
@@ -2247,7 +2247,7 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2271,19 +2271,19 @@
         <v>3.2</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
         <v>2.24</v>
       </c>
       <c r="V6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W6">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y6">
         <v>11</v>
@@ -2298,7 +2298,7 @@
         <v>16</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
         <v>11.5</v>
@@ -2316,13 +2316,13 @@
         <v>18</v>
       </c>
       <c r="AI6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL6">
         <v>60</v>
@@ -2334,7 +2334,7 @@
         <v>42</v>
       </c>
       <c r="AO6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="AW6">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AX6">
         <v>21</v>
@@ -2370,82 +2370,82 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BC6">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE6">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BG6">
         <v>12.5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2474,13 +2474,13 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J7">
         <v>3.2</v>
@@ -2489,10 +2489,10 @@
         <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
         <v>2.58</v>
@@ -2519,13 +2519,13 @@
         <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -2534,7 +2534,7 @@
         <v>12.5</v>
       </c>
       <c r="AA7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB7">
         <v>11.5</v>
@@ -2546,13 +2546,13 @@
         <v>12.5</v>
       </c>
       <c r="AE7">
+        <v>38</v>
+      </c>
+      <c r="AF7">
         <v>34</v>
       </c>
-      <c r="AF7">
-        <v>32</v>
-      </c>
       <c r="AG7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH7">
         <v>28</v>
@@ -2588,7 +2588,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT7">
         <v>9.6</v>
@@ -2600,10 +2600,10 @@
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
         <v>16</v>
@@ -2612,82 +2612,82 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BB7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BD7">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BK7">
         <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM7">
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BV7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2713,7 +2713,7 @@
         <v>173</v>
       </c>
       <c r="F8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G8">
         <v>4.4</v>
@@ -2731,7 +2731,7 @@
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2746,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
         <v>1.4</v>
@@ -2755,22 +2755,22 @@
         <v>3.35</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
         <v>2.14</v>
       </c>
       <c r="V8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W8">
         <v>1.29</v>
       </c>
       <c r="X8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z8">
         <v>12.5</v>
@@ -2779,7 +2779,7 @@
         <v>27</v>
       </c>
       <c r="AB8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC8">
         <v>8.4</v>
@@ -2791,25 +2791,25 @@
         <v>21</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH8">
         <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK8">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>120</v>
@@ -2818,10 +2818,10 @@
         <v>70</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8">
         <v>8.6</v>
@@ -2830,109 +2830,109 @@
         <v>11</v>
       </c>
       <c r="AS8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU8">
         <v>7.6</v>
       </c>
       <c r="AV8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX8">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8">
         <v>15</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BB8">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE8">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BG8">
         <v>11.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI8">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM8">
-        <v>1.81</v>
+        <v>4.7</v>
       </c>
       <c r="BN8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BP8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BQ8">
-        <v>1.75</v>
+        <v>4.4</v>
       </c>
       <c r="BR8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BS8">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BW8">
-        <v>1.67</v>
+        <v>3.8</v>
       </c>
       <c r="BX8">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>1.74</v>
+        <v>4.3</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="CA8">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="CB8" t="s">
         <v>217</v>
@@ -2955,16 +2955,16 @@
         <v>174</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G9">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -2979,7 +2979,7 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
         <v>1.3</v>
@@ -2994,7 +2994,7 @@
         <v>1.39</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
         <v>1.73</v>
@@ -3009,13 +3009,13 @@
         <v>1.74</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Y9">
         <v>17</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA9">
         <v>75</v>
@@ -3024,22 +3024,22 @@
         <v>13</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>48</v>
       </c>
       <c r="AF9">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG9">
         <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI9">
         <v>60</v>
@@ -3048,16 +3048,16 @@
         <v>36</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AM9">
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -3066,13 +3066,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS9">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="AT9">
         <v>9.4</v>
@@ -3084,7 +3084,7 @@
         <v>13</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="AX9">
         <v>13</v>
@@ -3093,28 +3093,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BB9">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BF9">
         <v>14.5</v>
       </c>
       <c r="BG9">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="BH9">
         <v>4.1</v>
@@ -3138,7 +3138,7 @@
         <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP9">
         <v>20</v>
@@ -3203,16 +3203,16 @@
         <v>4.7</v>
       </c>
       <c r="H10">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I10">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J10">
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
         <v>1.44</v>
@@ -3245,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W10">
         <v>1.27</v>
@@ -3263,7 +3263,7 @@
         <v>23</v>
       </c>
       <c r="AB10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AE10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF10">
         <v>40</v>
@@ -3326,7 +3326,7 @@
         <v>9.4</v>
       </c>
       <c r="AW10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX10">
         <v>24</v>
@@ -3335,16 +3335,16 @@
         <v>15</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB10">
+        <v>7.2</v>
+      </c>
+      <c r="BC10">
         <v>7</v>
-      </c>
-      <c r="BC10">
-        <v>6.8</v>
       </c>
       <c r="BD10">
         <v>7</v>
@@ -3368,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>170</v>
@@ -3398,7 +3398,7 @@
         <v>5.2</v>
       </c>
       <c r="BU10">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BV10">
         <v>16.5</v>
@@ -3457,7 +3457,7 @@
         <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3469,7 +3469,7 @@
         <v>1.3</v>
       </c>
       <c r="P11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q11">
         <v>1.83</v>
@@ -3520,7 +3520,7 @@
         <v>14</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3535,7 +3535,7 @@
         <v>22</v>
       </c>
       <c r="AL11">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -3556,16 +3556,16 @@
         <v>23</v>
       </c>
       <c r="AS11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT11">
         <v>8.800000000000001</v>
       </c>
       <c r="AU11">
+        <v>7.6</v>
+      </c>
+      <c r="AV11">
         <v>7.8</v>
-      </c>
-      <c r="AV11">
-        <v>5.9</v>
       </c>
       <c r="AW11">
         <v>40</v>
@@ -3583,7 +3583,7 @@
         <v>6.6</v>
       </c>
       <c r="BB11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC11">
         <v>17.5</v>
@@ -3592,7 +3592,7 @@
         <v>6.2</v>
       </c>
       <c r="BE11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
         <v>11.5</v>
@@ -3601,61 +3601,61 @@
         <v>6.6</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ11">
         <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3681,7 +3681,7 @@
         <v>177</v>
       </c>
       <c r="F12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G12">
         <v>2.66</v>
@@ -3690,37 +3690,37 @@
         <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M12">
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q12">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T12">
         <v>1.98</v>
@@ -3741,7 +3741,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA12">
         <v>70</v>
@@ -3759,13 +3759,13 @@
         <v>55</v>
       </c>
       <c r="AF12">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI12">
         <v>75</v>
@@ -3798,7 +3798,7 @@
         <v>18</v>
       </c>
       <c r="AS12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3810,7 +3810,7 @@
         <v>12</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AX12">
         <v>14</v>
@@ -3819,85 +3819,85 @@
         <v>11</v>
       </c>
       <c r="AZ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BA12">
+        <v>6.8</v>
+      </c>
+      <c r="BB12">
+        <v>6.8</v>
+      </c>
+      <c r="BC12">
+        <v>6.6</v>
+      </c>
+      <c r="BD12">
+        <v>6.8</v>
+      </c>
+      <c r="BE12">
+        <v>7.2</v>
+      </c>
+      <c r="BF12">
+        <v>6.6</v>
+      </c>
+      <c r="BG12">
+        <v>7.6</v>
+      </c>
+      <c r="BH12">
+        <v>3.35</v>
+      </c>
+      <c r="BI12">
+        <v>2.38</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>200</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
         <v>6.4</v>
       </c>
-      <c r="BB12">
-        <v>6.2</v>
-      </c>
-      <c r="BC12">
-        <v>6.2</v>
-      </c>
-      <c r="BD12">
-        <v>6.4</v>
-      </c>
-      <c r="BE12">
-        <v>6.8</v>
-      </c>
-      <c r="BF12">
-        <v>6.2</v>
-      </c>
-      <c r="BG12">
-        <v>6.4</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12">
-        <v>15</v>
-      </c>
-      <c r="BK12">
-        <v>1.01</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
+      <c r="BO12">
+        <v>4.1</v>
+      </c>
+      <c r="BP12">
+        <v>27</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>50</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
         <v>7.4</v>
       </c>
-      <c r="BO12">
-        <v>3.85</v>
-      </c>
-      <c r="BP12">
-        <v>29</v>
-      </c>
-      <c r="BQ12">
-        <v>1.01</v>
-      </c>
-      <c r="BR12">
+      <c r="BU12">
+        <v>4.6</v>
+      </c>
+      <c r="BV12">
+        <v>34</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
         <v>55</v>
       </c>
-      <c r="BS12">
-        <v>1.01</v>
-      </c>
-      <c r="BT12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU12">
-        <v>4.4</v>
-      </c>
-      <c r="BV12">
-        <v>42</v>
-      </c>
-      <c r="BW12">
-        <v>1.01</v>
-      </c>
-      <c r="BX12">
-        <v>70</v>
-      </c>
       <c r="BY12">
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA12">
         <v>1.01</v>
@@ -3926,7 +3926,7 @@
         <v>2.9</v>
       </c>
       <c r="G13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H13">
         <v>3.05</v>
@@ -3941,37 +3941,37 @@
         <v>3.1</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="M13">
         <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O13">
         <v>1.75</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
       </c>
       <c r="R13">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S13">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="T13">
         <v>2.42</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.45</v>
@@ -4049,7 +4049,7 @@
         <v>5.2</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -4058,7 +4058,7 @@
         <v>13</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13">
         <v>21</v>
@@ -4085,61 +4085,61 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BJ13">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK13">
         <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BO13">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP13">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
+        <v>80</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>7.2</v>
+      </c>
+      <c r="BU13">
+        <v>4.5</v>
+      </c>
+      <c r="BV13">
+        <v>42</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>85</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
         <v>95</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>8.6</v>
-      </c>
-      <c r="BU13">
-        <v>3.85</v>
-      </c>
-      <c r="BV13">
-        <v>50</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>100</v>
-      </c>
-      <c r="BY13">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
       </c>
       <c r="CA13">
         <v>1.01</v>
@@ -4165,19 +4165,19 @@
         <v>179</v>
       </c>
       <c r="F14">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G14">
         <v>970</v>
       </c>
       <c r="H14">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="I14">
         <v>970</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -4186,19 +4186,19 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>4.8</v>
       </c>
       <c r="O14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R14">
         <v>1.18</v>
@@ -4213,10 +4213,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4413,7 +4413,7 @@
         <v>110</v>
       </c>
       <c r="H15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I15">
         <v>970</v>
@@ -4455,10 +4455,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4649,19 +4649,19 @@
         <v>181</v>
       </c>
       <c r="F16">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G16">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H16">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
         <v>3.7</v>
@@ -4682,7 +4682,7 @@
         <v>1.89</v>
       </c>
       <c r="Q16">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
         <v>1.32</v>
@@ -4697,10 +4697,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4894,7 +4894,7 @@
         <v>1.99</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -4906,10 +4906,10 @@
         <v>3.75</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
         <v>1.06</v>
@@ -4942,49 +4942,49 @@
         <v>1.3</v>
       </c>
       <c r="W17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA17">
         <v>110</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AC17">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD17">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE17">
+        <v>60</v>
+      </c>
+      <c r="AF17">
+        <v>15.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
         <v>65</v>
       </c>
-      <c r="AF17">
-        <v>13</v>
-      </c>
-      <c r="AG17">
-        <v>10.5</v>
-      </c>
-      <c r="AH17">
-        <v>18</v>
-      </c>
-      <c r="AI17">
-        <v>55</v>
-      </c>
       <c r="AJ17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AK17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL17">
         <v>34</v>
@@ -4993,124 +4993,124 @@
         <v>110</v>
       </c>
       <c r="AN17">
+        <v>15</v>
+      </c>
+      <c r="AO17">
+        <v>60</v>
+      </c>
+      <c r="AP17">
+        <v>12</v>
+      </c>
+      <c r="AQ17">
         <v>12.5</v>
       </c>
-      <c r="AO17">
-        <v>48</v>
-      </c>
-      <c r="AP17">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17">
-        <v>14.5</v>
-      </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB17">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BC17">
         <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF17">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH17">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI17">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="BJ17">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN17">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO17">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT17">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BU17">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV17">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX17">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ17">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB17" t="s">
         <v>217</v>
@@ -5136,13 +5136,13 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H18">
         <v>1.31</v>
       </c>
       <c r="I18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J18">
         <v>5.1</v>
@@ -5169,7 +5169,7 @@
         <v>1.89</v>
       </c>
       <c r="R18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S18">
         <v>3.25</v>
@@ -5193,7 +5193,7 @@
         <v>7.2</v>
       </c>
       <c r="Z18">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AA18">
         <v>10.5</v>
@@ -5208,58 +5208,58 @@
         <v>13.5</v>
       </c>
       <c r="AE18">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF18">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AG18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AH18">
         <v>42</v>
       </c>
       <c r="AI18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
       </c>
       <c r="AK18">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="AL18">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AM18">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AN18">
         <v>1000</v>
       </c>
       <c r="AO18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AP18">
         <v>12</v>
       </c>
       <c r="AQ18">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AR18">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS18">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT18">
         <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AV18">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW18">
         <v>12</v>
@@ -5268,7 +5268,7 @@
         <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AZ18">
         <v>1.01</v>
@@ -5301,7 +5301,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5313,7 +5313,7 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
@@ -5331,25 +5331,25 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5405,22 +5405,22 @@
         <v>1.54</v>
       </c>
       <c r="P19">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
       </c>
       <c r="R19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T19">
         <v>1.96</v>
       </c>
       <c r="U19">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
         <v>1.27</v>
@@ -5432,13 +5432,13 @@
         <v>10.5</v>
       </c>
       <c r="Y19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z19">
         <v>40</v>
       </c>
       <c r="AA19">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -5450,7 +5450,7 @@
         <v>22</v>
       </c>
       <c r="AE19">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF19">
         <v>12</v>
@@ -5462,7 +5462,7 @@
         <v>30</v>
       </c>
       <c r="AI19">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ19">
         <v>36</v>
@@ -5474,16 +5474,16 @@
         <v>75</v>
       </c>
       <c r="AM19">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN19">
         <v>36</v>
       </c>
       <c r="AO19">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP19">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19">
         <v>10</v>
@@ -5513,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA19">
         <v>1.01</v>
@@ -5543,7 +5543,7 @@
         <v>2.22</v>
       </c>
       <c r="BJ19">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BK19">
         <v>1.01</v>
@@ -5555,43 +5555,43 @@
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO19">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV19">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
@@ -5617,13 +5617,13 @@
         <v>185</v>
       </c>
       <c r="F20">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G20">
         <v>2.76</v>
       </c>
       <c r="H20">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I20">
         <v>3.15</v>
@@ -5632,13 +5632,13 @@
         <v>3.55</v>
       </c>
       <c r="K20">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>1.32</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
         <v>3.5</v>
@@ -5647,115 +5647,115 @@
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q20">
         <v>1.96</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
         <v>1.56</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS20">
         <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW20">
         <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA20">
         <v>1.01</v>
@@ -5773,7 +5773,7 @@
         <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG20">
         <v>1.01</v>
@@ -5859,22 +5859,22 @@
         <v>186</v>
       </c>
       <c r="F21">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G21">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H21">
         <v>2.62</v>
       </c>
       <c r="I21">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5883,34 +5883,34 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O21">
         <v>1.31</v>
       </c>
       <c r="P21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q21">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S21">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X21">
         <v>17</v>
@@ -5919,7 +5919,7 @@
         <v>14</v>
       </c>
       <c r="Z21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA21">
         <v>55</v>
@@ -5934,7 +5934,7 @@
         <v>15.5</v>
       </c>
       <c r="AE21">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF21">
         <v>23</v>
@@ -5943,16 +5943,16 @@
         <v>15</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI21">
         <v>55</v>
       </c>
       <c r="AJ21">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK21">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL21">
         <v>55</v>
@@ -5961,40 +5961,40 @@
         <v>110</v>
       </c>
       <c r="AN21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO21">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AP21">
         <v>10</v>
       </c>
       <c r="AQ21">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS21">
         <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV21">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
         <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY21">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
         <v>12.5</v>
@@ -6015,10 +6015,10 @@
         <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH21">
         <v>4</v>
@@ -6104,13 +6104,13 @@
         <v>3.25</v>
       </c>
       <c r="G22">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H22">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I22">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J22">
         <v>3.7</v>
@@ -6119,7 +6119,7 @@
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M22">
         <v>1.04</v>
@@ -6137,13 +6137,13 @@
         <v>1.64</v>
       </c>
       <c r="R22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S22">
         <v>2.56</v>
       </c>
       <c r="T22">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U22">
         <v>2.38</v>
@@ -6152,49 +6152,49 @@
         <v>1.76</v>
       </c>
       <c r="W22">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X22">
         <v>25</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z22">
+        <v>19</v>
+      </c>
+      <c r="AA22">
+        <v>32</v>
+      </c>
+      <c r="AB22">
+        <v>20</v>
+      </c>
+      <c r="AC22">
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <v>13</v>
+      </c>
+      <c r="AE22">
+        <v>24</v>
+      </c>
+      <c r="AF22">
+        <v>32</v>
+      </c>
+      <c r="AG22">
         <v>17</v>
       </c>
-      <c r="AA22">
-        <v>29</v>
-      </c>
-      <c r="AB22">
+      <c r="AH22">
         <v>18</v>
       </c>
-      <c r="AC22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD22">
-        <v>12</v>
-      </c>
-      <c r="AE22">
-        <v>25</v>
-      </c>
-      <c r="AF22">
-        <v>28</v>
-      </c>
-      <c r="AG22">
-        <v>15.5</v>
-      </c>
-      <c r="AH22">
-        <v>16.5</v>
-      </c>
       <c r="AI22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ22">
         <v>65</v>
       </c>
       <c r="AK22">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL22">
         <v>44</v>
@@ -6212,16 +6212,16 @@
         <v>18</v>
       </c>
       <c r="AQ22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS22">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="AT22">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -6230,94 +6230,94 @@
         <v>9.6</v>
       </c>
       <c r="AW22">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX22">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="AY22">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA22">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BB22">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BC22">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BD22">
+        <v>4.6</v>
+      </c>
+      <c r="BE22">
+        <v>22</v>
+      </c>
+      <c r="BF22">
+        <v>19</v>
+      </c>
+      <c r="BG22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH22">
+        <v>4.7</v>
+      </c>
+      <c r="BI22">
+        <v>3.6</v>
+      </c>
+      <c r="BJ22">
+        <v>10</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>95</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>8</v>
+      </c>
+      <c r="BO22">
+        <v>5.4</v>
+      </c>
+      <c r="BP22">
+        <v>28</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>36</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
         <v>6.2</v>
       </c>
-      <c r="BE22">
-        <v>6.8</v>
-      </c>
-      <c r="BF22">
-        <v>21</v>
-      </c>
-      <c r="BG22">
-        <v>10</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.01</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.01</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.01</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.01</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.01</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
@@ -6346,28 +6346,28 @@
         <v>4.5</v>
       </c>
       <c r="G23">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H23">
         <v>1.69</v>
       </c>
       <c r="I23">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>5.4</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="O23">
         <v>1.17</v>
@@ -6376,25 +6376,25 @@
         <v>2.4</v>
       </c>
       <c r="Q23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R23">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S23">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="T23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X23">
         <v>29</v>
@@ -6457,7 +6457,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS23">
         <v>13.5</v>
@@ -6478,7 +6478,7 @@
         <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ23">
         <v>12.5</v>
@@ -6505,61 +6505,61 @@
         <v>5.9</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO23">
         <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
@@ -6585,7 +6585,7 @@
         <v>189</v>
       </c>
       <c r="F24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G24">
         <v>4.8</v>
@@ -6606,7 +6606,7 @@
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
         <v>5.8</v>
@@ -6642,19 +6642,19 @@
         <v>32</v>
       </c>
       <c r="Y24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA24">
         <v>23</v>
       </c>
       <c r="AB24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD24">
         <v>12.5</v>
@@ -6663,13 +6663,13 @@
         <v>19.5</v>
       </c>
       <c r="AF24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG24">
         <v>22</v>
       </c>
       <c r="AH24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24">
         <v>30</v>
@@ -6687,19 +6687,19 @@
         <v>70</v>
       </c>
       <c r="AN24">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO24">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS24">
         <v>15</v>
@@ -6711,13 +6711,13 @@
         <v>9.6</v>
       </c>
       <c r="AV24">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AW24">
         <v>12.5</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY24">
         <v>14</v>
@@ -6726,25 +6726,25 @@
         <v>12.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC24">
+        <v>36</v>
+      </c>
+      <c r="BD24">
         <v>34</v>
       </c>
-      <c r="BD24">
-        <v>1.01</v>
-      </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG24">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6830,28 +6830,28 @@
         <v>1.7</v>
       </c>
       <c r="G25">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I25">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K25">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>1.12</v>
@@ -6863,28 +6863,28 @@
         <v>1.37</v>
       </c>
       <c r="R25">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S25">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T25">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="V25">
         <v>1.23</v>
       </c>
       <c r="W25">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X25">
         <v>40</v>
       </c>
       <c r="Y25">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z25">
         <v>55</v>
@@ -6893,7 +6893,7 @@
         <v>120</v>
       </c>
       <c r="AB25">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AC25">
         <v>15.5</v>
@@ -6902,7 +6902,7 @@
         <v>23</v>
       </c>
       <c r="AE25">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF25">
         <v>17</v>
@@ -6917,7 +6917,7 @@
         <v>42</v>
       </c>
       <c r="AJ25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK25">
         <v>15.5</v>
@@ -6929,7 +6929,7 @@
         <v>44</v>
       </c>
       <c r="AN25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO25">
         <v>29</v>
@@ -6938,13 +6938,13 @@
         <v>30</v>
       </c>
       <c r="AQ25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR25">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="AS25">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT25">
         <v>16</v>
@@ -6953,40 +6953,40 @@
         <v>11</v>
       </c>
       <c r="AV25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW25">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25">
         <v>13</v>
       </c>
       <c r="BA25">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BB25">
         <v>17</v>
       </c>
       <c r="BC25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD25">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BE25">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25">
         <v>4.6</v>
       </c>
       <c r="BG25">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7069,7 +7069,7 @@
         <v>191</v>
       </c>
       <c r="F26">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>2.12</v>
@@ -7078,7 +7078,7 @@
         <v>3.5</v>
       </c>
       <c r="I26">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J26">
         <v>3.9</v>
@@ -7093,22 +7093,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P26">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q26">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S26">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="T26">
         <v>1.42</v>
@@ -7117,25 +7117,25 @@
         <v>2.42</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
         <v>1.89</v>
       </c>
       <c r="X26">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y26">
         <v>28</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA26">
         <v>75</v>
       </c>
       <c r="AB26">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AC26">
         <v>12.5</v>
@@ -7144,22 +7144,22 @@
         <v>20</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF26">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG26">
         <v>14</v>
       </c>
       <c r="AH26">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AI26">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ26">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK26">
         <v>23</v>
@@ -7171,61 +7171,61 @@
         <v>60</v>
       </c>
       <c r="AN26">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO26">
         <v>25</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ26">
         <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT26">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
         <v>12</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX26">
         <v>12.5</v>
       </c>
       <c r="AY26">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ26">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB26">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC26">
         <v>13.5</v>
       </c>
       <c r="BD26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG26">
         <v>15</v>
@@ -7359,10 +7359,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7562,7 +7562,7 @@
         <v>2.08</v>
       </c>
       <c r="I28">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J28">
         <v>3.7</v>
@@ -7721,7 +7721,7 @@
         <v>3.35</v>
       </c>
       <c r="BJ28">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK28">
         <v>1.01</v>
@@ -7733,10 +7733,10 @@
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BO28">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP28">
         <v>36</v>
@@ -7751,13 +7751,13 @@
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BU28">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BV28">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW28">
         <v>1.01</v>
@@ -7795,22 +7795,22 @@
         <v>194</v>
       </c>
       <c r="F29">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="G29">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H29">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I29">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J29">
         <v>4.3</v>
       </c>
       <c r="K29">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7822,19 +7822,19 @@
         <v>6.2</v>
       </c>
       <c r="O29">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q29">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S29">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="T29">
         <v>1.52</v>
@@ -7843,10 +7843,10 @@
         <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X29">
         <v>36</v>
@@ -7855,10 +7855,10 @@
         <v>25</v>
       </c>
       <c r="Z29">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA29">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB29">
         <v>16</v>
@@ -7870,10 +7870,10 @@
         <v>21</v>
       </c>
       <c r="AE29">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7882,10 +7882,10 @@
         <v>17</v>
       </c>
       <c r="AI29">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ29">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK29">
         <v>18.5</v>
@@ -7897,121 +7897,121 @@
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO29">
         <v>26</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ29">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT29">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AU29">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX29">
         <v>11</v>
       </c>
       <c r="AY29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ29">
         <v>11.5</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB29">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE29">
         <v>42</v>
       </c>
       <c r="BF29">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG29">
         <v>21</v>
       </c>
       <c r="BH29">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
         <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
         <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
         <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
         <v>1.01</v>
@@ -8040,7 +8040,7 @@
         <v>1.93</v>
       </c>
       <c r="G30">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>3.7</v>
@@ -8049,7 +8049,7 @@
         <v>4.1</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K30">
         <v>4.7</v>
@@ -8070,10 +8070,10 @@
         <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R30">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S30">
         <v>2.8</v>
@@ -8088,7 +8088,7 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="X30">
         <v>20</v>
@@ -8097,43 +8097,43 @@
         <v>18</v>
       </c>
       <c r="Z30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA30">
         <v>80</v>
       </c>
       <c r="AB30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC30">
         <v>9.6</v>
       </c>
       <c r="AD30">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE30">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF30">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG30">
         <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI30">
         <v>55</v>
       </c>
       <c r="AJ30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL30">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM30">
         <v>85</v>
@@ -8142,7 +8142,7 @@
         <v>13</v>
       </c>
       <c r="AO30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP30">
         <v>15</v>
@@ -8151,25 +8151,25 @@
         <v>13.5</v>
       </c>
       <c r="AR30">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AS30">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT30">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU30">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV30">
         <v>12.5</v>
       </c>
       <c r="AW30">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY30">
         <v>9.199999999999999</v>
@@ -8178,7 +8178,7 @@
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB30">
         <v>20</v>
@@ -8187,16 +8187,16 @@
         <v>16.5</v>
       </c>
       <c r="BD30">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE30">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF30">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG30">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH30">
         <v>4.4</v>
@@ -8205,7 +8205,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ30">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BK30">
         <v>7</v>
@@ -8217,37 +8217,37 @@
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP30">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BQ30">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS30">
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU30">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV30">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY30">
         <v>1.01</v>
@@ -8279,13 +8279,13 @@
         <v>196</v>
       </c>
       <c r="F31">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G31">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H31">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I31">
         <v>2.84</v>
@@ -8294,16 +8294,16 @@
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M31">
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O31">
         <v>1.29</v>
@@ -8312,10 +8312,10 @@
         <v>2.04</v>
       </c>
       <c r="Q31">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S31">
         <v>3.2</v>
@@ -8330,7 +8330,7 @@
         <v>1.54</v>
       </c>
       <c r="W31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X31">
         <v>19</v>
@@ -8363,7 +8363,7 @@
         <v>13</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
         <v>40</v>
@@ -8396,7 +8396,7 @@
         <v>15.5</v>
       </c>
       <c r="AS31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
@@ -8405,7 +8405,7 @@
         <v>7.4</v>
       </c>
       <c r="AV31">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AW31">
         <v>21</v>
@@ -8533,37 +8533,37 @@
         <v>15.5</v>
       </c>
       <c r="J32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R32">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T32">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U32">
         <v>1.99</v>
@@ -8575,7 +8575,7 @@
         <v>4.4</v>
       </c>
       <c r="X32">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y32">
         <v>60</v>
@@ -8593,7 +8593,7 @@
         <v>16.5</v>
       </c>
       <c r="AD32">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE32">
         <v>190</v>
@@ -8605,7 +8605,7 @@
         <v>11.5</v>
       </c>
       <c r="AH32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI32">
         <v>140</v>
@@ -8623,7 +8623,7 @@
         <v>170</v>
       </c>
       <c r="AN32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO32">
         <v>190</v>
@@ -8632,13 +8632,13 @@
         <v>30</v>
       </c>
       <c r="AQ32">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR32">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS32">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT32">
         <v>11.5</v>
@@ -8647,10 +8647,10 @@
         <v>14</v>
       </c>
       <c r="AV32">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW32">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX32">
         <v>8.4</v>
@@ -8662,7 +8662,7 @@
         <v>24</v>
       </c>
       <c r="BA32">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB32">
         <v>9.4</v>
@@ -8674,13 +8674,13 @@
         <v>26</v>
       </c>
       <c r="BE32">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF32">
         <v>3.3</v>
       </c>
       <c r="BG32">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH32">
         <v>5.8</v>
@@ -8689,10 +8689,10 @@
         <v>4.1</v>
       </c>
       <c r="BJ32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK32">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>130</v>
@@ -8701,16 +8701,16 @@
         <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BO32">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP32">
         <v>8</v>
       </c>
       <c r="BQ32">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR32">
         <v>22</v>
@@ -8719,7 +8719,7 @@
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
@@ -8820,10 +8820,10 @@
         <v>19.5</v>
       </c>
       <c r="Y33">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z33">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA33">
         <v>65</v>
@@ -8856,7 +8856,7 @@
         <v>34</v>
       </c>
       <c r="AK33">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL33">
         <v>38</v>
@@ -8868,19 +8868,19 @@
         <v>15</v>
       </c>
       <c r="AO33">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AP33">
         <v>16</v>
       </c>
       <c r="AQ33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR33">
         <v>21</v>
       </c>
       <c r="AS33">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AT33">
         <v>10</v>
@@ -8892,37 +8892,37 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AX33">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY33">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ33">
         <v>14</v>
       </c>
       <c r="BA33">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BB33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC33">
         <v>19</v>
       </c>
       <c r="BD33">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE33">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF33">
         <v>12.5</v>
       </c>
       <c r="BG33">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8931,7 +8931,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ33">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
         <v>1.01</v>
@@ -8943,28 +8943,28 @@
         <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
         <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
         <v>1000</v>
@@ -8973,13 +8973,13 @@
         <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
         <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
         <v>1.01</v>
@@ -9005,7 +9005,7 @@
         <v>199</v>
       </c>
       <c r="F34">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G34">
         <v>2.16</v>
@@ -9017,13 +9017,13 @@
         <v>4.6</v>
       </c>
       <c r="J34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M34">
         <v>1.08</v>
@@ -9035,10 +9035,10 @@
         <v>1.37</v>
       </c>
       <c r="P34">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q34">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R34">
         <v>1.28</v>
@@ -9047,7 +9047,7 @@
         <v>3.85</v>
       </c>
       <c r="T34">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U34">
         <v>1.92</v>
@@ -9056,7 +9056,7 @@
         <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X34">
         <v>14</v>
@@ -9071,10 +9071,10 @@
         <v>110</v>
       </c>
       <c r="AB34">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD34">
         <v>21</v>
@@ -9083,7 +9083,7 @@
         <v>70</v>
       </c>
       <c r="AF34">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG34">
         <v>12.5</v>
@@ -9107,46 +9107,46 @@
         <v>140</v>
       </c>
       <c r="AN34">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO34">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP34">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR34">
         <v>4.7</v>
       </c>
       <c r="AS34">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT34">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU34">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV34">
         <v>13.5</v>
       </c>
       <c r="AW34">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX34">
         <v>9.4</v>
       </c>
       <c r="AY34">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
         <v>15</v>
       </c>
       <c r="BA34">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB34">
         <v>19.5</v>
@@ -9155,73 +9155,73 @@
         <v>18.5</v>
       </c>
       <c r="BD34">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE34">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF34">
         <v>14</v>
       </c>
       <c r="BG34">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK34">
         <v>1.01</v>
       </c>
       <c r="BL34">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM34">
         <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ34">
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW34">
         <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY34">
         <v>1.01</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA34">
         <v>1.01</v>
@@ -9247,25 +9247,25 @@
         <v>200</v>
       </c>
       <c r="F35">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G35">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H35">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I35">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L35">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M35">
         <v>1.06</v>
@@ -9286,16 +9286,16 @@
         <v>1.4</v>
       </c>
       <c r="S35">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T35">
         <v>1.64</v>
       </c>
       <c r="U35">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
         <v>1.47</v>
@@ -9331,7 +9331,7 @@
         <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI35">
         <v>38</v>
@@ -9361,13 +9361,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR35">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="AT35">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU35">
         <v>7.2</v>
@@ -9379,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="AX35">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY35">
         <v>9.6</v>
@@ -9388,25 +9388,25 @@
         <v>13</v>
       </c>
       <c r="BA35">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="BB35">
+        <v>7.8</v>
+      </c>
+      <c r="BC35">
+        <v>7.2</v>
+      </c>
+      <c r="BD35">
         <v>7.6</v>
-      </c>
-      <c r="BC35">
-        <v>22</v>
-      </c>
-      <c r="BD35">
-        <v>7.4</v>
       </c>
       <c r="BE35">
         <v>8.4</v>
       </c>
       <c r="BF35">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG35">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH35">
         <v>4.3</v>
@@ -9489,13 +9489,13 @@
         <v>201</v>
       </c>
       <c r="F36">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G36">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H36">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I36">
         <v>3.3</v>
@@ -9504,7 +9504,7 @@
         <v>3.8</v>
       </c>
       <c r="K36">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9528,19 +9528,19 @@
         <v>1.5</v>
       </c>
       <c r="S36">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="T36">
         <v>1.62</v>
       </c>
       <c r="U36">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V36">
         <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X36">
         <v>23</v>
@@ -9564,7 +9564,7 @@
         <v>17</v>
       </c>
       <c r="AE36">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF36">
         <v>17.5</v>
@@ -9576,16 +9576,16 @@
         <v>16.5</v>
       </c>
       <c r="AI36">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK36">
         <v>28</v>
       </c>
       <c r="AL36">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM36">
         <v>85</v>
@@ -9603,7 +9603,7 @@
         <v>12.5</v>
       </c>
       <c r="AR36">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="AS36">
         <v>4.9</v>
@@ -9639,7 +9639,7 @@
         <v>19.5</v>
       </c>
       <c r="BD36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE36">
         <v>4.9</v>
@@ -9657,7 +9657,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ36">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
         <v>1.01</v>
@@ -9669,43 +9669,43 @@
         <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP36">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
         <v>1.01</v>
       </c>
       <c r="BR36">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
         <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV36">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
         <v>1.01</v>
       </c>
       <c r="BX36">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY36">
         <v>1.01</v>
       </c>
       <c r="BZ36">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
         <v>1.01</v>
@@ -9731,31 +9731,31 @@
         <v>202</v>
       </c>
       <c r="F37">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H37">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I37">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J37">
         <v>4.1</v>
       </c>
       <c r="K37">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L37">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M37">
         <v>1.05</v>
       </c>
       <c r="N37">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O37">
         <v>1.24</v>
@@ -9767,7 +9767,7 @@
         <v>1.72</v>
       </c>
       <c r="R37">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S37">
         <v>2.86</v>
@@ -9776,13 +9776,13 @@
         <v>1.69</v>
       </c>
       <c r="U37">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
         <v>1.34</v>
       </c>
       <c r="W37">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X37">
         <v>19.5</v>
@@ -9836,7 +9836,7 @@
         <v>11.5</v>
       </c>
       <c r="AO37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP37">
         <v>17.5</v>
@@ -9848,10 +9848,10 @@
         <v>26</v>
       </c>
       <c r="AS37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU37">
         <v>8.6</v>
@@ -9893,61 +9893,61 @@
         <v>30</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK37">
         <v>1.01</v>
       </c>
       <c r="BL37">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM37">
         <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO37">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ37">
         <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS37">
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU37">
         <v>1.01</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW37">
         <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY37">
         <v>1.01</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA37">
         <v>1.01</v>
@@ -9973,16 +9973,16 @@
         <v>203</v>
       </c>
       <c r="F38">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G38">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H38">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J38">
         <v>3.5</v>
@@ -9991,7 +9991,7 @@
         <v>3.6</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M38">
         <v>1.07</v>
@@ -10003,10 +10003,10 @@
         <v>1.33</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q38">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R38">
         <v>1.37</v>
@@ -10018,13 +10018,13 @@
         <v>1.78</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X38">
         <v>14.5</v>
@@ -10036,7 +10036,7 @@
         <v>24</v>
       </c>
       <c r="AA38">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB38">
         <v>10.5</v>
@@ -10048,10 +10048,10 @@
         <v>14.5</v>
       </c>
       <c r="AE38">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF38">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG38">
         <v>11.5</v>
@@ -10069,16 +10069,16 @@
         <v>26</v>
       </c>
       <c r="AL38">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM38">
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO38">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP38">
         <v>12.5</v>
@@ -10102,7 +10102,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX38">
         <v>13.5</v>
@@ -10117,7 +10117,7 @@
         <v>42</v>
       </c>
       <c r="BB38">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC38">
         <v>22</v>
@@ -10135,64 +10135,64 @@
         <v>30</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK38">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL38">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM38">
         <v>28</v>
       </c>
       <c r="BN38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BO38">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP38">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BQ38">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR38">
+        <v>36</v>
+      </c>
+      <c r="BS38">
+        <v>4.9</v>
+      </c>
+      <c r="BT38">
+        <v>7.4</v>
+      </c>
+      <c r="BU38">
+        <v>5.1</v>
+      </c>
+      <c r="BV38">
+        <v>30</v>
+      </c>
+      <c r="BW38">
+        <v>4.8</v>
+      </c>
+      <c r="BX38">
         <v>44</v>
       </c>
-      <c r="BS38">
-        <v>1.01</v>
-      </c>
-      <c r="BT38">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU38">
-        <v>4.5</v>
-      </c>
-      <c r="BV38">
-        <v>36</v>
-      </c>
-      <c r="BW38">
-        <v>1.01</v>
-      </c>
-      <c r="BX38">
-        <v>48</v>
-      </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BZ38">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB38" t="s">
         <v>217</v>
@@ -10224,16 +10224,16 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J39">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K39">
         <v>3.8</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M39">
         <v>1.08</v>
@@ -10245,13 +10245,13 @@
         <v>1.37</v>
       </c>
       <c r="P39">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q39">
         <v>2.12</v>
       </c>
       <c r="R39">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S39">
         <v>3.95</v>
@@ -10275,7 +10275,7 @@
         <v>16</v>
       </c>
       <c r="Z39">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA39">
         <v>140</v>
@@ -10326,7 +10326,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ39">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR39">
         <v>34</v>
@@ -10377,64 +10377,64 @@
         <v>70</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI39">
-        <v>1.78</v>
+        <v>1.21</v>
       </c>
       <c r="BJ39">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BN39">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="BO39">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="BP39">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BR39">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV39">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="BX39">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="BZ39">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="s">
         <v>217</v>
@@ -10457,7 +10457,7 @@
         <v>205</v>
       </c>
       <c r="F40">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G40">
         <v>2.52</v>
@@ -10475,40 +10475,40 @@
         <v>3.65</v>
       </c>
       <c r="L40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M40">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N40">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P40">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q40">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R40">
         <v>1.32</v>
       </c>
       <c r="S40">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T40">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U40">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V40">
         <v>1.46</v>
       </c>
       <c r="W40">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X40">
         <v>13.5</v>
@@ -10523,7 +10523,7 @@
         <v>55</v>
       </c>
       <c r="AB40">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC40">
         <v>8.199999999999999</v>
@@ -10604,16 +10604,16 @@
         <v>32</v>
       </c>
       <c r="BC40">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD40">
         <v>36</v>
       </c>
       <c r="BE40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF40">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG40">
         <v>25</v>
@@ -10628,7 +10628,7 @@
         <v>11</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL40">
         <v>150</v>
@@ -10637,10 +10637,10 @@
         <v>1.01</v>
       </c>
       <c r="BN40">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP40">
         <v>23</v>
@@ -10655,10 +10655,10 @@
         <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU40">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV40">
         <v>29</v>
@@ -10699,22 +10699,22 @@
         <v>206</v>
       </c>
       <c r="F41">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H41">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I41">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J41">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="L41">
         <v>1.33</v>
@@ -10723,7 +10723,7 @@
         <v>1.07</v>
       </c>
       <c r="N41">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O41">
         <v>1.34</v>
@@ -10735,10 +10735,10 @@
         <v>2.04</v>
       </c>
       <c r="R41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S41">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T41">
         <v>2.16</v>
@@ -10750,46 +10750,46 @@
         <v>1.11</v>
       </c>
       <c r="W41">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X41">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y41">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z41">
         <v>90</v>
       </c>
       <c r="AA41">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="AB41">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC41">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD41">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AE41">
         <v>190</v>
       </c>
       <c r="AF41">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG41">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH41">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI41">
         <v>170</v>
       </c>
       <c r="AJ41">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AK41">
         <v>22</v>
@@ -10801,16 +10801,16 @@
         <v>240</v>
       </c>
       <c r="AN41">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO41">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AP41">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ41">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR41">
         <v>1.01</v>
@@ -10822,7 +10822,7 @@
         <v>5.9</v>
       </c>
       <c r="AU41">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV41">
         <v>1.01</v>
@@ -10831,31 +10831,31 @@
         <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY41">
         <v>8.6</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA41">
         <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC41">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE41">
         <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG41">
         <v>1.01</v>
@@ -10867,7 +10867,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK41">
         <v>1.01</v>
@@ -10879,25 +10879,25 @@
         <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO41">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BP41">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
         <v>1.01</v>
       </c>
       <c r="BR41">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS41">
         <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU41">
         <v>1.01</v>
@@ -10915,7 +10915,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA41">
         <v>1.01</v>
@@ -10941,28 +10941,28 @@
         <v>207</v>
       </c>
       <c r="F42">
+        <v>2.92</v>
+      </c>
+      <c r="G42">
         <v>2.96</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
       </c>
       <c r="H42">
         <v>2.54</v>
       </c>
       <c r="I42">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J42">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L42">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N42">
         <v>4.5</v>
@@ -10974,25 +10974,25 @@
         <v>2.2</v>
       </c>
       <c r="Q42">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R42">
         <v>1.46</v>
       </c>
       <c r="S42">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T42">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U42">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V42">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X42">
         <v>17.5</v>
@@ -11004,7 +11004,7 @@
         <v>18.5</v>
       </c>
       <c r="AA42">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB42">
         <v>14.5</v>
@@ -11064,7 +11064,7 @@
         <v>13</v>
       </c>
       <c r="AU42">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV42">
         <v>10.5</v>
@@ -11103,64 +11103,64 @@
         <v>15.5</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL42">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP42">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB42" t="s">
         <v>217</v>
@@ -11192,7 +11192,7 @@
         <v>3.3</v>
       </c>
       <c r="I43">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J43">
         <v>3.65</v>
@@ -11201,28 +11201,28 @@
         <v>3.85</v>
       </c>
       <c r="L43">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M43">
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O43">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q43">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="R43">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S43">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T43">
         <v>1.65</v>
@@ -11246,13 +11246,13 @@
         <v>30</v>
       </c>
       <c r="AA43">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB43">
         <v>11.5</v>
       </c>
       <c r="AC43">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD43">
         <v>16.5</v>
@@ -11261,7 +11261,7 @@
         <v>40</v>
       </c>
       <c r="AF43">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG43">
         <v>11.5</v>
@@ -11279,19 +11279,19 @@
         <v>23</v>
       </c>
       <c r="AL43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM43">
         <v>85</v>
       </c>
       <c r="AN43">
+        <v>15</v>
+      </c>
+      <c r="AO43">
+        <v>40</v>
+      </c>
+      <c r="AP43">
         <v>14.5</v>
-      </c>
-      <c r="AO43">
-        <v>36</v>
-      </c>
-      <c r="AP43">
-        <v>15</v>
       </c>
       <c r="AQ43">
         <v>13</v>
@@ -11300,13 +11300,13 @@
         <v>22</v>
       </c>
       <c r="AS43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT43">
         <v>9.800000000000001</v>
       </c>
       <c r="AU43">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV43">
         <v>12.5</v>
@@ -11315,7 +11315,7 @@
         <v>32</v>
       </c>
       <c r="AX43">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY43">
         <v>9.6</v>
@@ -11336,70 +11336,70 @@
         <v>29</v>
       </c>
       <c r="BE43">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG43">
         <v>24</v>
       </c>
       <c r="BH43">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ43">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK43">
         <v>1.01</v>
       </c>
       <c r="BL43">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM43">
         <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO43">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BP43">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BQ43">
         <v>1.01</v>
       </c>
       <c r="BR43">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS43">
         <v>1.01</v>
       </c>
       <c r="BT43">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BU43">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV43">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BW43">
         <v>1.01</v>
       </c>
       <c r="BX43">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY43">
         <v>1.01</v>
       </c>
       <c r="BZ43">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="CA43">
         <v>1.01</v>
@@ -11924,7 +11924,7 @@
         <v>4.4</v>
       </c>
       <c r="K46">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L46">
         <v>1.29</v>
@@ -11936,16 +11936,16 @@
         <v>5.1</v>
       </c>
       <c r="O46">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P46">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q46">
         <v>1.6</v>
       </c>
       <c r="R46">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S46">
         <v>2.56</v>
@@ -11963,7 +11963,7 @@
         <v>1.19</v>
       </c>
       <c r="X46">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y46">
         <v>12</v>
@@ -11972,10 +11972,10 @@
         <v>14</v>
       </c>
       <c r="AA46">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AB46">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC46">
         <v>13</v>
@@ -11984,13 +11984,13 @@
         <v>12.5</v>
       </c>
       <c r="AE46">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AF46">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AG46">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH46">
         <v>23</v>
@@ -12014,37 +12014,37 @@
         <v>75</v>
       </c>
       <c r="AO46">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AP46">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ46">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR46">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AS46">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AT46">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="AU46">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AV46">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AW46">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX46">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="AY46">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="AZ46">
         <v>13.5</v>
@@ -12053,22 +12053,22 @@
         <v>20</v>
       </c>
       <c r="BB46">
+        <v>5.1</v>
+      </c>
+      <c r="BC46">
         <v>5</v>
-      </c>
-      <c r="BC46">
-        <v>4.9</v>
       </c>
       <c r="BD46">
         <v>4.9</v>
       </c>
       <c r="BE46">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF46">
         <v>4.9</v>
       </c>
       <c r="BG46">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH46">
         <v>5</v>
@@ -12169,7 +12169,7 @@
         <v>3.85</v>
       </c>
       <c r="L47">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M47">
         <v>1.09</v>
@@ -12641,10 +12641,10 @@
         <v>1.69</v>
       </c>
       <c r="H49">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I49">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J49">
         <v>4.1</v>
@@ -12653,25 +12653,25 @@
         <v>4.5</v>
       </c>
       <c r="L49">
+        <v>1.32</v>
+      </c>
+      <c r="M49">
+        <v>1.06</v>
+      </c>
+      <c r="N49">
+        <v>4.2</v>
+      </c>
+      <c r="O49">
         <v>1.27</v>
       </c>
-      <c r="M49">
-        <v>1.05</v>
-      </c>
-      <c r="N49">
-        <v>4.3</v>
-      </c>
-      <c r="O49">
-        <v>1.26</v>
-      </c>
       <c r="P49">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q49">
         <v>1.79</v>
       </c>
       <c r="R49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S49">
         <v>3</v>
@@ -12680,10 +12680,10 @@
         <v>1.72</v>
       </c>
       <c r="U49">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W49">
         <v>2.44</v>
@@ -12698,10 +12698,10 @@
         <v>60</v>
       </c>
       <c r="AA49">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB49">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC49">
         <v>11.5</v>
@@ -12731,10 +12731,10 @@
         <v>19.5</v>
       </c>
       <c r="AL49">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM49">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN49">
         <v>9</v>
@@ -12749,109 +12749,109 @@
         <v>16.5</v>
       </c>
       <c r="AR49">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AS49">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT49">
         <v>8.199999999999999</v>
       </c>
       <c r="AU49">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV49">
         <v>17.5</v>
       </c>
       <c r="AW49">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX49">
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ49">
         <v>15.5</v>
       </c>
       <c r="BA49">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB49">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC49">
         <v>13</v>
       </c>
       <c r="BD49">
+        <v>5.2</v>
+      </c>
+      <c r="BE49">
         <v>5.3</v>
       </c>
-      <c r="BE49">
-        <v>5.6</v>
-      </c>
       <c r="BF49">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG49">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH49">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI49">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ49">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK49">
         <v>1.01</v>
       </c>
       <c r="BL49">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM49">
         <v>1.01</v>
       </c>
       <c r="BN49">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO49">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP49">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ49">
         <v>1.01</v>
       </c>
       <c r="BR49">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS49">
         <v>1.01</v>
       </c>
       <c r="BT49">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU49">
         <v>1.01</v>
       </c>
       <c r="BV49">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW49">
         <v>1.01</v>
       </c>
       <c r="BX49">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY49">
         <v>1.01</v>
       </c>
       <c r="BZ49">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA49">
         <v>1.01</v>
@@ -12892,7 +12892,7 @@
         <v>6.4</v>
       </c>
       <c r="K50">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -12910,7 +12910,7 @@
         <v>2.4</v>
       </c>
       <c r="Q50">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R50">
         <v>1.58</v>
@@ -12928,19 +12928,19 @@
         <v>1.07</v>
       </c>
       <c r="W50">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X50">
         <v>23</v>
       </c>
       <c r="Y50">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z50">
         <v>160</v>
       </c>
       <c r="AA50">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="AB50">
         <v>9.4</v>
@@ -12949,10 +12949,10 @@
         <v>15</v>
       </c>
       <c r="AD50">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE50">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AF50">
         <v>8</v>
@@ -12991,10 +12991,10 @@
         <v>34</v>
       </c>
       <c r="AR50">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS50">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT50">
         <v>8.199999999999999</v>
@@ -13018,7 +13018,7 @@
         <v>30</v>
       </c>
       <c r="BA50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB50">
         <v>8.6</v>
@@ -13030,13 +13030,13 @@
         <v>34</v>
       </c>
       <c r="BE50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF50">
         <v>4.4</v>
       </c>
       <c r="BG50">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13128,7 +13128,7 @@
         <v>5.9</v>
       </c>
       <c r="I51">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J51">
         <v>4.2</v>
@@ -13161,10 +13161,10 @@
         <v>2.66</v>
       </c>
       <c r="T51">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="U51">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V51">
         <v>1.16</v>
@@ -13188,7 +13188,7 @@
         <v>11.5</v>
       </c>
       <c r="AC51">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD51">
         <v>28</v>
@@ -13278,7 +13278,7 @@
         <v>5.8</v>
       </c>
       <c r="BG51">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH51">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-02.xlsx
@@ -820,7 +820,7 @@
     <t>Portuguesa FC</t>
   </si>
   <si>
-    <t>2026-09-01 19:21:03</t>
+    <t>2026-09-01 21:35:40</t>
   </si>
 </sst>
 </file>
@@ -1414,226 +1414,226 @@
         <v>199</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
+        <v>5.4</v>
+      </c>
+      <c r="J2">
+        <v>2.96</v>
+      </c>
+      <c r="K2">
+        <v>3.1</v>
+      </c>
+      <c r="L2">
+        <v>2.5</v>
+      </c>
+      <c r="M2">
+        <v>1.17</v>
+      </c>
+      <c r="N2">
+        <v>2.14</v>
+      </c>
+      <c r="O2">
+        <v>1.84</v>
+      </c>
+      <c r="P2">
+        <v>1.38</v>
+      </c>
+      <c r="Q2">
+        <v>3.5</v>
+      </c>
+      <c r="R2">
+        <v>1.12</v>
+      </c>
+      <c r="S2">
+        <v>8.6</v>
+      </c>
+      <c r="T2">
+        <v>2.74</v>
+      </c>
+      <c r="U2">
+        <v>1.51</v>
+      </c>
+      <c r="V2">
+        <v>1.25</v>
+      </c>
+      <c r="W2">
+        <v>1.88</v>
+      </c>
+      <c r="X2">
         <v>6.4</v>
       </c>
-      <c r="J2">
-        <v>3.9</v>
-      </c>
-      <c r="K2">
-        <v>4.1</v>
-      </c>
-      <c r="L2">
-        <v>1.43</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.7</v>
-      </c>
-      <c r="O2">
-        <v>1.34</v>
-      </c>
-      <c r="P2">
-        <v>1.92</v>
-      </c>
-      <c r="Q2">
-        <v>2.02</v>
-      </c>
-      <c r="R2">
-        <v>1.34</v>
-      </c>
-      <c r="S2">
-        <v>3.7</v>
-      </c>
-      <c r="T2">
-        <v>1.98</v>
-      </c>
-      <c r="U2">
-        <v>1.93</v>
-      </c>
-      <c r="V2">
-        <v>1.18</v>
-      </c>
-      <c r="W2">
-        <v>2.36</v>
-      </c>
-      <c r="X2">
-        <v>14</v>
-      </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA2">
         <v>200</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2">
+        <v>140</v>
+      </c>
+      <c r="AF2">
+        <v>10</v>
+      </c>
+      <c r="AG2">
+        <v>13.5</v>
+      </c>
+      <c r="AH2">
+        <v>48</v>
+      </c>
+      <c r="AI2">
+        <v>230</v>
+      </c>
+      <c r="AJ2">
+        <v>30</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>130</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>60</v>
+      </c>
+      <c r="AO2">
+        <v>330</v>
+      </c>
+      <c r="AP2">
+        <v>5.9</v>
+      </c>
+      <c r="AQ2">
+        <v>9.6</v>
+      </c>
+      <c r="AR2">
+        <v>32</v>
+      </c>
+      <c r="AS2">
+        <v>130</v>
+      </c>
+      <c r="AT2">
+        <v>4.9</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>22</v>
+      </c>
+      <c r="AW2">
         <v>110</v>
       </c>
-      <c r="AF2">
+      <c r="AX2">
         <v>9.4</v>
       </c>
-      <c r="AG2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>95</v>
-      </c>
-      <c r="AJ2">
-        <v>17.5</v>
-      </c>
-      <c r="AK2">
+      <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
+        <v>36</v>
+      </c>
+      <c r="BA2">
+        <v>150</v>
+      </c>
+      <c r="BB2">
+        <v>26</v>
+      </c>
+      <c r="BC2">
+        <v>34</v>
+      </c>
+      <c r="BD2">
+        <v>100</v>
+      </c>
+      <c r="BE2">
+        <v>360</v>
+      </c>
+      <c r="BF2">
+        <v>40</v>
+      </c>
+      <c r="BG2">
+        <v>180</v>
+      </c>
+      <c r="BH2">
+        <v>1.56</v>
+      </c>
+      <c r="BI2">
+        <v>1.52</v>
+      </c>
+      <c r="BJ2">
+        <v>44</v>
+      </c>
+      <c r="BK2">
+        <v>32</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>20</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>5.1</v>
+      </c>
+      <c r="BP2">
+        <v>55</v>
+      </c>
+      <c r="BQ2">
+        <v>42</v>
+      </c>
+      <c r="BR2">
+        <v>370</v>
+      </c>
+      <c r="BS2">
         <v>19</v>
       </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
+      <c r="BT2">
+        <v>11</v>
+      </c>
+      <c r="BU2">
+        <v>9.6</v>
+      </c>
+      <c r="BV2">
+        <v>180</v>
+      </c>
+      <c r="BW2">
+        <v>100</v>
+      </c>
+      <c r="BX2">
+        <v>650</v>
+      </c>
+      <c r="BY2">
+        <v>19.5</v>
+      </c>
+      <c r="BZ2">
+        <v>860</v>
+      </c>
+      <c r="CA2">
         <v>160</v>
-      </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>130</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>17</v>
-      </c>
-      <c r="AR2">
-        <v>38</v>
-      </c>
-      <c r="AS2">
-        <v>110</v>
-      </c>
-      <c r="AT2">
-        <v>7</v>
-      </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>20</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>8.4</v>
-      </c>
-      <c r="AY2">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2">
-        <v>20</v>
-      </c>
-      <c r="BA2">
-        <v>50</v>
-      </c>
-      <c r="BB2">
-        <v>15.5</v>
-      </c>
-      <c r="BC2">
-        <v>16.5</v>
-      </c>
-      <c r="BD2">
-        <v>34</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2">
-        <v>10.5</v>
-      </c>
-      <c r="BG2">
-        <v>65</v>
-      </c>
-      <c r="BH2">
-        <v>3.75</v>
-      </c>
-      <c r="BI2">
-        <v>2.96</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
-      <c r="BK2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL2">
-        <v>180</v>
-      </c>
-      <c r="BM2">
-        <v>7.4</v>
-      </c>
-      <c r="BN2">
-        <v>4.4</v>
-      </c>
-      <c r="BO2">
-        <v>3.8</v>
-      </c>
-      <c r="BP2">
-        <v>12.5</v>
-      </c>
-      <c r="BQ2">
-        <v>5.1</v>
-      </c>
-      <c r="BR2">
-        <v>30</v>
-      </c>
-      <c r="BS2">
-        <v>6.2</v>
-      </c>
-      <c r="BT2">
-        <v>10.5</v>
-      </c>
-      <c r="BU2">
-        <v>7.4</v>
-      </c>
-      <c r="BV2">
-        <v>55</v>
-      </c>
-      <c r="BW2">
-        <v>6.8</v>
-      </c>
-      <c r="BX2">
-        <v>60</v>
-      </c>
-      <c r="BY2">
-        <v>7</v>
-      </c>
-      <c r="BZ2">
-        <v>25</v>
-      </c>
-      <c r="CA2">
-        <v>6</v>
       </c>
       <c r="CB2" t="s">
         <v>268</v>
@@ -1656,22 +1656,22 @@
         <v>200</v>
       </c>
       <c r="F3">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.45</v>
@@ -1680,16 +1680,16 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O3">
         <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
         <v>1.3</v>
@@ -1698,58 +1698,58 @@
         <v>4.1</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U3">
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
+        <v>11.5</v>
+      </c>
+      <c r="Y3">
+        <v>9.4</v>
+      </c>
+      <c r="Z3">
+        <v>14.5</v>
+      </c>
+      <c r="AA3">
+        <v>34</v>
+      </c>
+      <c r="AB3">
         <v>12</v>
-      </c>
-      <c r="Y3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>14</v>
-      </c>
-      <c r="AA3">
-        <v>36</v>
-      </c>
-      <c r="AB3">
-        <v>12.5</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
         <v>34</v>
       </c>
       <c r="AF3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>19</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1758,10 +1758,10 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
@@ -1770,31 +1770,31 @@
         <v>8.4</v>
       </c>
       <c r="AR3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1803,64 +1803,64 @@
         <v>55</v>
       </c>
       <c r="BC3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE3">
-        <v>16.5</v>
+        <v>90</v>
       </c>
       <c r="BF3">
         <v>40</v>
       </c>
       <c r="BG3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BH3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI3">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>160</v>
+        <v>990</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS3">
         <v>9</v>
       </c>
       <c r="BT3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="BW3">
         <v>6.8</v>
@@ -1869,13 +1869,13 @@
         <v>34</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>268</v>
@@ -1910,7 +1910,7 @@
         <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1928,10 +1928,10 @@
         <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1943,7 +1943,7 @@
         <v>2</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -1958,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AA4">
         <v>70</v>
@@ -1982,13 +1982,13 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AI4">
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK4">
         <v>38</v>
@@ -2006,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>8.800000000000001</v>
@@ -2015,7 +2015,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -2036,7 +2036,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
         <v>44</v>
@@ -2051,22 +2051,22 @@
         <v>38</v>
       </c>
       <c r="BE4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG4">
         <v>32</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>200</v>
       </c>
       <c r="BM4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4">
         <v>5.4</v>
@@ -2087,13 +2087,13 @@
         <v>27</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
@@ -2105,19 +2105,19 @@
         <v>34</v>
       </c>
       <c r="BW4">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4">
         <v>50</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
         <v>268</v>
@@ -2140,19 +2140,19 @@
         <v>202</v>
       </c>
       <c r="F5">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H5">
         <v>4.1</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
         <v>3.9</v>
@@ -2170,10 +2170,10 @@
         <v>1.29</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R5">
         <v>1.42</v>
@@ -2191,19 +2191,19 @@
         <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB5">
         <v>10.5</v>
@@ -2218,7 +2218,7 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>11</v>
@@ -2233,16 +2233,16 @@
         <v>25</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO5">
         <v>55</v>
@@ -2251,10 +2251,10 @@
         <v>14</v>
       </c>
       <c r="AQ5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS5">
         <v>55</v>
@@ -2266,7 +2266,7 @@
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW5">
         <v>40</v>
@@ -2290,10 +2290,10 @@
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -2311,16 +2311,16 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BL5">
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO5">
         <v>4.2</v>
@@ -2329,37 +2329,37 @@
         <v>16</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BT5">
         <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BZ5">
         <v>26</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB5" t="s">
         <v>268</v>
@@ -2388,16 +2388,16 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J6">
         <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.44</v>
@@ -2412,7 +2412,7 @@
         <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q6">
         <v>2.06</v>
@@ -2424,7 +2424,7 @@
         <v>3.65</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
         <v>2.02</v>
@@ -2439,7 +2439,7 @@
         <v>15</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
         <v>11.5</v>
@@ -2466,7 +2466,7 @@
         <v>21</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>48</v>
@@ -2520,22 +2520,22 @@
         <v>16</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD6">
         <v>46</v>
       </c>
       <c r="BE6">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BF6">
         <v>46</v>
@@ -2547,37 +2547,37 @@
         <v>3.6</v>
       </c>
       <c r="BI6">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL6">
         <v>160</v>
       </c>
       <c r="BM6">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6">
         <v>7.8</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>46</v>
       </c>
       <c r="BQ6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
         <v>4.6</v>
@@ -2589,19 +2589,19 @@
         <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BX6">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BY6">
+        <v>7.6</v>
+      </c>
+      <c r="BZ6">
+        <v>27</v>
+      </c>
+      <c r="CA6">
         <v>7.4</v>
-      </c>
-      <c r="BZ6">
-        <v>32</v>
-      </c>
-      <c r="CA6">
-        <v>7.2</v>
       </c>
       <c r="CB6" t="s">
         <v>268</v>
@@ -2633,13 +2633,13 @@
         <v>1.96</v>
       </c>
       <c r="I7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2657,7 +2657,7 @@
         <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R7">
         <v>1.39</v>
@@ -2672,7 +2672,7 @@
         <v>2.14</v>
       </c>
       <c r="V7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W7">
         <v>1.29</v>
@@ -2693,7 +2693,7 @@
         <v>16</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
@@ -2702,7 +2702,7 @@
         <v>21</v>
       </c>
       <c r="AF7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG7">
         <v>17.5</v>
@@ -2768,16 +2768,16 @@
         <v>16</v>
       </c>
       <c r="BB7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF7">
         <v>11</v>
@@ -2789,7 +2789,7 @@
         <v>3.95</v>
       </c>
       <c r="BI7">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7">
         <v>10</v>
@@ -2801,10 +2801,10 @@
         <v>150</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
         <v>5.8</v>
@@ -2813,13 +2813,13 @@
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR7">
         <v>44</v>
       </c>
       <c r="BS7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT7">
         <v>4.7</v>
@@ -2837,13 +2837,13 @@
         <v>28</v>
       </c>
       <c r="BY7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
         <v>23</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="s">
         <v>268</v>
@@ -2899,7 +2899,7 @@
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R8">
         <v>1.4</v>
@@ -2908,7 +2908,7 @@
         <v>3.25</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
         <v>2.24</v>
@@ -2920,7 +2920,7 @@
         <v>1.77</v>
       </c>
       <c r="X8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y8">
         <v>17.5</v>
@@ -2935,7 +2935,7 @@
         <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>15</v>
@@ -2944,13 +2944,13 @@
         <v>48</v>
       </c>
       <c r="AF8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI8">
         <v>60</v>
@@ -2968,7 +2968,7 @@
         <v>110</v>
       </c>
       <c r="AN8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO8">
         <v>38</v>
@@ -2980,10 +2980,10 @@
         <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT8">
         <v>9.4</v>
@@ -3010,7 +3010,7 @@
         <v>32</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC8">
         <v>20</v>
@@ -3108,16 +3108,16 @@
         <v>206</v>
       </c>
       <c r="F9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
         <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J9">
         <v>3.6</v>
@@ -3126,13 +3126,13 @@
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
         <v>1.29</v>
@@ -3141,22 +3141,22 @@
         <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R9">
         <v>1.42</v>
       </c>
       <c r="S9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W9">
         <v>1.38</v>
@@ -3225,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="AS9">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AT9">
         <v>13</v>
@@ -3252,13 +3252,13 @@
         <v>19</v>
       </c>
       <c r="BB9">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BD9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE9">
         <v>42</v>
@@ -3270,7 +3270,7 @@
         <v>13.5</v>
       </c>
       <c r="BH9">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI9">
         <v>2.88</v>
@@ -3350,7 +3350,7 @@
         <v>207</v>
       </c>
       <c r="F10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G10">
         <v>3.85</v>
@@ -3368,25 +3368,25 @@
         <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M10">
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
         <v>3.2</v>
@@ -3395,7 +3395,7 @@
         <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.86</v>
@@ -3419,10 +3419,10 @@
         <v>18</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE10">
         <v>23</v>
@@ -3434,7 +3434,7 @@
         <v>15.5</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
         <v>36</v>
@@ -3455,7 +3455,7 @@
         <v>42</v>
       </c>
       <c r="AO10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP10">
         <v>14.5</v>
@@ -3467,7 +3467,7 @@
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT10">
         <v>13.5</v>
@@ -3485,7 +3485,7 @@
         <v>23</v>
       </c>
       <c r="AY10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ10">
         <v>15</v>
@@ -3512,40 +3512,40 @@
         <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
         <v>11</v>
       </c>
       <c r="BK10">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="BL10">
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN10">
         <v>8.199999999999999</v>
       </c>
       <c r="BO10">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT10">
         <v>5.6</v>
@@ -3557,19 +3557,19 @@
         <v>17</v>
       </c>
       <c r="BW10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX10">
         <v>32</v>
       </c>
       <c r="BY10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ10">
         <v>26</v>
       </c>
       <c r="CA10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB10" t="s">
         <v>268</v>
@@ -3601,7 +3601,7 @@
         <v>2.1</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J11">
         <v>3.5</v>
@@ -3610,19 +3610,19 @@
         <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
         <v>1.37</v>
       </c>
       <c r="P11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
         <v>2.1</v>
@@ -3670,7 +3670,7 @@
         <v>42</v>
       </c>
       <c r="AF11">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AG11">
         <v>17</v>
@@ -3754,13 +3754,13 @@
         <v>15.5</v>
       </c>
       <c r="BH11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
         <v>8</v>
@@ -3769,10 +3769,10 @@
         <v>160</v>
       </c>
       <c r="BM11">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN11">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BO11">
         <v>5.8</v>
@@ -3781,13 +3781,13 @@
         <v>40</v>
       </c>
       <c r="BQ11">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR11">
         <v>55</v>
       </c>
       <c r="BS11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BT11">
         <v>5</v>
@@ -3796,22 +3796,22 @@
         <v>4.1</v>
       </c>
       <c r="BV11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BW11">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BX11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY11">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA11">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB11" t="s">
         <v>268</v>
@@ -3834,22 +3834,22 @@
         <v>209</v>
       </c>
       <c r="F12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
         <v>1.3</v>
@@ -3870,7 +3870,7 @@
         <v>1.63</v>
       </c>
       <c r="R12">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S12">
         <v>2.56</v>
@@ -3885,61 +3885,61 @@
         <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X12">
         <v>23</v>
       </c>
       <c r="Y12">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z12">
         <v>55</v>
       </c>
       <c r="AA12">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC12">
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG12">
         <v>10</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ12">
         <v>15</v>
       </c>
       <c r="AK12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL12">
         <v>30</v>
       </c>
       <c r="AM12">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN12">
         <v>6.6</v>
       </c>
       <c r="AO12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP12">
         <v>20</v>
@@ -3948,16 +3948,16 @@
         <v>24</v>
       </c>
       <c r="AR12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS12">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AT12">
         <v>10</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
         <v>20</v>
@@ -3975,7 +3975,7 @@
         <v>17.5</v>
       </c>
       <c r="BA12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB12">
         <v>13.5</v>
@@ -3987,7 +3987,7 @@
         <v>25</v>
       </c>
       <c r="BE12">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF12">
         <v>6</v>
@@ -4076,37 +4076,37 @@
         <v>210</v>
       </c>
       <c r="F13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H13">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J13">
         <v>3.2</v>
       </c>
       <c r="K13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M13">
         <v>1.13</v>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O13">
         <v>1.56</v>
       </c>
       <c r="P13">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q13">
         <v>2.68</v>
@@ -4115,22 +4115,22 @@
         <v>1.2</v>
       </c>
       <c r="S13">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T13">
         <v>2.26</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W13">
         <v>1.29</v>
       </c>
       <c r="X13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -4142,10 +4142,10 @@
         <v>32</v>
       </c>
       <c r="AB13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
         <v>12.5</v>
@@ -4181,19 +4181,19 @@
         <v>600</v>
       </c>
       <c r="AO13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR13">
         <v>10</v>
       </c>
       <c r="AS13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT13">
         <v>10</v>
@@ -4205,22 +4205,22 @@
         <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX13">
         <v>23</v>
       </c>
       <c r="AY13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA13">
         <v>42</v>
       </c>
       <c r="BB13">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BC13">
         <v>46</v>
@@ -4229,22 +4229,22 @@
         <v>55</v>
       </c>
       <c r="BE13">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH13">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI13">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
         <v>8.800000000000001</v>
@@ -4256,13 +4256,13 @@
         <v>6</v>
       </c>
       <c r="BN13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ13">
         <v>5.5</v>
@@ -4271,7 +4271,7 @@
         <v>75</v>
       </c>
       <c r="BS13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
@@ -4280,16 +4280,16 @@
         <v>3.8</v>
       </c>
       <c r="BV13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ13">
         <v>55</v>
@@ -4318,19 +4318,19 @@
         <v>211</v>
       </c>
       <c r="F14">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>110</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>110</v>
@@ -4342,7 +4342,7 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
         <v>1.34</v>
@@ -4351,13 +4351,13 @@
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="R14">
         <v>1.18</v>
       </c>
       <c r="S14">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4366,10 +4366,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4387,7 +4387,7 @@
         <v>1000</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD14">
         <v>1000</v>
@@ -4408,7 +4408,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14">
         <v>1000</v>
@@ -4420,7 +4420,7 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO14">
         <v>1000</v>
@@ -4477,7 +4477,7 @@
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4560,226 +4560,226 @@
         <v>212</v>
       </c>
       <c r="F15">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="G15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H15">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="J15">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="K15">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="L15">
         <v>1.6</v>
       </c>
       <c r="M15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O15">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="P15">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S15">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="U15">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="V15">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X15">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y15">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z15">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="AA15">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AB15">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AD15">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE15">
+        <v>440</v>
+      </c>
+      <c r="AF15">
+        <v>90</v>
+      </c>
+      <c r="AG15">
+        <v>970</v>
+      </c>
+      <c r="AH15">
         <v>75</v>
       </c>
-      <c r="AF15">
-        <v>22</v>
-      </c>
-      <c r="AG15">
-        <v>18.5</v>
-      </c>
-      <c r="AH15">
-        <v>36</v>
-      </c>
       <c r="AI15">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ15">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AK15">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AL15">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AM15">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AO15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ15">
-        <v>6.8</v>
+        <v>1.68</v>
       </c>
       <c r="AR15">
-        <v>16.5</v>
+        <v>1.66</v>
       </c>
       <c r="AS15">
-        <v>5.6</v>
+        <v>1.72</v>
       </c>
       <c r="AT15">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU15">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AW15">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="AX15">
-        <v>15.5</v>
+        <v>1.7</v>
       </c>
       <c r="AY15">
-        <v>13.5</v>
+        <v>1.66</v>
       </c>
       <c r="AZ15">
-        <v>5.1</v>
+        <v>1.69</v>
       </c>
       <c r="BA15">
-        <v>5.7</v>
+        <v>1.72</v>
       </c>
       <c r="BB15">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="BC15">
-        <v>5.4</v>
+        <v>1.71</v>
       </c>
       <c r="BD15">
-        <v>5.7</v>
+        <v>1.72</v>
       </c>
       <c r="BE15">
-        <v>5.9</v>
+        <v>1.73</v>
       </c>
       <c r="BF15">
-        <v>5.6</v>
+        <v>1.72</v>
       </c>
       <c r="BG15">
-        <v>5.7</v>
+        <v>1.73</v>
       </c>
       <c r="BH15">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>268</v>
@@ -4802,7 +4802,7 @@
         <v>213</v>
       </c>
       <c r="F16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G16">
         <v>3.8</v>
@@ -4811,7 +4811,7 @@
         <v>2.24</v>
       </c>
       <c r="I16">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J16">
         <v>3.45</v>
@@ -4820,7 +4820,7 @@
         <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="M16">
         <v>1.06</v>
@@ -4841,7 +4841,7 @@
         <v>1.4</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
         <v>1.63</v>
@@ -4850,7 +4850,7 @@
         <v>2.42</v>
       </c>
       <c r="V16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W16">
         <v>1.36</v>
@@ -4874,16 +4874,16 @@
         <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE16">
         <v>24</v>
       </c>
       <c r="AF16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH16">
         <v>16.5</v>
@@ -4904,7 +4904,7 @@
         <v>90</v>
       </c>
       <c r="AN16">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO16">
         <v>17.5</v>
@@ -4919,10 +4919,10 @@
         <v>14</v>
       </c>
       <c r="AS16">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AT16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU16">
         <v>6.8</v>
@@ -4934,7 +4934,7 @@
         <v>20</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AY16">
         <v>13</v>
@@ -4949,19 +4949,19 @@
         <v>55</v>
       </c>
       <c r="BC16">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE16">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BF16">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BG16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5044,13 +5044,13 @@
         <v>214</v>
       </c>
       <c r="F17">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G17">
         <v>2.1</v>
       </c>
       <c r="H17">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I17">
         <v>5.1</v>
@@ -5059,7 +5059,7 @@
         <v>3.4</v>
       </c>
       <c r="K17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>1.32</v>
@@ -5068,16 +5068,16 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P17">
         <v>1.61</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="R17">
         <v>1.18</v>
@@ -5098,22 +5098,22 @@
         <v>1.9</v>
       </c>
       <c r="X17">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y17">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z17">
         <v>500</v>
       </c>
       <c r="AA17">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB17">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC17">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD17">
         <v>500</v>
@@ -5125,7 +5125,7 @@
         <v>500</v>
       </c>
       <c r="AG17">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH17">
         <v>500</v>
@@ -5134,7 +5134,7 @@
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK17">
         <v>500</v>
@@ -5143,13 +5143,13 @@
         <v>500</v>
       </c>
       <c r="AM17">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17">
         <v>500</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP17">
         <v>1.01</v>
@@ -5164,10 +5164,10 @@
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV17">
         <v>1.01</v>
@@ -5200,10 +5200,10 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5343,13 +5343,13 @@
         <v>10.5</v>
       </c>
       <c r="Y18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA18">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18">
         <v>7.8</v>
@@ -5364,40 +5364,40 @@
         <v>500</v>
       </c>
       <c r="AF18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH18">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI18">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL18">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM18">
         <v>500</v>
       </c>
       <c r="AN18">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO18">
         <v>500</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR18">
         <v>1.01</v>
@@ -5406,10 +5406,10 @@
         <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV18">
         <v>1.01</v>
@@ -5418,10 +5418,10 @@
         <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ18">
         <v>1.01</v>
@@ -5442,10 +5442,10 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5528,22 +5528,22 @@
         <v>216</v>
       </c>
       <c r="F19">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="G19">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="H19">
         <v>3.9</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="J19">
         <v>3.3</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
         <v>1.34</v>
@@ -5576,13 +5576,13 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="X19">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y19">
         <v>500</v>
@@ -5591,13 +5591,13 @@
         <v>500</v>
       </c>
       <c r="AA19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB19">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC19">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD19">
         <v>500</v>
@@ -5609,7 +5609,7 @@
         <v>500</v>
       </c>
       <c r="AG19">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH19">
         <v>500</v>
@@ -5618,7 +5618,7 @@
         <v>500</v>
       </c>
       <c r="AJ19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK19">
         <v>500</v>
@@ -5627,16 +5627,16 @@
         <v>500</v>
       </c>
       <c r="AM19">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>500</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19">
         <v>1.01</v>
@@ -5648,10 +5648,10 @@
         <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV19">
         <v>1.01</v>
@@ -5660,7 +5660,7 @@
         <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AY19">
         <v>1.01</v>
@@ -5684,10 +5684,10 @@
         <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5776,7 +5776,7 @@
         <v>2.56</v>
       </c>
       <c r="H20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I20">
         <v>3.95</v>
@@ -5845,7 +5845,7 @@
         <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AF20">
         <v>15.5</v>
@@ -5860,70 +5860,70 @@
         <v>500</v>
       </c>
       <c r="AJ20">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AK20">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL20">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM20">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO20">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP20">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20">
+        <v>5.6</v>
+      </c>
+      <c r="AR20">
+        <v>5.7</v>
+      </c>
+      <c r="AS20">
+        <v>6.6</v>
+      </c>
+      <c r="AT20">
+        <v>5.6</v>
+      </c>
+      <c r="AU20">
+        <v>4.4</v>
+      </c>
+      <c r="AV20">
+        <v>5</v>
+      </c>
+      <c r="AW20">
+        <v>6.4</v>
+      </c>
+      <c r="AX20">
+        <v>4.9</v>
+      </c>
+      <c r="AY20">
         <v>4.6</v>
       </c>
-      <c r="AR20">
-        <v>5.6</v>
-      </c>
-      <c r="AS20">
+      <c r="AZ20">
+        <v>5.4</v>
+      </c>
+      <c r="BA20">
+        <v>6.6</v>
+      </c>
+      <c r="BB20">
+        <v>6</v>
+      </c>
+      <c r="BC20">
+        <v>5.9</v>
+      </c>
+      <c r="BD20">
         <v>6.4</v>
       </c>
-      <c r="AT20">
-        <v>4</v>
-      </c>
-      <c r="AU20">
-        <v>3.8</v>
-      </c>
-      <c r="AV20">
-        <v>4.9</v>
-      </c>
-      <c r="AW20">
-        <v>6.2</v>
-      </c>
-      <c r="AX20">
-        <v>4.8</v>
-      </c>
-      <c r="AY20">
-        <v>4.5</v>
-      </c>
-      <c r="AZ20">
-        <v>5.3</v>
-      </c>
-      <c r="BA20">
-        <v>6.4</v>
-      </c>
-      <c r="BB20">
-        <v>5.9</v>
-      </c>
-      <c r="BC20">
-        <v>5.7</v>
-      </c>
-      <c r="BD20">
-        <v>6.2</v>
-      </c>
       <c r="BE20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF20">
         <v>5.7</v>
@@ -6012,16 +6012,16 @@
         <v>218</v>
       </c>
       <c r="F21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="H21">
         <v>2.88</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="J21">
         <v>2.52</v>
@@ -6036,13 +6036,13 @@
         <v>1.01</v>
       </c>
       <c r="N21">
+        <v>1.27</v>
+      </c>
+      <c r="O21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
         <v>1.26</v>
-      </c>
-      <c r="O21">
-        <v>1.01</v>
-      </c>
-      <c r="P21">
-        <v>1.25</v>
       </c>
       <c r="Q21">
         <v>1.32</v>
@@ -6051,7 +6051,7 @@
         <v>1.18</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6063,7 +6063,7 @@
         <v>1.17</v>
       </c>
       <c r="W21">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6078,10 +6078,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -6093,7 +6093,7 @@
         <v>500</v>
       </c>
       <c r="AG21">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH21">
         <v>1000</v>
@@ -6102,7 +6102,7 @@
         <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK21">
         <v>500</v>
@@ -6132,10 +6132,10 @@
         <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV21">
         <v>1.01</v>
@@ -6168,10 +6168,10 @@
         <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6260,16 +6260,16 @@
         <v>2.12</v>
       </c>
       <c r="H22">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I22">
         <v>5.4</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L22">
         <v>1.32</v>
@@ -6281,7 +6281,7 @@
         <v>3.4</v>
       </c>
       <c r="O22">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="P22">
         <v>1.83</v>
@@ -6356,64 +6356,64 @@
         <v>140</v>
       </c>
       <c r="AN22">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO22">
         <v>80</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6544,10 +6544,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6559,13 +6559,13 @@
         <v>1000</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23">
         <v>1000</v>
       </c>
       <c r="AC23">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD23">
         <v>1000</v>
@@ -6586,7 +6586,7 @@
         <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK23">
         <v>1000</v>
@@ -6652,10 +6652,10 @@
         <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6738,34 +6738,34 @@
         <v>221</v>
       </c>
       <c r="F24">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="G24">
         <v>2.1</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I24">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L24">
         <v>1.39</v>
       </c>
       <c r="M24">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P24">
         <v>1.5</v>
@@ -6786,61 +6786,61 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W24">
         <v>1.9</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AC24">
         <v>970</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH24">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AI24">
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO24">
         <v>1000</v>
@@ -6894,10 +6894,10 @@
         <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6980,19 +6980,19 @@
         <v>222</v>
       </c>
       <c r="F25">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G25">
         <v>2.56</v>
       </c>
       <c r="H25">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I25">
         <v>3.4</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
         <v>3.6</v>
@@ -7028,7 +7028,7 @@
         <v>2.12</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.64</v>
@@ -7040,10 +7040,10 @@
         <v>15</v>
       </c>
       <c r="Z25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA25">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB25">
         <v>12.5</v>
@@ -7052,7 +7052,7 @@
         <v>7.8</v>
       </c>
       <c r="AD25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE25">
         <v>48</v>
@@ -7079,7 +7079,7 @@
         <v>50</v>
       </c>
       <c r="AM25">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN25">
         <v>27</v>
@@ -7100,19 +7100,19 @@
         <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25">
         <v>6.8</v>
       </c>
       <c r="AV25">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW25">
         <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY25">
         <v>8.6</v>
@@ -7139,7 +7139,7 @@
         <v>16</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7225,7 +7225,7 @@
         <v>1.37</v>
       </c>
       <c r="G26">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="H26">
         <v>4.2</v>
@@ -7246,7 +7246,7 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O26">
         <v>1.11</v>
@@ -7312,7 +7312,7 @@
         <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK26">
         <v>1000</v>
@@ -7324,7 +7324,7 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AO26">
         <v>1000</v>
@@ -7381,7 +7381,7 @@
         <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7473,19 +7473,19 @@
         <v>3.8</v>
       </c>
       <c r="I27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J27">
         <v>3.35</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27">
         <v>1.33</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N27">
         <v>3.45</v>
@@ -7500,10 +7500,10 @@
         <v>2</v>
       </c>
       <c r="R27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T27">
         <v>1.83</v>
@@ -7518,112 +7518,112 @@
         <v>1.83</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC27">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7712,7 +7712,7 @@
         <v>2.06</v>
       </c>
       <c r="H28">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I28">
         <v>4.2</v>
@@ -7721,7 +7721,7 @@
         <v>3.8</v>
       </c>
       <c r="K28">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7757,7 +7757,7 @@
         <v>1.31</v>
       </c>
       <c r="W28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X28">
         <v>21</v>
@@ -7766,10 +7766,10 @@
         <v>21</v>
       </c>
       <c r="Z28">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB28">
         <v>10.5</v>
@@ -7799,10 +7799,10 @@
         <v>28</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL28">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM28">
         <v>200</v>
@@ -7820,10 +7820,10 @@
         <v>14.5</v>
       </c>
       <c r="AR28">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS28">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT28">
         <v>9.199999999999999</v>
@@ -7832,10 +7832,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AW28">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX28">
         <v>11</v>
@@ -7844,19 +7844,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ28">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BA28">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB28">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC28">
         <v>17</v>
       </c>
       <c r="BD28">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BE28">
         <v>5.9</v>
@@ -7865,13 +7865,13 @@
         <v>10.5</v>
       </c>
       <c r="BG28">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BH28">
         <v>4.3</v>
       </c>
       <c r="BI28">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BJ28">
         <v>11.5</v>
@@ -7883,13 +7883,13 @@
         <v>130</v>
       </c>
       <c r="BM28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN28">
         <v>5.7</v>
       </c>
       <c r="BO28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP28">
         <v>16.5</v>
@@ -7907,7 +7907,7 @@
         <v>9</v>
       </c>
       <c r="BU28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV28">
         <v>40</v>
@@ -7922,7 +7922,7 @@
         <v>4.3</v>
       </c>
       <c r="BZ28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA28">
         <v>4</v>
@@ -7948,22 +7948,22 @@
         <v>226</v>
       </c>
       <c r="F29">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G29">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H29">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K29">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7972,34 +7972,34 @@
         <v>1.09</v>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="O29">
         <v>1.37</v>
       </c>
       <c r="P29">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q29">
         <v>2.12</v>
       </c>
       <c r="R29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S29">
         <v>3.9</v>
       </c>
       <c r="T29">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U29">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X29">
         <v>13</v>
@@ -8008,13 +8008,13 @@
         <v>13</v>
       </c>
       <c r="Z29">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA29">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB29">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC29">
         <v>7.8</v>
@@ -8026,13 +8026,13 @@
         <v>55</v>
       </c>
       <c r="AF29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29">
         <v>70</v>
@@ -8047,67 +8047,67 @@
         <v>55</v>
       </c>
       <c r="AM29">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO29">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS29">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT29">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU29">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV29">
+        <v>11.5</v>
+      </c>
+      <c r="AW29">
+        <v>6.4</v>
+      </c>
+      <c r="AX29">
         <v>11</v>
       </c>
-      <c r="AW29">
-        <v>5.7</v>
-      </c>
-      <c r="AX29">
-        <v>12</v>
-      </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
         <v>14</v>
       </c>
       <c r="BA29">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB29">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC29">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BD29">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE29">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF29">
         <v>18</v>
       </c>
       <c r="BG29">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8190,10 +8190,10 @@
         <v>227</v>
       </c>
       <c r="F30">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="G30">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="H30">
         <v>1.32</v>
@@ -8205,7 +8205,7 @@
         <v>5.1</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L30">
         <v>1.35</v>
@@ -8229,7 +8229,7 @@
         <v>1.36</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T30">
         <v>2.34</v>
@@ -8238,7 +8238,7 @@
         <v>1.64</v>
       </c>
       <c r="V30">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="W30">
         <v>1.07</v>
@@ -8307,7 +8307,7 @@
         <v>6</v>
       </c>
       <c r="AS30">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT30">
         <v>5.8</v>
@@ -8432,40 +8432,40 @@
         <v>228</v>
       </c>
       <c r="F31">
+        <v>3.3</v>
+      </c>
+      <c r="G31">
+        <v>3.65</v>
+      </c>
+      <c r="H31">
+        <v>2.82</v>
+      </c>
+      <c r="I31">
+        <v>3.05</v>
+      </c>
+      <c r="J31">
+        <v>2.6</v>
+      </c>
+      <c r="K31">
+        <v>2.82</v>
+      </c>
+      <c r="L31">
+        <v>1.55</v>
+      </c>
+      <c r="M31">
+        <v>1.18</v>
+      </c>
+      <c r="N31">
+        <v>2.2</v>
+      </c>
+      <c r="O31">
+        <v>1.72</v>
+      </c>
+      <c r="P31">
+        <v>1.38</v>
+      </c>
+      <c r="Q31">
         <v>3.2</v>
-      </c>
-      <c r="G31">
-        <v>3.5</v>
-      </c>
-      <c r="H31">
-        <v>2.7</v>
-      </c>
-      <c r="I31">
-        <v>2.94</v>
-      </c>
-      <c r="J31">
-        <v>2.74</v>
-      </c>
-      <c r="K31">
-        <v>3.2</v>
-      </c>
-      <c r="L31">
-        <v>1.54</v>
-      </c>
-      <c r="M31">
-        <v>1.13</v>
-      </c>
-      <c r="N31">
-        <v>2.28</v>
-      </c>
-      <c r="O31">
-        <v>1.68</v>
-      </c>
-      <c r="P31">
-        <v>1.34</v>
-      </c>
-      <c r="Q31">
-        <v>3</v>
       </c>
       <c r="R31">
         <v>1.14</v>
@@ -8474,76 +8474,76 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="V31">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X31">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y31">
         <v>8.800000000000001</v>
       </c>
       <c r="Z31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA31">
         <v>65</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC31">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD31">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE31">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF31">
         <v>26</v>
       </c>
       <c r="AG31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH31">
         <v>34</v>
       </c>
       <c r="AI31">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AJ31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL31">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AM31">
         <v>320</v>
       </c>
       <c r="AN31">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="AO31">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP31">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ31">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR31">
         <v>12</v>
@@ -8555,22 +8555,22 @@
         <v>6.2</v>
       </c>
       <c r="AU31">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW31">
         <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY31">
         <v>12</v>
       </c>
       <c r="AZ31">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA31">
         <v>1.01</v>
@@ -8588,10 +8588,10 @@
         <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
         <v>2.2</v>
       </c>
       <c r="H32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I32">
         <v>4.7</v>
@@ -8698,13 +8698,13 @@
         <v>1.13</v>
       </c>
       <c r="N32">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q32">
         <v>2.64</v>
@@ -8716,10 +8716,10 @@
         <v>5.4</v>
       </c>
       <c r="T32">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="U32">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V32">
         <v>1.27</v>
@@ -8737,7 +8737,7 @@
         <v>40</v>
       </c>
       <c r="AA32">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -8773,7 +8773,7 @@
         <v>80</v>
       </c>
       <c r="AM32">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN32">
         <v>36</v>
@@ -8791,7 +8791,7 @@
         <v>5.7</v>
       </c>
       <c r="AS32">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT32">
         <v>6</v>
@@ -8800,7 +8800,7 @@
         <v>6.6</v>
       </c>
       <c r="AV32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW32">
         <v>6.2</v>
@@ -8833,7 +8833,7 @@
         <v>22</v>
       </c>
       <c r="BG32">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH32">
         <v>3.1</v>
@@ -8931,7 +8931,7 @@
         <v>4.8</v>
       </c>
       <c r="K33">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8940,7 +8940,7 @@
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O33">
         <v>1.2</v>
@@ -8952,13 +8952,13 @@
         <v>1.55</v>
       </c>
       <c r="R33">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S33">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T33">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U33">
         <v>1.11</v>
@@ -9006,7 +9006,7 @@
         <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK33">
         <v>1000</v>
@@ -9018,7 +9018,7 @@
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AO33">
         <v>1000</v>
@@ -9048,10 +9048,10 @@
         <v>1.04</v>
       </c>
       <c r="AX33">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AY33">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AZ33">
         <v>1.04</v>
@@ -9060,7 +9060,7 @@
         <v>1.04</v>
       </c>
       <c r="BB33">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BC33">
         <v>1.04</v>
@@ -9072,10 +9072,10 @@
         <v>1.04</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BG33">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9161,13 +9161,13 @@
         <v>2.62</v>
       </c>
       <c r="G34">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H34">
         <v>2.64</v>
       </c>
       <c r="I34">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J34">
         <v>3.4</v>
@@ -9206,10 +9206,10 @@
         <v>2.1</v>
       </c>
       <c r="V34">
+        <v>1.53</v>
+      </c>
+      <c r="W34">
         <v>1.52</v>
-      </c>
-      <c r="W34">
-        <v>1.51</v>
       </c>
       <c r="X34">
         <v>15</v>
@@ -9224,7 +9224,7 @@
         <v>240</v>
       </c>
       <c r="AB34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC34">
         <v>8.4</v>
@@ -9233,7 +9233,7 @@
         <v>13</v>
       </c>
       <c r="AE34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF34">
         <v>20</v>
@@ -9257,7 +9257,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN34">
         <v>28</v>
@@ -9269,7 +9269,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ34">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR34">
         <v>15</v>
@@ -9278,10 +9278,10 @@
         <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU34">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV34">
         <v>10</v>
@@ -9290,7 +9290,7 @@
         <v>1.01</v>
       </c>
       <c r="AX34">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AY34">
         <v>10</v>
@@ -9302,13 +9302,13 @@
         <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC34">
         <v>14.5</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE34">
         <v>1.01</v>
@@ -9317,7 +9317,7 @@
         <v>5.5</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9400,10 +9400,10 @@
         <v>232</v>
       </c>
       <c r="F35">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G35">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -9412,7 +9412,7 @@
         <v>130</v>
       </c>
       <c r="J35">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="K35">
         <v>110</v>
@@ -9424,7 +9424,7 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O35">
         <v>1.2</v>
@@ -9451,7 +9451,7 @@
         <v>1.02</v>
       </c>
       <c r="W35">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9502,7 +9502,7 @@
         <v>1000</v>
       </c>
       <c r="AN35">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO35">
         <v>1000</v>
@@ -9520,7 +9520,7 @@
         <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU35">
         <v>1.01</v>
@@ -9556,10 +9556,10 @@
         <v>1.01</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9657,7 +9657,7 @@
         <v>3.85</v>
       </c>
       <c r="K36">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9708,10 +9708,10 @@
         <v>1000</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD36">
         <v>1000</v>
@@ -9720,10 +9720,10 @@
         <v>1000</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH36">
         <v>1000</v>
@@ -9732,19 +9732,19 @@
         <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM36">
         <v>1000</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO36">
         <v>1000</v>
@@ -9801,7 +9801,7 @@
         <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9887,10 +9887,10 @@
         <v>2.58</v>
       </c>
       <c r="G37">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H37">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -9902,7 +9902,7 @@
         <v>3.65</v>
       </c>
       <c r="L37">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M37">
         <v>1.07</v>
@@ -9920,7 +9920,7 @@
         <v>1.98</v>
       </c>
       <c r="R37">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S37">
         <v>3.5</v>
@@ -9935,7 +9935,7 @@
         <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="X37">
         <v>14.5</v>
@@ -9956,34 +9956,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD37">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF37">
         <v>19</v>
       </c>
       <c r="AG37">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH37">
         <v>19</v>
       </c>
       <c r="AI37">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ37">
         <v>50</v>
       </c>
       <c r="AK37">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL37">
         <v>55</v>
       </c>
       <c r="AM37">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN37">
         <v>44</v>
@@ -10126,7 +10126,7 @@
         <v>235</v>
       </c>
       <c r="F38">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G38">
         <v>3.4</v>
@@ -10135,10 +10135,10 @@
         <v>2.24</v>
       </c>
       <c r="I38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J38">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K38">
         <v>3.95</v>
@@ -10147,22 +10147,22 @@
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P38">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q38">
         <v>1.66</v>
       </c>
       <c r="R38">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S38">
         <v>2.62</v>
@@ -10171,22 +10171,22 @@
         <v>1.57</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W38">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z38">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA38">
         <v>32</v>
@@ -10195,25 +10195,25 @@
         <v>17</v>
       </c>
       <c r="AC38">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE38">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF38">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG38">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH38">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ38">
         <v>60</v>
@@ -10225,10 +10225,10 @@
         <v>38</v>
       </c>
       <c r="AM38">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO38">
         <v>13.5</v>
@@ -10237,49 +10237,49 @@
         <v>19</v>
       </c>
       <c r="AQ38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR38">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS38">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="AT38">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU38">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV38">
         <v>10</v>
       </c>
       <c r="AW38">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX38">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY38">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA38">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BB38">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="BC38">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BD38">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE38">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF38">
         <v>21</v>
@@ -10383,7 +10383,7 @@
         <v>4.4</v>
       </c>
       <c r="K39">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>1.22</v>
@@ -10410,10 +10410,10 @@
         <v>2.32</v>
       </c>
       <c r="T39">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V39">
         <v>2.46</v>
@@ -10428,7 +10428,7 @@
         <v>13.5</v>
       </c>
       <c r="Z39">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA39">
         <v>19</v>
@@ -10467,7 +10467,7 @@
         <v>65</v>
       </c>
       <c r="AM39">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN39">
         <v>55</v>
@@ -10488,7 +10488,7 @@
         <v>13.5</v>
       </c>
       <c r="AT39">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU39">
         <v>9.800000000000001</v>
@@ -10500,7 +10500,7 @@
         <v>13</v>
       </c>
       <c r="AX39">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY39">
         <v>18</v>
@@ -10509,22 +10509,22 @@
         <v>15.5</v>
       </c>
       <c r="BA39">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB39">
+        <v>7.2</v>
+      </c>
+      <c r="BC39">
         <v>6.8</v>
       </c>
-      <c r="BC39">
-        <v>6.4</v>
-      </c>
       <c r="BD39">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE39">
+        <v>7</v>
+      </c>
+      <c r="BF39">
         <v>6.6</v>
-      </c>
-      <c r="BF39">
-        <v>6.2</v>
       </c>
       <c r="BG39">
         <v>5.5</v>
@@ -10554,7 +10554,7 @@
         <v>1.01</v>
       </c>
       <c r="BP39">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ39">
         <v>1.01</v>
@@ -10584,7 +10584,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ39">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA39">
         <v>1.01</v>
@@ -10634,7 +10634,7 @@
         <v>1.02</v>
       </c>
       <c r="N40">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O40">
         <v>1.13</v>
@@ -10718,7 +10718,7 @@
         <v>29</v>
       </c>
       <c r="AP40">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ40">
         <v>21</v>
@@ -10852,7 +10852,7 @@
         <v>238</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G41">
         <v>4.3</v>
@@ -10861,7 +10861,7 @@
         <v>2</v>
       </c>
       <c r="I41">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J41">
         <v>3.65</v>
@@ -10876,13 +10876,13 @@
         <v>1.06</v>
       </c>
       <c r="N41">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O41">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P41">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q41">
         <v>1.79</v>
@@ -10891,7 +10891,7 @@
         <v>1.46</v>
       </c>
       <c r="S41">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T41">
         <v>1.68</v>
@@ -10900,7 +10900,7 @@
         <v>2.36</v>
       </c>
       <c r="V41">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W41">
         <v>1.31</v>
@@ -10918,7 +10918,7 @@
         <v>24</v>
       </c>
       <c r="AB41">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC41">
         <v>8.4</v>
@@ -10954,7 +10954,7 @@
         <v>320</v>
       </c>
       <c r="AN41">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO41">
         <v>12.5</v>
@@ -11005,7 +11005,7 @@
         <v>32</v>
       </c>
       <c r="BE41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF41">
         <v>23</v>
@@ -11014,13 +11014,13 @@
         <v>11</v>
       </c>
       <c r="BH41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI41">
         <v>3.4</v>
       </c>
       <c r="BJ41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK41">
         <v>1.01</v>
@@ -11032,7 +11032,7 @@
         <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO41">
         <v>5.8</v>
@@ -11062,7 +11062,7 @@
         <v>1.01</v>
       </c>
       <c r="BX41">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY41">
         <v>1.01</v>
@@ -11097,19 +11097,19 @@
         <v>1.37</v>
       </c>
       <c r="G42">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H42">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I42">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J42">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K42">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L42">
         <v>1.33</v>
@@ -11118,40 +11118,40 @@
         <v>1.06</v>
       </c>
       <c r="N42">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O42">
         <v>1.27</v>
       </c>
       <c r="P42">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q42">
         <v>1.81</v>
       </c>
       <c r="R42">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S42">
         <v>3.1</v>
       </c>
       <c r="T42">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U42">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V42">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W42">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X42">
         <v>18.5</v>
       </c>
       <c r="Y42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z42">
         <v>120</v>
@@ -11166,13 +11166,13 @@
         <v>12</v>
       </c>
       <c r="AD42">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AE42">
         <v>230</v>
       </c>
       <c r="AF42">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG42">
         <v>11</v>
@@ -11184,19 +11184,19 @@
         <v>190</v>
       </c>
       <c r="AJ42">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL42">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AM42">
         <v>230</v>
       </c>
       <c r="AN42">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO42">
         <v>360</v>
@@ -11208,10 +11208,10 @@
         <v>23</v>
       </c>
       <c r="AR42">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS42">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT42">
         <v>6.4</v>
@@ -11223,19 +11223,19 @@
         <v>30</v>
       </c>
       <c r="AW42">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX42">
         <v>6.6</v>
       </c>
       <c r="AY42">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ42">
         <v>23</v>
       </c>
       <c r="BA42">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB42">
         <v>8.6</v>
@@ -11247,13 +11247,13 @@
         <v>34</v>
       </c>
       <c r="BE42">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF42">
         <v>6</v>
       </c>
       <c r="BG42">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11378,7 +11378,7 @@
         <v>3.3</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U43">
         <v>1.01</v>
@@ -11450,7 +11450,7 @@
         <v>4.2</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS43">
         <v>1.01</v>
@@ -11462,7 +11462,7 @@
         <v>4.4</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW43">
         <v>1.01</v>
@@ -11581,7 +11581,7 @@
         <v>2.04</v>
       </c>
       <c r="G44">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H44">
         <v>3.55</v>
@@ -11590,10 +11590,10 @@
         <v>3.75</v>
       </c>
       <c r="J44">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K44">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11608,16 +11608,16 @@
         <v>1.17</v>
       </c>
       <c r="P44">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q44">
         <v>1.53</v>
       </c>
       <c r="R44">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S44">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T44">
         <v>1.51</v>
@@ -11629,7 +11629,7 @@
         <v>1.37</v>
       </c>
       <c r="W44">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X44">
         <v>28</v>
@@ -11650,7 +11650,7 @@
         <v>10.5</v>
       </c>
       <c r="AD44">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE44">
         <v>36</v>
@@ -11686,7 +11686,7 @@
         <v>25</v>
       </c>
       <c r="AP44">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ44">
         <v>18.5</v>
@@ -11695,7 +11695,7 @@
         <v>14.5</v>
       </c>
       <c r="AS44">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT44">
         <v>13</v>
@@ -11847,19 +11847,19 @@
         <v>6.2</v>
       </c>
       <c r="O45">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P45">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q45">
         <v>1.46</v>
       </c>
       <c r="R45">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S45">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T45">
         <v>1.52</v>
@@ -11889,7 +11889,7 @@
         <v>29</v>
       </c>
       <c r="AC45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD45">
         <v>10.5</v>
@@ -11910,16 +11910,16 @@
         <v>26</v>
       </c>
       <c r="AJ45">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK45">
         <v>50</v>
       </c>
       <c r="AL45">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM45">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN45">
         <v>34</v>
@@ -11928,7 +11928,7 @@
         <v>7.2</v>
       </c>
       <c r="AP45">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AQ45">
         <v>12.5</v>
@@ -11952,7 +11952,7 @@
         <v>12</v>
       </c>
       <c r="AX45">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AY45">
         <v>14</v>
@@ -11964,19 +11964,19 @@
         <v>20</v>
       </c>
       <c r="BB45">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC45">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD45">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE45">
         <v>15</v>
       </c>
       <c r="BF45">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG45">
         <v>6</v>
@@ -12068,7 +12068,7 @@
         <v>1.73</v>
       </c>
       <c r="H46">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I46">
         <v>5.1</v>
@@ -12086,7 +12086,7 @@
         <v>1.02</v>
       </c>
       <c r="N46">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O46">
         <v>1.12</v>
@@ -12095,16 +12095,16 @@
         <v>3.4</v>
       </c>
       <c r="Q46">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R46">
         <v>2.04</v>
       </c>
       <c r="S46">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="T46">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U46">
         <v>2.98</v>
@@ -12125,10 +12125,10 @@
         <v>55</v>
       </c>
       <c r="AA46">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AB46">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC46">
         <v>13.5</v>
@@ -12140,7 +12140,7 @@
         <v>46</v>
       </c>
       <c r="AF46">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG46">
         <v>12</v>
@@ -12173,13 +12173,13 @@
         <v>32</v>
       </c>
       <c r="AQ46">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="AR46">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS46">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT46">
         <v>16.5</v>
@@ -12215,7 +12215,7 @@
         <v>19</v>
       </c>
       <c r="BE46">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BF46">
         <v>4.6</v>
@@ -12307,10 +12307,10 @@
         <v>2.04</v>
       </c>
       <c r="G47">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H47">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I47">
         <v>3.95</v>
@@ -12337,25 +12337,25 @@
         <v>2.22</v>
       </c>
       <c r="Q47">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="R47">
         <v>1.49</v>
       </c>
       <c r="S47">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T47">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U47">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V47">
         <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X47">
         <v>29</v>
@@ -12376,7 +12376,7 @@
         <v>9</v>
       </c>
       <c r="AD47">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE47">
         <v>42</v>
@@ -12391,7 +12391,7 @@
         <v>16.5</v>
       </c>
       <c r="AI47">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ47">
         <v>25</v>
@@ -12439,13 +12439,13 @@
         <v>12.5</v>
       </c>
       <c r="AY47">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ47">
         <v>14.5</v>
       </c>
       <c r="BA47">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BB47">
         <v>21</v>
@@ -12463,7 +12463,7 @@
         <v>10</v>
       </c>
       <c r="BG47">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BH47">
         <v>4.4</v>
@@ -12546,19 +12546,19 @@
         <v>245</v>
       </c>
       <c r="F48">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>3.1</v>
       </c>
       <c r="H48">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I48">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J48">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K48">
         <v>3.65</v>
@@ -12570,61 +12570,61 @@
         <v>1.05</v>
       </c>
       <c r="N48">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O48">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P48">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q48">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R48">
+        <v>1.49</v>
+      </c>
+      <c r="S48">
+        <v>2.84</v>
+      </c>
+      <c r="T48">
+        <v>1.61</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
+        <v>1.63</v>
+      </c>
+      <c r="W48">
         <v>1.48</v>
       </c>
-      <c r="S48">
-        <v>2.74</v>
-      </c>
-      <c r="T48">
-        <v>1.6</v>
-      </c>
-      <c r="U48">
-        <v>2.44</v>
-      </c>
-      <c r="V48">
-        <v>1.62</v>
-      </c>
-      <c r="W48">
-        <v>1.47</v>
-      </c>
       <c r="X48">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y48">
         <v>14</v>
       </c>
       <c r="Z48">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA48">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB48">
         <v>15</v>
       </c>
       <c r="AC48">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD48">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE48">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF48">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AG48">
         <v>13.5</v>
@@ -12633,70 +12633,70 @@
         <v>15.5</v>
       </c>
       <c r="AI48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ48">
         <v>48</v>
       </c>
       <c r="AK48">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL48">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AM48">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN48">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO48">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP48">
         <v>15.5</v>
       </c>
       <c r="AQ48">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR48">
         <v>16.5</v>
       </c>
       <c r="AS48">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AT48">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU48">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV48">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW48">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AX48">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AY48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ48">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA48">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BB48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC48">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BD48">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE48">
         <v>32</v>
@@ -12717,13 +12717,13 @@
         <v>11</v>
       </c>
       <c r="BK48">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL48">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM48">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN48">
         <v>7.4</v>
@@ -12735,13 +12735,13 @@
         <v>26</v>
       </c>
       <c r="BQ48">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR48">
         <v>38</v>
       </c>
       <c r="BS48">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT48">
         <v>6.6</v>
@@ -12750,7 +12750,7 @@
         <v>4.3</v>
       </c>
       <c r="BV48">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW48">
         <v>4.2</v>
@@ -12759,7 +12759,7 @@
         <v>34</v>
       </c>
       <c r="BY48">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -12797,7 +12797,7 @@
         <v>2.68</v>
       </c>
       <c r="I49">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J49">
         <v>3.6</v>
@@ -12818,7 +12818,7 @@
         <v>1.3</v>
       </c>
       <c r="P49">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q49">
         <v>1.86</v>
@@ -12836,13 +12836,13 @@
         <v>2.3</v>
       </c>
       <c r="V49">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
         <v>1.54</v>
       </c>
       <c r="X49">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y49">
         <v>12.5</v>
@@ -12872,7 +12872,7 @@
         <v>12.5</v>
       </c>
       <c r="AH49">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI49">
         <v>40</v>
@@ -12881,10 +12881,10 @@
         <v>42</v>
       </c>
       <c r="AK49">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL49">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM49">
         <v>80</v>
@@ -12896,7 +12896,7 @@
         <v>24</v>
       </c>
       <c r="AP49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ49">
         <v>11.5</v>
@@ -12944,10 +12944,10 @@
         <v>38</v>
       </c>
       <c r="BF49">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG49">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH49">
         <v>3.7</v>
@@ -12959,7 +12959,7 @@
         <v>9.4</v>
       </c>
       <c r="BK49">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL49">
         <v>120</v>
@@ -12971,7 +12971,7 @@
         <v>6.2</v>
       </c>
       <c r="BO49">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP49">
         <v>21</v>
@@ -12980,7 +12980,7 @@
         <v>1.01</v>
       </c>
       <c r="BR49">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS49">
         <v>1.01</v>
@@ -13030,22 +13030,22 @@
         <v>247</v>
       </c>
       <c r="F50">
+        <v>1.26</v>
+      </c>
+      <c r="G50">
         <v>1.27</v>
-      </c>
-      <c r="G50">
-        <v>1.28</v>
       </c>
       <c r="H50">
         <v>13.5</v>
       </c>
       <c r="I50">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J50">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K50">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L50">
         <v>1.2</v>
@@ -13066,46 +13066,46 @@
         <v>1.42</v>
       </c>
       <c r="R50">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S50">
         <v>2.06</v>
       </c>
       <c r="T50">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U50">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V50">
         <v>1.07</v>
       </c>
       <c r="W50">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X50">
         <v>34</v>
       </c>
       <c r="Y50">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z50">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA50">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AB50">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC50">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD50">
         <v>55</v>
       </c>
       <c r="AE50">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF50">
         <v>9.6</v>
@@ -13117,7 +13117,7 @@
         <v>29</v>
       </c>
       <c r="AI50">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ50">
         <v>11</v>
@@ -13129,40 +13129,40 @@
         <v>32</v>
       </c>
       <c r="AM50">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AN50">
         <v>3.75</v>
       </c>
       <c r="AO50">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ50">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR50">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AS50">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AT50">
         <v>12</v>
       </c>
       <c r="AU50">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV50">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW50">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AX50">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY50">
         <v>10.5</v>
@@ -13171,10 +13171,10 @@
         <v>24</v>
       </c>
       <c r="BA50">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BB50">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC50">
         <v>11.5</v>
@@ -13189,13 +13189,13 @@
         <v>3.3</v>
       </c>
       <c r="BG50">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH50">
         <v>5.8</v>
       </c>
       <c r="BI50">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ50">
         <v>13</v>
@@ -13222,7 +13222,7 @@
         <v>5.3</v>
       </c>
       <c r="BR50">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS50">
         <v>1.01</v>
@@ -13272,10 +13272,10 @@
         <v>248</v>
       </c>
       <c r="F51">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G51">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H51">
         <v>4.1</v>
@@ -13290,10 +13290,10 @@
         <v>3.65</v>
       </c>
       <c r="L51">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N51">
         <v>3.3</v>
@@ -13302,7 +13302,7 @@
         <v>1.38</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q51">
         <v>2.08</v>
@@ -13314,7 +13314,7 @@
         <v>4.1</v>
       </c>
       <c r="T51">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="U51">
         <v>2</v>
@@ -13323,7 +13323,7 @@
         <v>1.29</v>
       </c>
       <c r="W51">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X51">
         <v>13</v>
@@ -13332,106 +13332,106 @@
         <v>14.5</v>
       </c>
       <c r="Z51">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA51">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB51">
         <v>8.800000000000001</v>
       </c>
       <c r="AC51">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD51">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE51">
         <v>60</v>
       </c>
       <c r="AF51">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG51">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AH51">
         <v>20</v>
       </c>
       <c r="AI51">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ51">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK51">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL51">
         <v>44</v>
       </c>
       <c r="AM51">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN51">
         <v>19</v>
       </c>
       <c r="AO51">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AP51">
         <v>10</v>
       </c>
       <c r="AQ51">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR51">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AS51">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AT51">
+        <v>7.6</v>
+      </c>
+      <c r="AU51">
         <v>7.2</v>
       </c>
-      <c r="AU51">
-        <v>6.6</v>
-      </c>
       <c r="AV51">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW51">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="AX51">
+        <v>10.5</v>
+      </c>
+      <c r="AY51">
         <v>9.4</v>
       </c>
-      <c r="AY51">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ51">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA51">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BB51">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC51">
         <v>20</v>
       </c>
       <c r="BD51">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BE51">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG51">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH51">
         <v>3.55</v>
@@ -13517,10 +13517,10 @@
         <v>2.3</v>
       </c>
       <c r="G52">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H52">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I52">
         <v>3.3</v>
@@ -13544,19 +13544,19 @@
         <v>1.25</v>
       </c>
       <c r="P52">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q52">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R52">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S52">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T52">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U52">
         <v>2.36</v>
@@ -13571,16 +13571,16 @@
         <v>19</v>
       </c>
       <c r="Y52">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z52">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AA52">
         <v>130</v>
       </c>
       <c r="AB52">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC52">
         <v>9</v>
@@ -13604,22 +13604,22 @@
         <v>150</v>
       </c>
       <c r="AJ52">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AK52">
         <v>38</v>
       </c>
       <c r="AL52">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM52">
         <v>500</v>
       </c>
       <c r="AN52">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AO52">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP52">
         <v>16</v>
@@ -13631,10 +13631,10 @@
         <v>21</v>
       </c>
       <c r="AS52">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="AT52">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU52">
         <v>7.6</v>
@@ -13643,7 +13643,7 @@
         <v>12</v>
       </c>
       <c r="AW52">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX52">
         <v>14</v>
@@ -13652,7 +13652,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ52">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA52">
         <v>9.800000000000001</v>
@@ -13661,19 +13661,19 @@
         <v>14.5</v>
       </c>
       <c r="BC52">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD52">
         <v>16</v>
       </c>
       <c r="BE52">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF52">
         <v>13</v>
       </c>
       <c r="BG52">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13759,7 +13759,7 @@
         <v>2.4</v>
       </c>
       <c r="G53">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H53">
         <v>3.1</v>
@@ -13798,70 +13798,70 @@
         <v>2.78</v>
       </c>
       <c r="T53">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U53">
         <v>2.44</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X53">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y53">
         <v>16</v>
       </c>
       <c r="Z53">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA53">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB53">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC53">
         <v>10.5</v>
       </c>
       <c r="AD53">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE53">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF53">
         <v>18</v>
       </c>
       <c r="AG53">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH53">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI53">
         <v>38</v>
       </c>
       <c r="AJ53">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK53">
         <v>23</v>
       </c>
       <c r="AL53">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM53">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN53">
         <v>14</v>
       </c>
       <c r="AO53">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP53">
         <v>16.5</v>
@@ -13873,7 +13873,7 @@
         <v>21</v>
       </c>
       <c r="AS53">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT53">
         <v>12.5</v>
@@ -13894,13 +13894,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ53">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA53">
         <v>32</v>
       </c>
       <c r="BB53">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC53">
         <v>20</v>
@@ -13912,10 +13912,10 @@
         <v>55</v>
       </c>
       <c r="BF53">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG53">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13998,16 +13998,16 @@
         <v>251</v>
       </c>
       <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
         <v>2.02</v>
       </c>
-      <c r="G54">
-        <v>2.04</v>
-      </c>
       <c r="H54">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I54">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -14028,16 +14028,16 @@
         <v>1.24</v>
       </c>
       <c r="P54">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q54">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R54">
         <v>1.51</v>
       </c>
       <c r="S54">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T54">
         <v>1.68</v>
@@ -14046,16 +14046,16 @@
         <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W54">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X54">
         <v>19.5</v>
       </c>
       <c r="Y54">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z54">
         <v>30</v>
@@ -14082,22 +14082,22 @@
         <v>10.5</v>
       </c>
       <c r="AH54">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI54">
         <v>44</v>
       </c>
       <c r="AJ54">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK54">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL54">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM54">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AN54">
         <v>11.5</v>
@@ -14106,13 +14106,13 @@
         <v>34</v>
       </c>
       <c r="AP54">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ54">
         <v>16.5</v>
       </c>
       <c r="AR54">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS54">
         <v>32</v>
@@ -14142,13 +14142,13 @@
         <v>40</v>
       </c>
       <c r="BB54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC54">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD54">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="BE54">
         <v>40</v>
@@ -14157,10 +14157,10 @@
         <v>10</v>
       </c>
       <c r="BG54">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BH54">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BI54">
         <v>3.45</v>
@@ -14169,13 +14169,13 @@
         <v>9.4</v>
       </c>
       <c r="BK54">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL54">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM54">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BN54">
         <v>4.9</v>
@@ -14187,37 +14187,37 @@
         <v>14</v>
       </c>
       <c r="BQ54">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR54">
         <v>29</v>
       </c>
       <c r="BS54">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BT54">
         <v>7.4</v>
       </c>
       <c r="BU54">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BV54">
         <v>30</v>
       </c>
       <c r="BW54">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BX54">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY54">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BZ54">
         <v>19.5</v>
       </c>
       <c r="CA54">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="CB54" t="s">
         <v>268</v>
@@ -14243,16 +14243,16 @@
         <v>2.32</v>
       </c>
       <c r="G55">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H55">
         <v>3.4</v>
       </c>
       <c r="I55">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J55">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K55">
         <v>3.6</v>
@@ -14264,28 +14264,28 @@
         <v>1.07</v>
       </c>
       <c r="N55">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O55">
         <v>1.33</v>
       </c>
       <c r="P55">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q55">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R55">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S55">
         <v>3.55</v>
       </c>
       <c r="T55">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U55">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V55">
         <v>1.4</v>
@@ -14294,7 +14294,7 @@
         <v>1.74</v>
       </c>
       <c r="X55">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y55">
         <v>13.5</v>
@@ -14324,7 +14324,7 @@
         <v>11</v>
       </c>
       <c r="AH55">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI55">
         <v>60</v>
@@ -14333,7 +14333,7 @@
         <v>30</v>
       </c>
       <c r="AK55">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL55">
         <v>40</v>
@@ -14345,10 +14345,10 @@
         <v>19</v>
       </c>
       <c r="AO55">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP55">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ55">
         <v>12</v>
@@ -14360,7 +14360,7 @@
         <v>50</v>
       </c>
       <c r="AT55">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU55">
         <v>7.2</v>
@@ -14378,7 +14378,7 @@
         <v>10</v>
       </c>
       <c r="AZ55">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA55">
         <v>44</v>
@@ -14387,13 +14387,13 @@
         <v>26</v>
       </c>
       <c r="BC55">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD55">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE55">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF55">
         <v>16.5</v>
@@ -14482,22 +14482,22 @@
         <v>253</v>
       </c>
       <c r="F56">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G56">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H56">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I56">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J56">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K56">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L56">
         <v>1.4</v>
@@ -14512,10 +14512,10 @@
         <v>1.37</v>
       </c>
       <c r="P56">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q56">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R56">
         <v>1.32</v>
@@ -14527,16 +14527,16 @@
         <v>1.97</v>
       </c>
       <c r="U56">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V56">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W56">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X56">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y56">
         <v>16</v>
@@ -14545,16 +14545,16 @@
         <v>38</v>
       </c>
       <c r="AA56">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB56">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC56">
         <v>8.4</v>
       </c>
       <c r="AD56">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE56">
         <v>150</v>
@@ -14563,7 +14563,7 @@
         <v>10.5</v>
       </c>
       <c r="AG56">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH56">
         <v>22</v>
@@ -14572,7 +14572,7 @@
         <v>80</v>
       </c>
       <c r="AJ56">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK56">
         <v>21</v>
@@ -14581,16 +14581,16 @@
         <v>42</v>
       </c>
       <c r="AM56">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN56">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO56">
         <v>90</v>
       </c>
       <c r="AP56">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ56">
         <v>15</v>
@@ -14599,16 +14599,16 @@
         <v>32</v>
       </c>
       <c r="AS56">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AT56">
         <v>7.4</v>
       </c>
       <c r="AU56">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV56">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW56">
         <v>60</v>
@@ -14617,16 +14617,16 @@
         <v>9.6</v>
       </c>
       <c r="AY56">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ56">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA56">
         <v>65</v>
       </c>
       <c r="BB56">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC56">
         <v>19</v>
@@ -14638,10 +14638,10 @@
         <v>65</v>
       </c>
       <c r="BF56">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG56">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH56">
         <v>970</v>
@@ -14680,7 +14680,7 @@
         <v>1.22</v>
       </c>
       <c r="BT56">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BU56">
         <v>1.22</v>
@@ -14724,7 +14724,7 @@
         <v>254</v>
       </c>
       <c r="F57">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G57">
         <v>2.52</v>
@@ -14736,10 +14736,10 @@
         <v>3.15</v>
       </c>
       <c r="J57">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K57">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L57">
         <v>1.44</v>
@@ -14760,7 +14760,7 @@
         <v>2.04</v>
       </c>
       <c r="R57">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S57">
         <v>3.75</v>
@@ -14805,7 +14805,7 @@
         <v>18</v>
       </c>
       <c r="AG57">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH57">
         <v>19</v>
@@ -14901,7 +14901,7 @@
         <v>140</v>
       </c>
       <c r="BM57">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN57">
         <v>6.2</v>
@@ -14910,7 +14910,7 @@
         <v>4.3</v>
       </c>
       <c r="BP57">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ57">
         <v>4.8</v>
@@ -14919,7 +14919,7 @@
         <v>40</v>
       </c>
       <c r="BS57">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT57">
         <v>7</v>
@@ -14937,7 +14937,7 @@
         <v>40</v>
       </c>
       <c r="BY57">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ57">
         <v>36</v>
@@ -14969,76 +14969,76 @@
         <v>2.82</v>
       </c>
       <c r="G58">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H58">
         <v>2.64</v>
       </c>
       <c r="I58">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K58">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L58">
         <v>1.4</v>
       </c>
       <c r="M58">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N58">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="O58">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P58">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q58">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R58">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S58">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T58">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U58">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W58">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X58">
         <v>13</v>
       </c>
       <c r="Y58">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z58">
         <v>22</v>
       </c>
       <c r="AA58">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB58">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC58">
         <v>7.6</v>
       </c>
       <c r="AD58">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE58">
         <v>44</v>
@@ -15047,37 +15047,37 @@
         <v>20</v>
       </c>
       <c r="AG58">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH58">
         <v>23</v>
       </c>
       <c r="AI58">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ58">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK58">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL58">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM58">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN58">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO58">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP58">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ58">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR58">
         <v>15</v>
@@ -15089,10 +15089,10 @@
         <v>8.6</v>
       </c>
       <c r="AU58">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV58">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW58">
         <v>22</v>
@@ -15101,10 +15101,10 @@
         <v>16.5</v>
       </c>
       <c r="AY58">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ58">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA58">
         <v>32</v>
@@ -15217,13 +15217,13 @@
         <v>8</v>
       </c>
       <c r="I59">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J59">
         <v>4.1</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L59">
         <v>1.31</v>
@@ -15232,7 +15232,7 @@
         <v>1.07</v>
       </c>
       <c r="N59">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O59">
         <v>1.35</v>
@@ -15244,7 +15244,7 @@
         <v>2.04</v>
       </c>
       <c r="R59">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S59">
         <v>3.7</v>
@@ -15271,7 +15271,7 @@
         <v>480</v>
       </c>
       <c r="AA59">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB59">
         <v>7.2</v>
@@ -15286,7 +15286,7 @@
         <v>190</v>
       </c>
       <c r="AF59">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AG59">
         <v>12.5</v>
@@ -15322,10 +15322,10 @@
         <v>18.5</v>
       </c>
       <c r="AR59">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS59">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT59">
         <v>5.9</v>
@@ -15337,7 +15337,7 @@
         <v>14.5</v>
       </c>
       <c r="AW59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX59">
         <v>6.2</v>
@@ -15349,7 +15349,7 @@
         <v>20</v>
       </c>
       <c r="BA59">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BB59">
         <v>11.5</v>
@@ -15361,13 +15361,13 @@
         <v>36</v>
       </c>
       <c r="BE59">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF59">
         <v>8.6</v>
       </c>
       <c r="BG59">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH59">
         <v>1000</v>
@@ -15453,7 +15453,7 @@
         <v>2.92</v>
       </c>
       <c r="G60">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H60">
         <v>2.56</v>
@@ -15468,7 +15468,7 @@
         <v>3.75</v>
       </c>
       <c r="L60">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M60">
         <v>1.06</v>
@@ -15480,7 +15480,7 @@
         <v>1.26</v>
       </c>
       <c r="P60">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q60">
         <v>1.8</v>
@@ -15504,13 +15504,13 @@
         <v>1.51</v>
       </c>
       <c r="X60">
+        <v>17</v>
+      </c>
+      <c r="Y60">
+        <v>12.5</v>
+      </c>
+      <c r="Z60">
         <v>17.5</v>
-      </c>
-      <c r="Y60">
-        <v>13</v>
-      </c>
-      <c r="Z60">
-        <v>18</v>
       </c>
       <c r="AA60">
         <v>36</v>
@@ -15519,13 +15519,13 @@
         <v>14.5</v>
       </c>
       <c r="AC60">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD60">
         <v>12</v>
       </c>
       <c r="AE60">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF60">
         <v>21</v>
@@ -15543,7 +15543,7 @@
         <v>46</v>
       </c>
       <c r="AK60">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL60">
         <v>38</v>
@@ -15552,13 +15552,13 @@
         <v>70</v>
       </c>
       <c r="AN60">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO60">
         <v>18</v>
       </c>
       <c r="AP60">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ60">
         <v>12</v>
@@ -15615,22 +15615,22 @@
         <v>3.75</v>
       </c>
       <c r="BI60">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ60">
         <v>11</v>
       </c>
       <c r="BK60">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL60">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM60">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN60">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO60">
         <v>5.5</v>
@@ -15639,13 +15639,13 @@
         <v>26</v>
       </c>
       <c r="BQ60">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR60">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS60">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT60">
         <v>5.6</v>
@@ -15657,19 +15657,19 @@
         <v>22</v>
       </c>
       <c r="BW60">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX60">
         <v>34</v>
       </c>
       <c r="BY60">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BZ60">
         <v>26</v>
       </c>
       <c r="CA60">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB60" t="s">
         <v>268</v>
@@ -15698,16 +15698,16 @@
         <v>2.2</v>
       </c>
       <c r="H61">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I61">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J61">
         <v>3.8</v>
       </c>
       <c r="K61">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L61">
         <v>1.35</v>
@@ -15749,7 +15749,7 @@
         <v>18</v>
       </c>
       <c r="Y61">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z61">
         <v>32</v>
@@ -15863,13 +15863,13 @@
         <v>10.5</v>
       </c>
       <c r="BK61">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL61">
         <v>110</v>
       </c>
       <c r="BM61">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN61">
         <v>5.8</v>
@@ -15887,10 +15887,10 @@
         <v>30</v>
       </c>
       <c r="BS61">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT61">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU61">
         <v>5.5</v>
@@ -15899,19 +15899,19 @@
         <v>32</v>
       </c>
       <c r="BW61">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX61">
         <v>42</v>
       </c>
       <c r="BY61">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ61">
         <v>25</v>
       </c>
       <c r="CA61">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB61" t="s">
         <v>268</v>
@@ -15958,19 +15958,19 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="O62">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P62">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
       </c>
       <c r="R62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S62">
         <v>3.85</v>
@@ -16194,10 +16194,10 @@
         <v>4.7</v>
       </c>
       <c r="L63">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M63">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N63">
         <v>5.3</v>
@@ -16209,19 +16209,19 @@
         <v>2.42</v>
       </c>
       <c r="Q63">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R63">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S63">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T63">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U63">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
         <v>2.52</v>
@@ -16233,7 +16233,7 @@
         <v>24</v>
       </c>
       <c r="Y63">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z63">
         <v>11.5</v>
@@ -16248,7 +16248,7 @@
         <v>12</v>
       </c>
       <c r="AD63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE63">
         <v>16</v>
@@ -16281,7 +16281,7 @@
         <v>65</v>
       </c>
       <c r="AO63">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP63">
         <v>19.5</v>
@@ -16302,7 +16302,7 @@
         <v>9.4</v>
       </c>
       <c r="AV63">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW63">
         <v>14</v>
@@ -16320,7 +16320,7 @@
         <v>25</v>
       </c>
       <c r="BB63">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC63">
         <v>55</v>
@@ -16332,10 +16332,10 @@
         <v>42</v>
       </c>
       <c r="BF63">
-        <v>8.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BG63">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH63">
         <v>5</v>
@@ -16418,7 +16418,7 @@
         <v>261</v>
       </c>
       <c r="F64">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G64">
         <v>110</v>
@@ -16430,7 +16430,7 @@
         <v>110</v>
       </c>
       <c r="J64">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K64">
         <v>110</v>
@@ -16451,7 +16451,7 @@
         <v>1.25</v>
       </c>
       <c r="Q64">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R64">
         <v>1.18</v>
@@ -16466,10 +16466,10 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -16529,7 +16529,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR64">
         <v>1.01</v>
@@ -16544,7 +16544,7 @@
         <v>1.01</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW64">
         <v>1.01</v>
@@ -16690,7 +16690,7 @@
         <v>1.43</v>
       </c>
       <c r="P65">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q65">
         <v>2.28</v>
@@ -16699,13 +16699,13 @@
         <v>1.24</v>
       </c>
       <c r="S65">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T65">
         <v>2.04</v>
       </c>
       <c r="U65">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V65">
         <v>1.21</v>
@@ -16744,7 +16744,7 @@
         <v>11</v>
       </c>
       <c r="AH65">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI65">
         <v>120</v>
@@ -16753,7 +16753,7 @@
         <v>23</v>
       </c>
       <c r="AK65">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL65">
         <v>60</v>
@@ -16777,7 +16777,7 @@
         <v>14.5</v>
       </c>
       <c r="AS65">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT65">
         <v>6</v>
@@ -16789,7 +16789,7 @@
         <v>18.5</v>
       </c>
       <c r="AW65">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX65">
         <v>8.800000000000001</v>
@@ -16801,43 +16801,43 @@
         <v>20</v>
       </c>
       <c r="BA65">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB65">
         <v>14.5</v>
       </c>
       <c r="BC65">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BD65">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE65">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF65">
         <v>12</v>
       </c>
       <c r="BG65">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH65">
         <v>1000</v>
       </c>
       <c r="BI65">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BJ65">
         <v>16</v>
       </c>
       <c r="BK65">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BN65">
         <v>6</v>
@@ -16849,16 +16849,16 @@
         <v>20</v>
       </c>
       <c r="BQ65">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BR65">
         <v>50</v>
       </c>
       <c r="BS65">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BT65">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU65">
         <v>5.3</v>
@@ -16867,19 +16867,19 @@
         <v>75</v>
       </c>
       <c r="BW65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BX65">
         <v>95</v>
       </c>
       <c r="BY65">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BZ65">
         <v>46</v>
       </c>
       <c r="CA65">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CB65" t="s">
         <v>268</v>
@@ -16920,7 +16920,7 @@
         <v>4</v>
       </c>
       <c r="L66">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M66">
         <v>1.01</v>
@@ -17147,7 +17147,7 @@
         <v>1.62</v>
       </c>
       <c r="G67">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H67">
         <v>5.7</v>
@@ -17195,7 +17195,7 @@
         <v>1.18</v>
       </c>
       <c r="W67">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X67">
         <v>20</v>
@@ -17234,7 +17234,7 @@
         <v>90</v>
       </c>
       <c r="AJ67">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK67">
         <v>19.5</v>
@@ -17246,7 +17246,7 @@
         <v>130</v>
       </c>
       <c r="AN67">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO67">
         <v>110</v>
@@ -17258,10 +17258,10 @@
         <v>16.5</v>
       </c>
       <c r="AR67">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS67">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT67">
         <v>8</v>
@@ -17273,7 +17273,7 @@
         <v>17.5</v>
       </c>
       <c r="AW67">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX67">
         <v>9.199999999999999</v>
@@ -17285,7 +17285,7 @@
         <v>15.5</v>
       </c>
       <c r="BA67">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB67">
         <v>12.5</v>
@@ -17297,13 +17297,13 @@
         <v>16</v>
       </c>
       <c r="BE67">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF67">
         <v>8</v>
       </c>
       <c r="BG67">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH67">
         <v>4.1</v>
@@ -17386,22 +17386,22 @@
         <v>265</v>
       </c>
       <c r="F68">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G68">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H68">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I68">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J68">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K68">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17419,13 +17419,13 @@
         <v>2.52</v>
       </c>
       <c r="Q68">
+        <v>1.61</v>
+      </c>
+      <c r="R68">
         <v>1.6</v>
       </c>
-      <c r="R68">
-        <v>1.59</v>
-      </c>
       <c r="S68">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T68">
         <v>2.22</v>
@@ -17434,7 +17434,7 @@
         <v>1.75</v>
       </c>
       <c r="V68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W68">
         <v>4.5</v>
@@ -17443,25 +17443,25 @@
         <v>26</v>
       </c>
       <c r="Y68">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z68">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA68">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="AB68">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC68">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AD68">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE68">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AF68">
         <v>8</v>
@@ -17473,7 +17473,7 @@
         <v>38</v>
       </c>
       <c r="AI68">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ68">
         <v>9.800000000000001</v>
@@ -17485,37 +17485,37 @@
         <v>55</v>
       </c>
       <c r="AM68">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN68">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO68">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="AP68">
         <v>22</v>
       </c>
       <c r="AQ68">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AR68">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AS68">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AT68">
         <v>8.4</v>
       </c>
       <c r="AU68">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV68">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AW68">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AX68">
         <v>7</v>
@@ -17524,28 +17524,28 @@
         <v>10</v>
       </c>
       <c r="AZ68">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA68">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB68">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC68">
         <v>12.5</v>
       </c>
       <c r="BD68">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE68">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BF68">
         <v>4.1</v>
       </c>
       <c r="BG68">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -17631,10 +17631,10 @@
         <v>1.56</v>
       </c>
       <c r="G69">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H69">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I69">
         <v>6.8</v>
@@ -17643,7 +17643,7 @@
         <v>4.2</v>
       </c>
       <c r="K69">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -17664,13 +17664,13 @@
         <v>1.68</v>
       </c>
       <c r="R69">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S69">
         <v>2.72</v>
       </c>
       <c r="T69">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U69">
         <v>2.06</v>
@@ -17679,7 +17679,7 @@
         <v>1.17</v>
       </c>
       <c r="W69">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X69">
         <v>23</v>
@@ -17727,19 +17727,19 @@
         <v>36</v>
       </c>
       <c r="AM69">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN69">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AO69">
         <v>95</v>
       </c>
       <c r="AP69">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ69">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR69">
         <v>38</v>
@@ -17748,34 +17748,34 @@
         <v>110</v>
       </c>
       <c r="AT69">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU69">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV69">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW69">
         <v>55</v>
       </c>
       <c r="AX69">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY69">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ69">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA69">
         <v>50</v>
       </c>
       <c r="BB69">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC69">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD69">
         <v>23</v>
@@ -17784,7 +17784,7 @@
         <v>70</v>
       </c>
       <c r="BF69">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG69">
         <v>60</v>
@@ -17882,7 +17882,7 @@
         <v>110</v>
       </c>
       <c r="J70">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="K70">
         <v>110</v>
@@ -17894,13 +17894,13 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O70">
         <v>1.02</v>
       </c>
       <c r="P70">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q70">
         <v>1.42</v>
@@ -17918,10 +17918,10 @@
         <v>1.01</v>
       </c>
       <c r="V70">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -17993,7 +17993,7 @@
         <v>1.01</v>
       </c>
       <c r="AU70">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV70">
         <v>1.01</v>
